--- a/Atea modell.xlsx
+++ b/Atea modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D876D2D7-7C27-8E48-8F7F-8F42ABF27949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CE81C0-2D14-8543-A1DA-FEA31C67B5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25040" yWindow="500" windowWidth="26160" windowHeight="26500" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17200" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="143">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -461,6 +461,15 @@
   </si>
   <si>
     <t>Danmark</t>
+  </si>
+  <si>
+    <t>Gearing</t>
+  </si>
+  <si>
+    <t>P/B</t>
+  </si>
+  <si>
+    <t>EBITDA margin</t>
   </si>
 </sst>
 </file>
@@ -650,7 +659,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -710,11 +719,10 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1077,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9D41D6-FA1C-5144-915F-9569A5873643}">
-  <dimension ref="A1:EV80"/>
+  <dimension ref="A1:EV81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -1241,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -1297,6 +1305,13 @@
       <c r="T4" s="12">
         <v>9654</v>
       </c>
+      <c r="U4" s="12">
+        <v>10423</v>
+      </c>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="14"/>
       <c r="Z4" s="23">
         <v>36655</v>
       </c>
@@ -1420,6 +1435,13 @@
       <c r="T5" s="14">
         <v>-6811</v>
       </c>
+      <c r="U5" s="14">
+        <v>-7550</v>
+      </c>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
       <c r="Z5" s="24">
         <v>-28897</v>
       </c>
@@ -1442,42 +1464,42 @@
         <v>-26318</v>
       </c>
       <c r="AG5" s="15">
-        <f>AG4*-0.705</f>
-        <v>-28722.355649999998</v>
-      </c>
-      <c r="AH5" s="57">
+        <f>AG4*-0.715</f>
+        <v>-29129.764950000001</v>
+      </c>
+      <c r="AH5" s="14">
         <f t="shared" ref="AH5:AP5" si="1">AH4*-0.705</f>
         <v>-30445.696989</v>
       </c>
-      <c r="AI5" s="57">
+      <c r="AI5" s="14">
         <f t="shared" si="1"/>
         <v>-32272.438808340004</v>
       </c>
-      <c r="AJ5" s="57">
+      <c r="AJ5" s="14">
         <f t="shared" si="1"/>
         <v>-34208.785136840408</v>
       </c>
-      <c r="AK5" s="57">
+      <c r="AK5" s="14">
         <f t="shared" si="1"/>
         <v>-36261.312245050831</v>
       </c>
-      <c r="AL5" s="57">
+      <c r="AL5" s="14">
         <f t="shared" si="1"/>
         <v>-38436.990979753878</v>
       </c>
-      <c r="AM5" s="57">
+      <c r="AM5" s="14">
         <f t="shared" si="1"/>
         <v>-40743.210438539121</v>
       </c>
-      <c r="AN5" s="57">
+      <c r="AN5" s="14">
         <f t="shared" si="1"/>
         <v>-43187.803064851469</v>
       </c>
-      <c r="AO5" s="57">
+      <c r="AO5" s="14">
         <f t="shared" si="1"/>
         <v>-45779.071248742555</v>
       </c>
-      <c r="AP5" s="57">
+      <c r="AP5" s="14">
         <f t="shared" si="1"/>
         <v>-48525.815523667115</v>
       </c>
@@ -1488,7 +1510,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>18093.838972999998</v>
+        <v>17419.534414999998</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>49</v>
@@ -1561,6 +1583,14 @@
         <f>SUM(T4:T5)</f>
         <v>2843</v>
       </c>
+      <c r="U6" s="14">
+        <f>SUM(U4:U5)</f>
+        <v>2873</v>
+      </c>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
       <c r="Z6" s="14">
         <f t="shared" ref="Z6:AE6" si="3">SUM(Z4:Z5)</f>
         <v>7758</v>
@@ -1591,7 +1621,7 @@
       </c>
       <c r="AG6" s="15">
         <f t="shared" ref="AG6" si="5">SUM(AG4:AG5)</f>
-        <v>12018.574350000003</v>
+        <v>11611.16505</v>
       </c>
       <c r="AH6" s="14">
         <f t="shared" ref="AH6" si="6">SUM(AH4:AH5)</f>
@@ -1635,7 +1665,7 @@
         <v>36</v>
       </c>
       <c r="B7" s="5">
-        <f>S35</f>
+        <f>S36</f>
         <v>1594</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1692,6 +1722,13 @@
       <c r="T7" s="14">
         <v>-2092</v>
       </c>
+      <c r="U7" s="14">
+        <v>-2118</v>
+      </c>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
       <c r="Z7" s="24">
         <v>-5584</v>
       </c>
@@ -1714,44 +1751,44 @@
         <v>-7963</v>
       </c>
       <c r="AG7" s="15">
-        <f>AF7*1.08</f>
-        <v>-8600.0400000000009</v>
+        <f>AF7*1.07</f>
+        <v>-8520.41</v>
       </c>
       <c r="AH7" s="14">
         <f>AG7*1.05</f>
-        <v>-9030.0420000000013</v>
+        <v>-8946.4305000000004</v>
       </c>
       <c r="AI7" s="14">
         <f t="shared" ref="AI7:AP7" si="15">AH7*1.05</f>
-        <v>-9481.544100000001</v>
+        <v>-9393.7520250000016</v>
       </c>
       <c r="AJ7" s="14">
         <f t="shared" si="15"/>
-        <v>-9955.6213050000006</v>
+        <v>-9863.4396262500013</v>
       </c>
       <c r="AK7" s="14">
         <f t="shared" si="15"/>
-        <v>-10453.402370250002</v>
+        <v>-10356.611607562501</v>
       </c>
       <c r="AL7" s="14">
         <f t="shared" si="15"/>
-        <v>-10976.072488762502</v>
+        <v>-10874.442187940627</v>
       </c>
       <c r="AM7" s="14">
         <f t="shared" si="15"/>
-        <v>-11524.876113200628</v>
+        <v>-11418.164297337658</v>
       </c>
       <c r="AN7" s="14">
         <f t="shared" si="15"/>
-        <v>-12101.119918860659</v>
+        <v>-11989.072512204542</v>
       </c>
       <c r="AO7" s="14">
         <f t="shared" si="15"/>
-        <v>-12706.175914803693</v>
+        <v>-12588.52613781477</v>
       </c>
       <c r="AP7" s="14">
         <f t="shared" si="15"/>
-        <v>-13341.484710543878</v>
+        <v>-13217.952444705508</v>
       </c>
     </row>
     <row r="8" spans="1:152" x14ac:dyDescent="0.25">
@@ -1759,7 +1796,7 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <f>S41+S46</f>
+        <f>S42+S47</f>
         <v>592</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1816,6 +1853,13 @@
       <c r="T8" s="14">
         <v>-233</v>
       </c>
+      <c r="U8" s="14">
+        <v>-247</v>
+      </c>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
       <c r="Z8" s="24">
         <v>-766</v>
       </c>
@@ -1838,7 +1882,7 @@
         <v>-931</v>
       </c>
       <c r="AG8" s="15">
-        <f t="shared" ref="AG8:AH9" si="16">AF8*1.085</f>
+        <f t="shared" ref="AG8:AG9" si="16">AF8*1.085</f>
         <v>-1010.135</v>
       </c>
       <c r="AH8" s="14">
@@ -1884,7 +1928,7 @@
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>17091.838972999998</v>
+        <v>16417.534414999998</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>52</v>
@@ -1940,6 +1984,13 @@
       <c r="T9" s="14">
         <v>0</v>
       </c>
+      <c r="U9" s="14">
+        <v>0</v>
+      </c>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
       <c r="Z9" s="24">
         <v>-73</v>
       </c>
@@ -2075,6 +2126,14 @@
         <f>SUM(T6:T9)</f>
         <v>518</v>
       </c>
+      <c r="U10" s="12">
+        <f>SUM(U6:U9)</f>
+        <v>508</v>
+      </c>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
       <c r="Z10" s="12">
         <f t="shared" ref="Z10:AE10" si="19">SUM(Z6:Z9)</f>
         <v>1335</v>
@@ -2105,43 +2164,43 @@
       </c>
       <c r="AG10" s="13">
         <f t="shared" ref="AG10" si="21">SUM(AG6:AG9)</f>
-        <v>2399.7193500000017</v>
+        <v>2071.9400499999997</v>
       </c>
       <c r="AH10" s="12">
         <f t="shared" ref="AH10" si="22">SUM(AH6:AH9)</f>
-        <v>2639.8910610000025</v>
+        <v>2723.5025610000034</v>
       </c>
       <c r="AI10" s="12">
         <f t="shared" ref="AI10" si="23">SUM(AI6:AI9)</f>
-        <v>2899.2825021600042</v>
+        <v>2987.0745771600036</v>
       </c>
       <c r="AJ10" s="12">
         <f t="shared" ref="AJ10" si="24">SUM(AJ6:AJ9)</f>
-        <v>3179.2873286646022</v>
+        <v>3271.4690074146015</v>
       </c>
       <c r="AK10" s="12">
         <f t="shared" ref="AK10" si="25">SUM(AK6:AK9)</f>
-        <v>3481.3948385782287</v>
+        <v>3578.185601265729</v>
       </c>
       <c r="AL10" s="12">
         <f t="shared" ref="AL10" si="26">SUM(AL6:AL9)</f>
-        <v>3807.1963125963634</v>
+        <v>3908.8266134182381</v>
       </c>
       <c r="AM10" s="12">
         <f t="shared" ref="AM10" si="27">SUM(AM6:AM9)</f>
-        <v>4158.3917642407505</v>
+        <v>4265.1035801037197</v>
       </c>
       <c r="AN10" s="12">
         <f t="shared" ref="AN10" si="28">SUM(AN6:AN9)</f>
-        <v>4536.7971266282393</v>
+        <v>4648.8445332843557</v>
       </c>
       <c r="AO10" s="12">
         <f t="shared" ref="AO10" si="29">SUM(AO6:AO9)</f>
-        <v>4944.351903585627</v>
+        <v>5062.0016805745499</v>
       </c>
       <c r="AP10" s="12">
         <f t="shared" ref="AP10" si="30">SUM(AP6:AP9)</f>
-        <v>5383.1273146284402</v>
+        <v>5506.6595804668104</v>
       </c>
     </row>
     <row r="11" spans="1:152" x14ac:dyDescent="0.25">
@@ -2199,6 +2258,13 @@
       <c r="T11" s="14">
         <v>-194</v>
       </c>
+      <c r="U11" s="14">
+        <v>-188</v>
+      </c>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
       <c r="Z11" s="24">
         <f>-584-5</f>
         <v>-589</v>
@@ -2223,46 +2289,53 @@
         <v>-779</v>
       </c>
       <c r="AG11" s="15">
-        <v>-800</v>
+        <v>-765</v>
       </c>
       <c r="AH11" s="14">
-        <f t="shared" ref="AH8:AP11" si="31">AG11*1.075</f>
-        <v>-860</v>
+        <f t="shared" ref="AH11:AP11" si="31">AG11*1.075</f>
+        <v>-822.375</v>
       </c>
       <c r="AI11" s="14">
         <f t="shared" si="31"/>
-        <v>-924.5</v>
+        <v>-884.05312499999991</v>
       </c>
       <c r="AJ11" s="14">
         <f t="shared" si="31"/>
-        <v>-993.83749999999998</v>
+        <v>-950.35710937499982</v>
       </c>
       <c r="AK11" s="14">
         <f t="shared" si="31"/>
-        <v>-1068.3753124999998</v>
+        <v>-1021.6338925781248</v>
       </c>
       <c r="AL11" s="14">
         <f t="shared" si="31"/>
-        <v>-1148.5034609374998</v>
+        <v>-1098.2564345214842</v>
       </c>
       <c r="AM11" s="14">
         <f t="shared" si="31"/>
-        <v>-1234.6412205078122</v>
+        <v>-1180.6256671105955</v>
       </c>
       <c r="AN11" s="14">
         <f t="shared" si="31"/>
-        <v>-1327.239312045898</v>
+        <v>-1269.1725921438901</v>
       </c>
       <c r="AO11" s="14">
         <f t="shared" si="31"/>
-        <v>-1426.7822604493404</v>
+        <v>-1364.3605365546819</v>
       </c>
       <c r="AP11" s="14">
         <f t="shared" si="31"/>
-        <v>-1533.7909299830408</v>
+        <v>-1466.6875767962829</v>
       </c>
     </row>
     <row r="12" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="20">
+        <f>(B8-B7)/AG10</f>
+        <v>-0.48360472591859022</v>
+      </c>
       <c r="C12" s="1" t="s">
         <v>55</v>
       </c>
@@ -2334,7 +2407,14 @@
         <f>SUM(T10:T11)</f>
         <v>324</v>
       </c>
-      <c r="U12" s="14"/>
+      <c r="U12" s="12">
+        <f>SUM(U10:U11)</f>
+        <v>320</v>
+      </c>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14"/>
       <c r="Z12" s="12">
         <f t="shared" ref="Z12:AE12" si="33">SUM(Z10:Z11)</f>
         <v>746</v>
@@ -2365,43 +2445,43 @@
       </c>
       <c r="AG12" s="13">
         <f t="shared" ref="AG12" si="35">SUM(AG10:AG11)</f>
-        <v>1599.7193500000017</v>
+        <v>1306.9400499999997</v>
       </c>
       <c r="AH12" s="12">
         <f t="shared" ref="AH12" si="36">SUM(AH10:AH11)</f>
-        <v>1779.8910610000025</v>
+        <v>1901.1275610000034</v>
       </c>
       <c r="AI12" s="12">
         <f t="shared" ref="AI12" si="37">SUM(AI10:AI11)</f>
-        <v>1974.7825021600042</v>
+        <v>2103.0214521600037</v>
       </c>
       <c r="AJ12" s="12">
         <f t="shared" ref="AJ12" si="38">SUM(AJ10:AJ11)</f>
-        <v>2185.4498286646021</v>
+        <v>2321.1118980396018</v>
       </c>
       <c r="AK12" s="12">
         <f t="shared" ref="AK12" si="39">SUM(AK10:AK11)</f>
-        <v>2413.0195260782289</v>
+        <v>2556.5517086876043</v>
       </c>
       <c r="AL12" s="12">
         <f t="shared" ref="AL12" si="40">SUM(AL10:AL11)</f>
-        <v>2658.6928516588637</v>
+        <v>2810.570178896754</v>
       </c>
       <c r="AM12" s="12">
         <f t="shared" ref="AM12" si="41">SUM(AM10:AM11)</f>
-        <v>2923.7505437329382</v>
+        <v>3084.4779129931239</v>
       </c>
       <c r="AN12" s="12">
         <f t="shared" ref="AN12" si="42">SUM(AN10:AN11)</f>
-        <v>3209.5578145823411</v>
+        <v>3379.6719411404656</v>
       </c>
       <c r="AO12" s="12">
         <f t="shared" ref="AO12" si="43">SUM(AO10:AO11)</f>
-        <v>3517.5696431362867</v>
+        <v>3697.6411440198681</v>
       </c>
       <c r="AP12" s="12">
         <f t="shared" ref="AP12" si="44">SUM(AP10:AP11)</f>
-        <v>3849.3363846453994</v>
+        <v>4039.9720036705276</v>
       </c>
     </row>
     <row r="13" spans="1:152" x14ac:dyDescent="0.25">
@@ -2459,6 +2539,13 @@
       <c r="T13" s="14">
         <v>-16</v>
       </c>
+      <c r="U13" s="14">
+        <v>-37</v>
+      </c>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
       <c r="Z13" s="14">
         <v>-90</v>
       </c>
@@ -2522,6 +2609,13 @@
       </c>
     </row>
     <row r="14" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="8">
+        <f>B6/T41</f>
+        <v>3.8017316488432993</v>
+      </c>
       <c r="C14" s="2" t="s">
         <v>57</v>
       </c>
@@ -2593,6 +2687,14 @@
         <f>SUM(T12:T13)</f>
         <v>308</v>
       </c>
+      <c r="U14" s="14">
+        <f>SUM(U12:U13)</f>
+        <v>283</v>
+      </c>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
       <c r="Z14" s="14">
         <f t="shared" ref="Z14:AE14" si="47">SUM(Z12:Z13)</f>
         <v>656</v>
@@ -2623,43 +2725,43 @@
       </c>
       <c r="AG14" s="15">
         <f t="shared" ref="AG14" si="49">SUM(AG12:AG13)</f>
-        <v>1355.6093500000015</v>
+        <v>1062.8300499999996</v>
       </c>
       <c r="AH14" s="14">
         <f t="shared" ref="AH14" si="50">SUM(AH12:AH13)</f>
-        <v>1528.4577610000024</v>
+        <v>1649.6942610000033</v>
       </c>
       <c r="AI14" s="14">
         <f t="shared" ref="AI14" si="51">SUM(AI12:AI13)</f>
-        <v>1715.8062031600043</v>
+        <v>1844.0451531600038</v>
       </c>
       <c r="AJ14" s="14">
         <f t="shared" ref="AJ14" si="52">SUM(AJ12:AJ13)</f>
-        <v>1918.704240694602</v>
+        <v>2054.3663100696017</v>
       </c>
       <c r="AK14" s="14">
         <f t="shared" ref="AK14" si="53">SUM(AK12:AK13)</f>
-        <v>2138.2715704691291</v>
+        <v>2281.8037530785041</v>
       </c>
       <c r="AL14" s="14">
         <f t="shared" ref="AL14" si="54">SUM(AL12:AL13)</f>
-        <v>2375.7024573814906</v>
+        <v>2527.5797846193809</v>
       </c>
       <c r="AM14" s="14">
         <f t="shared" ref="AM14" si="55">SUM(AM12:AM13)</f>
-        <v>2632.2704376272441</v>
+        <v>2792.9978068874298</v>
       </c>
       <c r="AN14" s="14">
         <f t="shared" ref="AN14" si="56">SUM(AN12:AN13)</f>
-        <v>2909.3333052934759</v>
+        <v>3079.4474318516004</v>
       </c>
       <c r="AO14" s="14">
         <f t="shared" ref="AO14" si="57">SUM(AO12:AO13)</f>
-        <v>3208.3383985687556</v>
+        <v>3388.409899452337</v>
       </c>
       <c r="AP14" s="14">
         <f t="shared" ref="AP14" si="58">SUM(AP12:AP13)</f>
-        <v>3530.8282027408422</v>
+        <v>3721.4638217659704</v>
       </c>
     </row>
     <row r="15" spans="1:152" x14ac:dyDescent="0.25">
@@ -2717,6 +2819,13 @@
       <c r="T15" s="14">
         <v>-71</v>
       </c>
+      <c r="U15" s="14">
+        <v>-65</v>
+      </c>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
       <c r="Z15" s="14">
         <v>-127</v>
       </c>
@@ -2740,43 +2849,43 @@
       </c>
       <c r="AG15" s="15">
         <f t="shared" ref="AG15:AP15" si="59">AG14*-0.22</f>
-        <v>-298.23405700000035</v>
+        <v>-233.82261099999991</v>
       </c>
       <c r="AH15" s="14">
         <f t="shared" si="59"/>
-        <v>-336.26070742000053</v>
+        <v>-362.93273742000071</v>
       </c>
       <c r="AI15" s="14">
         <f t="shared" si="59"/>
-        <v>-377.47736469520095</v>
+        <v>-405.68993369520086</v>
       </c>
       <c r="AJ15" s="14">
         <f t="shared" si="59"/>
-        <v>-422.11493295281247</v>
+        <v>-451.96058821531238</v>
       </c>
       <c r="AK15" s="14">
         <f t="shared" si="59"/>
-        <v>-470.41974550320839</v>
+        <v>-501.99682567727092</v>
       </c>
       <c r="AL15" s="14">
         <f t="shared" si="59"/>
-        <v>-522.65454062392791</v>
+        <v>-556.06755261626381</v>
       </c>
       <c r="AM15" s="14">
         <f t="shared" si="59"/>
-        <v>-579.09949627799369</v>
+        <v>-614.45951751523455</v>
       </c>
       <c r="AN15" s="14">
         <f t="shared" si="59"/>
-        <v>-640.05332716456473</v>
+        <v>-677.47843500735212</v>
       </c>
       <c r="AO15" s="14">
         <f t="shared" si="59"/>
-        <v>-705.83444768512618</v>
+        <v>-745.45017787951417</v>
       </c>
       <c r="AP15" s="14">
         <f t="shared" si="59"/>
-        <v>-776.7822046029853</v>
+        <v>-818.72204078851348</v>
       </c>
     </row>
     <row r="16" spans="1:152" x14ac:dyDescent="0.25">
@@ -2851,6 +2960,14 @@
         <f>SUM(T14:T15)</f>
         <v>237</v>
       </c>
+      <c r="U16" s="12">
+        <f>SUM(U14:U15)</f>
+        <v>218</v>
+      </c>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
       <c r="Z16" s="12">
         <f t="shared" ref="Z16:AE16" si="61">SUM(Z14:Z15)</f>
         <v>529</v>
@@ -2881,486 +2998,486 @@
       </c>
       <c r="AG16" s="13">
         <f t="shared" ref="AG16" si="63">SUM(AG14:AG15)</f>
-        <v>1057.3752930000012</v>
+        <v>829.00743899999964</v>
       </c>
       <c r="AH16" s="12">
         <f t="shared" ref="AH16" si="64">SUM(AH14:AH15)</f>
-        <v>1192.1970535800019</v>
+        <v>1286.7615235800026</v>
       </c>
       <c r="AI16" s="12">
         <f t="shared" ref="AI16" si="65">SUM(AI14:AI15)</f>
-        <v>1338.3288384648033</v>
+        <v>1438.355219464803</v>
       </c>
       <c r="AJ16" s="12">
         <f t="shared" ref="AJ16" si="66">SUM(AJ14:AJ15)</f>
-        <v>1496.5893077417895</v>
+        <v>1602.4057218542894</v>
       </c>
       <c r="AK16" s="12">
         <f t="shared" ref="AK16" si="67">SUM(AK14:AK15)</f>
-        <v>1667.8518249659207</v>
+        <v>1779.8069274012332</v>
       </c>
       <c r="AL16" s="12">
         <f t="shared" ref="AL16" si="68">SUM(AL14:AL15)</f>
-        <v>1853.0479167575627</v>
+        <v>1971.5122320031171</v>
       </c>
       <c r="AM16" s="12">
         <f t="shared" ref="AM16" si="69">SUM(AM14:AM15)</f>
-        <v>2053.1709413492504</v>
+        <v>2178.5382893721953</v>
       </c>
       <c r="AN16" s="12">
         <f t="shared" ref="AN16" si="70">SUM(AN14:AN15)</f>
-        <v>2269.2799781289114</v>
+        <v>2401.9689968442481</v>
       </c>
       <c r="AO16" s="12">
         <f t="shared" ref="AO16" si="71">SUM(AO14:AO15)</f>
-        <v>2502.5039508836294</v>
+        <v>2642.9597215728227</v>
       </c>
       <c r="AP16" s="12">
         <f t="shared" ref="AP16" si="72">SUM(AP14:AP15)</f>
-        <v>2754.0459981378572</v>
+        <v>2902.741780977457</v>
       </c>
       <c r="AQ16" s="12">
         <f>AP16*(1+$AS$20)</f>
-        <v>2726.5055381564785</v>
+        <v>2873.7143631676822</v>
       </c>
       <c r="AR16" s="12">
         <f t="shared" ref="AR16:DC16" si="73">AQ16*(1+$AS$20)</f>
-        <v>2699.2404827749137</v>
+        <v>2844.9772195360056</v>
       </c>
       <c r="AS16" s="12">
         <f t="shared" si="73"/>
-        <v>2672.2480779471648</v>
+        <v>2816.5274473406457</v>
       </c>
       <c r="AT16" s="12">
         <f t="shared" si="73"/>
-        <v>2645.5255971676929</v>
+        <v>2788.3621728672392</v>
       </c>
       <c r="AU16" s="12">
         <f t="shared" si="73"/>
-        <v>2619.0703411960158</v>
+        <v>2760.4785511385667</v>
       </c>
       <c r="AV16" s="12">
         <f t="shared" si="73"/>
-        <v>2592.8796377840554</v>
+        <v>2732.873765627181</v>
       </c>
       <c r="AW16" s="12">
         <f t="shared" si="73"/>
-        <v>2566.9508414062147</v>
+        <v>2705.5450279709094</v>
       </c>
       <c r="AX16" s="12">
         <f t="shared" si="73"/>
-        <v>2541.2813329921528</v>
+        <v>2678.4895776912003</v>
       </c>
       <c r="AY16" s="12">
         <f t="shared" si="73"/>
-        <v>2515.8685196622314</v>
+        <v>2651.7046819142884</v>
       </c>
       <c r="AZ16" s="12">
         <f t="shared" si="73"/>
-        <v>2490.7098344656092</v>
+        <v>2625.1876350951457</v>
       </c>
       <c r="BA16" s="12">
         <f t="shared" si="73"/>
-        <v>2465.8027361209529</v>
+        <v>2598.9357587441941</v>
       </c>
       <c r="BB16" s="12">
         <f t="shared" si="73"/>
-        <v>2441.1447087597435</v>
+        <v>2572.946401156752</v>
       </c>
       <c r="BC16" s="12">
         <f t="shared" si="73"/>
-        <v>2416.733261672146</v>
+        <v>2547.2169371451846</v>
       </c>
       <c r="BD16" s="12">
         <f t="shared" si="73"/>
-        <v>2392.5659290554245</v>
+        <v>2521.7447677737327</v>
       </c>
       <c r="BE16" s="12">
         <f t="shared" si="73"/>
-        <v>2368.64026976487</v>
+        <v>2496.5273200959955</v>
       </c>
       <c r="BF16" s="12">
         <f t="shared" si="73"/>
-        <v>2344.9538670672214</v>
+        <v>2471.5620468950356</v>
       </c>
       <c r="BG16" s="12">
         <f t="shared" si="73"/>
-        <v>2321.5043283965492</v>
+        <v>2446.8464264260851</v>
       </c>
       <c r="BH16" s="12">
         <f t="shared" si="73"/>
-        <v>2298.2892851125839</v>
+        <v>2422.3779621618241</v>
       </c>
       <c r="BI16" s="12">
         <f t="shared" si="73"/>
-        <v>2275.3063922614579</v>
+        <v>2398.154182540206</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="73"/>
-        <v>2252.5533283388431</v>
+        <v>2374.1726407148039</v>
       </c>
       <c r="BK16" s="12">
         <f t="shared" si="73"/>
-        <v>2230.0277950554546</v>
+        <v>2350.4309143076557</v>
       </c>
       <c r="BL16" s="12">
         <f t="shared" si="73"/>
-        <v>2207.7275171049</v>
+        <v>2326.9266051645791</v>
       </c>
       <c r="BM16" s="12">
         <f t="shared" si="73"/>
-        <v>2185.6502419338508</v>
+        <v>2303.6573391129332</v>
       </c>
       <c r="BN16" s="12">
         <f t="shared" si="73"/>
-        <v>2163.7937395145123</v>
+        <v>2280.6207657218038</v>
       </c>
       <c r="BO16" s="12">
         <f t="shared" si="73"/>
-        <v>2142.1558021193673</v>
+        <v>2257.8145580645855</v>
       </c>
       <c r="BP16" s="12">
         <f t="shared" si="73"/>
-        <v>2120.7342440981738</v>
+        <v>2235.2364124839396</v>
       </c>
       <c r="BQ16" s="12">
         <f t="shared" si="73"/>
-        <v>2099.526901657192</v>
+        <v>2212.8840483591002</v>
       </c>
       <c r="BR16" s="12">
         <f t="shared" si="73"/>
-        <v>2078.53163264062</v>
+        <v>2190.7552078755093</v>
       </c>
       <c r="BS16" s="12">
         <f t="shared" si="73"/>
-        <v>2057.7463163142138</v>
+        <v>2168.8476557967542</v>
       </c>
       <c r="BT16" s="12">
         <f t="shared" si="73"/>
-        <v>2037.1688531510717</v>
+        <v>2147.1591792387867</v>
       </c>
       <c r="BU16" s="12">
         <f t="shared" si="73"/>
-        <v>2016.797164619561</v>
+        <v>2125.687587446399</v>
       </c>
       <c r="BV16" s="12">
         <f t="shared" si="73"/>
-        <v>1996.6291929733654</v>
+        <v>2104.4307115719348</v>
       </c>
       <c r="BW16" s="12">
         <f t="shared" si="73"/>
-        <v>1976.6629010436318</v>
+        <v>2083.3864044562156</v>
       </c>
       <c r="BX16" s="12">
         <f t="shared" si="73"/>
-        <v>1956.8962720331954</v>
+        <v>2062.5525404116534</v>
       </c>
       <c r="BY16" s="12">
         <f t="shared" si="73"/>
-        <v>1937.3273093128635</v>
+        <v>2041.9270150075367</v>
       </c>
       <c r="BZ16" s="12">
         <f t="shared" si="73"/>
-        <v>1917.9540362197349</v>
+        <v>2021.5077448574614</v>
       </c>
       <c r="CA16" s="12">
         <f t="shared" si="73"/>
-        <v>1898.7744958575377</v>
+        <v>2001.2926674088867</v>
       </c>
       <c r="CB16" s="12">
         <f t="shared" si="73"/>
-        <v>1879.7867508989623</v>
+        <v>1981.2797407347978</v>
       </c>
       <c r="CC16" s="12">
         <f t="shared" si="73"/>
-        <v>1860.9888833899727</v>
+        <v>1961.4669433274498</v>
       </c>
       <c r="CD16" s="12">
         <f t="shared" si="73"/>
-        <v>1842.3789945560729</v>
+        <v>1941.8522738941754</v>
       </c>
       <c r="CE16" s="12">
         <f t="shared" si="73"/>
-        <v>1823.9552046105123</v>
+        <v>1922.4337511552335</v>
       </c>
       <c r="CF16" s="12">
         <f t="shared" si="73"/>
-        <v>1805.715652564407</v>
+        <v>1903.209413643681</v>
       </c>
       <c r="CG16" s="12">
         <f t="shared" si="73"/>
-        <v>1787.6584960387629</v>
+        <v>1884.1773195072442</v>
       </c>
       <c r="CH16" s="12">
         <f t="shared" si="73"/>
-        <v>1769.7819110783753</v>
+        <v>1865.3355463121718</v>
       </c>
       <c r="CI16" s="12">
         <f t="shared" si="73"/>
-        <v>1752.0840919675916</v>
+        <v>1846.6821908490501</v>
       </c>
       <c r="CJ16" s="12">
         <f t="shared" si="73"/>
-        <v>1734.5632510479156</v>
+        <v>1828.2153689405595</v>
       </c>
       <c r="CK16" s="12">
         <f t="shared" si="73"/>
-        <v>1717.2176185374365</v>
+        <v>1809.933215251154</v>
       </c>
       <c r="CL16" s="12">
         <f t="shared" si="73"/>
-        <v>1700.0454423520621</v>
+        <v>1791.8338830986424</v>
       </c>
       <c r="CM16" s="12">
         <f t="shared" si="73"/>
-        <v>1683.0449879285416</v>
+        <v>1773.9155442676561</v>
       </c>
       <c r="CN16" s="12">
         <f t="shared" si="73"/>
-        <v>1666.2145380492561</v>
+        <v>1756.1763888249795</v>
       </c>
       <c r="CO16" s="12">
         <f t="shared" si="73"/>
-        <v>1649.5523926687636</v>
+        <v>1738.6146249367298</v>
       </c>
       <c r="CP16" s="12">
         <f t="shared" si="73"/>
-        <v>1633.0568687420759</v>
+        <v>1721.2284786873624</v>
       </c>
       <c r="CQ16" s="12">
         <f t="shared" si="73"/>
-        <v>1616.7263000546552</v>
+        <v>1704.0161939004888</v>
       </c>
       <c r="CR16" s="12">
         <f t="shared" si="73"/>
-        <v>1600.5590370541086</v>
+        <v>1686.9760319614838</v>
       </c>
       <c r="CS16" s="12">
         <f t="shared" si="73"/>
-        <v>1584.5534466835675</v>
+        <v>1670.1062716418689</v>
       </c>
       <c r="CT16" s="12">
         <f t="shared" si="73"/>
-        <v>1568.7079122167318</v>
+        <v>1653.4052089254503</v>
       </c>
       <c r="CU16" s="12">
         <f t="shared" si="73"/>
-        <v>1553.0208330945645</v>
+        <v>1636.8711568361957</v>
       </c>
       <c r="CV16" s="12">
         <f t="shared" si="73"/>
-        <v>1537.4906247636188</v>
+        <v>1620.5024452678338</v>
       </c>
       <c r="CW16" s="12">
         <f t="shared" si="73"/>
-        <v>1522.1157185159827</v>
+        <v>1604.2974208151554</v>
       </c>
       <c r="CX16" s="12">
         <f t="shared" si="73"/>
-        <v>1506.8945613308229</v>
+        <v>1588.254446607004</v>
       </c>
       <c r="CY16" s="12">
         <f t="shared" si="73"/>
-        <v>1491.8256157175147</v>
+        <v>1572.3719021409338</v>
       </c>
       <c r="CZ16" s="12">
         <f t="shared" si="73"/>
-        <v>1476.9073595603395</v>
+        <v>1556.6481831195244</v>
       </c>
       <c r="DA16" s="12">
         <f t="shared" si="73"/>
-        <v>1462.138285964736</v>
+        <v>1541.0817012883292</v>
       </c>
       <c r="DB16" s="12">
         <f t="shared" si="73"/>
-        <v>1447.5169031050887</v>
+        <v>1525.6708842754458</v>
       </c>
       <c r="DC16" s="12">
         <f t="shared" si="73"/>
-        <v>1433.0417340740378</v>
+        <v>1510.4141754326913</v>
       </c>
       <c r="DD16" s="12">
         <f t="shared" ref="DD16:EV16" si="74">DC16*(1+$AS$20)</f>
-        <v>1418.7113167332973</v>
+        <v>1495.3100336783643</v>
       </c>
       <c r="DE16" s="12">
         <f t="shared" si="74"/>
-        <v>1404.5242035659644</v>
+        <v>1480.3569333415808</v>
       </c>
       <c r="DF16" s="12">
         <f t="shared" si="74"/>
-        <v>1390.4789615303048</v>
+        <v>1465.5533640081649</v>
       </c>
       <c r="DG16" s="12">
         <f t="shared" si="74"/>
-        <v>1376.5741719150017</v>
+        <v>1450.8978303680833</v>
       </c>
       <c r="DH16" s="12">
         <f t="shared" si="74"/>
-        <v>1362.8084301958515</v>
+        <v>1436.3888520644025</v>
       </c>
       <c r="DI16" s="12">
         <f t="shared" si="74"/>
-        <v>1349.180345893893</v>
+        <v>1422.0249635437585</v>
       </c>
       <c r="DJ16" s="12">
         <f t="shared" si="74"/>
-        <v>1335.6885424349541</v>
+        <v>1407.804713908321</v>
       </c>
       <c r="DK16" s="12">
         <f t="shared" si="74"/>
-        <v>1322.3316570106047</v>
+        <v>1393.7266667692377</v>
       </c>
       <c r="DL16" s="12">
         <f t="shared" si="74"/>
-        <v>1309.1083404404985</v>
+        <v>1379.7894001015452</v>
       </c>
       <c r="DM16" s="12">
         <f t="shared" si="74"/>
-        <v>1296.0172570360935</v>
+        <v>1365.9915061005297</v>
       </c>
       <c r="DN16" s="12">
         <f t="shared" si="74"/>
-        <v>1283.0570844657325</v>
+        <v>1352.3315910395245</v>
       </c>
       <c r="DO16" s="12">
         <f t="shared" si="74"/>
-        <v>1270.2265136210751</v>
+        <v>1338.8082751291292</v>
       </c>
       <c r="DP16" s="12">
         <f t="shared" si="74"/>
-        <v>1257.5242484848643</v>
+        <v>1325.420192377838</v>
       </c>
       <c r="DQ16" s="12">
         <f t="shared" si="74"/>
-        <v>1244.9490060000157</v>
+        <v>1312.1659904540597</v>
       </c>
       <c r="DR16" s="12">
         <f t="shared" si="74"/>
-        <v>1232.4995159400155</v>
+        <v>1299.0443305495191</v>
       </c>
       <c r="DS16" s="12">
         <f t="shared" si="74"/>
-        <v>1220.1745207806152</v>
+        <v>1286.0538872440241</v>
       </c>
       <c r="DT16" s="12">
         <f t="shared" si="74"/>
-        <v>1207.972775572809</v>
+        <v>1273.1933483715839</v>
       </c>
       <c r="DU16" s="12">
         <f t="shared" si="74"/>
-        <v>1195.893047817081</v>
+        <v>1260.4614148878679</v>
       </c>
       <c r="DV16" s="12">
         <f t="shared" si="74"/>
-        <v>1183.9341173389103</v>
+        <v>1247.8568007389893</v>
       </c>
       <c r="DW16" s="12">
         <f t="shared" si="74"/>
-        <v>1172.0947761655211</v>
+        <v>1235.3782327315994</v>
       </c>
       <c r="DX16" s="12">
         <f t="shared" si="74"/>
-        <v>1160.3738284038659</v>
+        <v>1223.0244504042835</v>
       </c>
       <c r="DY16" s="12">
         <f t="shared" si="74"/>
-        <v>1148.7700901198273</v>
+        <v>1210.7942059002405</v>
       </c>
       <c r="DZ16" s="12">
         <f t="shared" si="74"/>
-        <v>1137.2823892186291</v>
+        <v>1198.6862638412381</v>
       </c>
       <c r="EA16" s="12">
         <f t="shared" si="74"/>
-        <v>1125.9095653264428</v>
+        <v>1186.6994012028256</v>
       </c>
       <c r="EB16" s="12">
         <f t="shared" si="74"/>
-        <v>1114.6504696731783</v>
+        <v>1174.8324071907973</v>
       </c>
       <c r="EC16" s="12">
         <f t="shared" si="74"/>
-        <v>1103.5039649764465</v>
+        <v>1163.0840831188893</v>
       </c>
       <c r="ED16" s="12">
         <f t="shared" si="74"/>
-        <v>1092.468925326682</v>
+        <v>1151.4532422877005</v>
       </c>
       <c r="EE16" s="12">
         <f t="shared" si="74"/>
-        <v>1081.544236073415</v>
+        <v>1139.9387098648235</v>
       </c>
       <c r="EF16" s="12">
         <f t="shared" si="74"/>
-        <v>1070.728793712681</v>
+        <v>1128.5393227661752</v>
       </c>
       <c r="EG16" s="12">
         <f t="shared" si="74"/>
-        <v>1060.021505775554</v>
+        <v>1117.2539295385134</v>
       </c>
       <c r="EH16" s="12">
         <f t="shared" si="74"/>
-        <v>1049.4212907177985</v>
+        <v>1106.0813902431282</v>
       </c>
       <c r="EI16" s="12">
         <f t="shared" si="74"/>
-        <v>1038.9270778106204</v>
+        <v>1095.0205763406968</v>
       </c>
       <c r="EJ16" s="12">
         <f t="shared" si="74"/>
-        <v>1028.5378070325141</v>
+        <v>1084.0703705772899</v>
       </c>
       <c r="EK16" s="12">
         <f t="shared" si="74"/>
-        <v>1018.252428962189</v>
+        <v>1073.2296668715169</v>
       </c>
       <c r="EL16" s="12">
         <f t="shared" si="74"/>
-        <v>1008.0699046725671</v>
+        <v>1062.4973702028017</v>
       </c>
       <c r="EM16" s="12">
         <f t="shared" si="74"/>
-        <v>997.98920562584135</v>
+        <v>1051.8723965007737</v>
       </c>
       <c r="EN16" s="12">
         <f t="shared" si="74"/>
-        <v>988.0093135695829</v>
+        <v>1041.353672535766</v>
       </c>
       <c r="EO16" s="12">
         <f t="shared" si="74"/>
-        <v>978.1292204338871</v>
+        <v>1030.9401358104083</v>
       </c>
       <c r="EP16" s="12">
         <f t="shared" si="74"/>
-        <v>968.34792822954819</v>
+        <v>1020.6307344523042</v>
       </c>
       <c r="EQ16" s="12">
         <f t="shared" si="74"/>
-        <v>958.66444894725271</v>
+        <v>1010.4244271077812</v>
       </c>
       <c r="ER16" s="12">
         <f t="shared" si="74"/>
-        <v>949.07780445778019</v>
+        <v>1000.3201828367033</v>
       </c>
       <c r="ES16" s="12">
         <f t="shared" si="74"/>
-        <v>939.58702641320235</v>
+        <v>990.31698100833626</v>
       </c>
       <c r="ET16" s="12">
         <f t="shared" si="74"/>
-        <v>930.19115614907037</v>
+        <v>980.41381119825292</v>
       </c>
       <c r="EU16" s="12">
         <f t="shared" si="74"/>
-        <v>920.8892445875797</v>
+        <v>970.60967308627039</v>
       </c>
       <c r="EV16" s="12">
         <f t="shared" si="74"/>
-        <v>911.68035214170391</v>
-      </c>
-    </row>
-    <row r="17" spans="3:45" x14ac:dyDescent="0.25">
+        <v>960.90357635540772</v>
+      </c>
+    </row>
+    <row r="17" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
         <v>60</v>
       </c>
@@ -3415,6 +3532,9 @@
       <c r="T17" s="9">
         <v>112.38409299999999</v>
       </c>
+      <c r="U17" s="9">
+        <v>112.38409299999999</v>
+      </c>
       <c r="Z17" s="9">
         <v>112.38409299999999</v>
       </c>
@@ -3467,7 +3587,7 @@
         <v>112.38409299999999</v>
       </c>
     </row>
-    <row r="18" spans="3:45" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
         <v>61</v>
       </c>
@@ -3539,6 +3659,10 @@
         <f>T16/T17</f>
         <v>2.1088393710665088</v>
       </c>
+      <c r="U18" s="18">
+        <f>U16/U17</f>
+        <v>1.9397762991244678</v>
+      </c>
       <c r="Z18" s="18">
         <f t="shared" ref="Z18:AE18" si="76">Z16/Z17</f>
         <v>4.707071845123135</v>
@@ -3569,46 +3693,46 @@
       </c>
       <c r="AG18" s="20">
         <f t="shared" ref="AG18" si="78">AG16/AG17</f>
-        <v>9.4085850121155605</v>
+        <v>7.3765549631654697</v>
       </c>
       <c r="AH18" s="18">
         <f t="shared" ref="AH18" si="79">AH16/AH17</f>
-        <v>10.608236644130784</v>
+        <v>11.449676633329263</v>
       </c>
       <c r="AI18" s="18">
         <f t="shared" ref="AI18" si="80">AI16/AI17</f>
-        <v>11.9085255104991</v>
+        <v>12.798565891925676</v>
       </c>
       <c r="AJ18" s="18">
         <f t="shared" ref="AJ18" si="81">AJ16/AJ17</f>
-        <v>13.316736094865218</v>
+        <v>14.258296517588921</v>
       </c>
       <c r="AK18" s="18">
         <f t="shared" ref="AK18" si="82">AK16/AK17</f>
-        <v>14.840639635414604</v>
+        <v>15.836822453167223</v>
       </c>
       <c r="AL18" s="18">
         <f t="shared" ref="AL18" si="83">AL16/AL17</f>
-        <v>16.488524908570138</v>
+        <v>17.542627069145073</v>
       </c>
       <c r="AM18" s="18">
         <f t="shared" ref="AM18" si="84">AM16/AM17</f>
-        <v>18.269230871928205</v>
+        <v>19.384756607611678</v>
       </c>
       <c r="AN18" s="18">
         <f t="shared" ref="AN18" si="85">AN16/AN17</f>
-        <v>20.192181273633729</v>
+        <v>21.372855648212138</v>
       </c>
       <c r="AO18" s="18">
         <f t="shared" ref="AO18" si="86">AO16/AO17</f>
-        <v>22.267421341235806</v>
+        <v>23.51720471306222</v>
       </c>
       <c r="AP18" s="18">
         <f t="shared" ref="AP18" si="87">AP16/AP17</f>
-        <v>24.505656669203688</v>
-      </c>
-    </row>
-    <row r="19" spans="3:45" x14ac:dyDescent="0.25">
+        <v>25.828760134029441</v>
+      </c>
+    </row>
+    <row r="19" spans="2:45" x14ac:dyDescent="0.25">
       <c r="AR19" s="2" t="s">
         <v>110</v>
       </c>
@@ -3616,7 +3740,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="3:45" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
@@ -3676,6 +3800,10 @@
         <f>(T4-P4)/P4</f>
         <v>0.12872676253945983</v>
       </c>
+      <c r="U20" s="19">
+        <f>(U4-Q4)/Q4</f>
+        <v>0.14049677207571945</v>
+      </c>
       <c r="Z20" s="19"/>
       <c r="AA20" s="19">
         <f t="shared" ref="AA20:AD20" si="89">(AA4-Z4)/Z4</f>
@@ -3748,7 +3876,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="21" spans="3:45" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C21" s="2" t="s">
         <v>62</v>
       </c>
@@ -3820,6 +3948,10 @@
         <f>T6/T4</f>
         <v>0.29448933084731715</v>
       </c>
+      <c r="U21" s="10">
+        <f>U6/U4</f>
+        <v>0.27564041063033673</v>
+      </c>
       <c r="Z21" s="10">
         <f t="shared" ref="Z21:AE21" si="93">Z6/Z4</f>
         <v>0.21164916109671258</v>
@@ -3850,7 +3982,7 @@
       </c>
       <c r="AG21" s="22">
         <f t="shared" si="94"/>
-        <v>0.29500000000000004</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="AH21" s="10">
         <f t="shared" si="94"/>
@@ -3893,1856 +4025,2285 @@
       </c>
       <c r="AS21" s="29">
         <f>NPV(AS19,AF16:EV16)</f>
-        <v>24377.091408000437</v>
-      </c>
-    </row>
-    <row r="22" spans="3:45" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
+        <v>25505.979644050683</v>
+      </c>
+    </row>
+    <row r="22" spans="2:45" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="56"/>
+      <c r="C22" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="25">
+        <f t="shared" ref="D22:S22" si="95">D10/D4</f>
+        <v>4.778453518679409E-2</v>
+      </c>
+      <c r="E22" s="25">
+        <f t="shared" si="95"/>
+        <v>5.7048748353096181E-2</v>
+      </c>
+      <c r="F22" s="25">
+        <f t="shared" si="95"/>
+        <v>5.4441969809453108E-2</v>
+      </c>
+      <c r="G22" s="25">
+        <f t="shared" si="95"/>
+        <v>6.2016293279022403E-2</v>
+      </c>
+      <c r="H22" s="25">
+        <f t="shared" si="95"/>
+        <v>4.8090197883110905E-2</v>
+      </c>
+      <c r="I22" s="25">
+        <f t="shared" si="95"/>
+        <v>5.2536640360766627E-2</v>
+      </c>
+      <c r="J22" s="25">
+        <f t="shared" si="95"/>
+        <v>6.0441689267725689E-2</v>
+      </c>
+      <c r="K22" s="25">
+        <f t="shared" si="95"/>
+        <v>6.1602298116820942E-2</v>
+      </c>
+      <c r="L22" s="25">
+        <f t="shared" si="95"/>
+        <v>5.7323165921640808E-2</v>
+      </c>
+      <c r="M22" s="25">
+        <f t="shared" si="95"/>
+        <v>5.0357995226730311E-2</v>
+      </c>
+      <c r="N22" s="25">
+        <f t="shared" si="95"/>
+        <v>6.1630965802329948E-2</v>
+      </c>
+      <c r="O22" s="25">
+        <f t="shared" si="95"/>
+        <v>5.2572074618428492E-2</v>
+      </c>
+      <c r="P22" s="25">
+        <f t="shared" si="95"/>
+        <v>5.4717642932304453E-2</v>
+      </c>
+      <c r="Q22" s="25">
+        <f t="shared" si="95"/>
+        <v>5.0661998030419084E-2</v>
+      </c>
+      <c r="R22" s="25">
+        <f t="shared" si="95"/>
+        <v>6.4627060358116925E-2</v>
+      </c>
+      <c r="S22" s="25">
+        <f t="shared" si="95"/>
+        <v>6.0522573764664057E-2</v>
+      </c>
+      <c r="T22" s="25">
+        <f>T10/T4</f>
+        <v>5.3656515434016991E-2</v>
+      </c>
+      <c r="U22" s="25">
+        <f>U10/U4</f>
+        <v>4.8738367072819727E-2</v>
+      </c>
+      <c r="Z22" s="25">
+        <f t="shared" ref="Z22:AP22" si="96">Z10/Z4</f>
+        <v>3.6420679307052242E-2</v>
+      </c>
+      <c r="AA22" s="25">
+        <f t="shared" si="96"/>
+        <v>3.7921170544009314E-2</v>
+      </c>
+      <c r="AB22" s="25">
+        <f t="shared" si="96"/>
+        <v>5.826401319714998E-2</v>
+      </c>
+      <c r="AC22" s="25">
+        <f t="shared" si="96"/>
+        <v>5.5900237676328055E-2</v>
+      </c>
+      <c r="AD22" s="25">
+        <f t="shared" si="96"/>
+        <v>5.5670816044260031E-2</v>
+      </c>
+      <c r="AE22" s="25">
+        <f t="shared" si="96"/>
+        <v>5.5171616111962522E-2</v>
+      </c>
+      <c r="AF22" s="25">
+        <f t="shared" si="96"/>
+        <v>5.770928645958745E-2</v>
+      </c>
+      <c r="AG22" s="56">
+        <f t="shared" si="96"/>
+        <v>5.0856474066743193E-2</v>
+      </c>
+      <c r="AH22" s="25">
+        <f t="shared" si="96"/>
+        <v>6.306537525479286E-2</v>
+      </c>
+      <c r="AI22" s="25">
+        <f t="shared" si="96"/>
+        <v>6.5253437752389148E-2</v>
+      </c>
+      <c r="AJ22" s="25">
+        <f t="shared" si="96"/>
+        <v>6.7420858150951474E-2</v>
+      </c>
+      <c r="AK22" s="25">
+        <f t="shared" si="96"/>
+        <v>6.9567831187263271E-2</v>
+      </c>
+      <c r="AL22" s="25">
+        <f t="shared" si="96"/>
+        <v>7.1694549760968396E-2</v>
+      </c>
+      <c r="AM22" s="25">
+        <f t="shared" si="96"/>
+        <v>7.380120495190258E-2</v>
+      </c>
+      <c r="AN22" s="25">
+        <f t="shared" si="96"/>
+        <v>7.5887986037262031E-2</v>
+      </c>
+      <c r="AO22" s="25">
+        <f t="shared" si="96"/>
+        <v>7.7955080508608651E-2</v>
+      </c>
+      <c r="AP22" s="25">
+        <f t="shared" si="96"/>
+        <v>8.0002674088716114E-2</v>
+      </c>
+      <c r="AR22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS22" s="9">
+        <v>112.38409299999999</v>
+      </c>
+    </row>
+    <row r="23" spans="2:45" x14ac:dyDescent="0.25">
+      <c r="C23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="10">
-        <f t="shared" ref="D22:P22" si="95">D12/D4</f>
+      <c r="D23" s="10">
+        <f t="shared" ref="D23:P23" si="97">D12/D4</f>
         <v>2.6498696785403997E-2</v>
       </c>
-      <c r="E22" s="10">
-        <f t="shared" si="95"/>
+      <c r="E23" s="10">
+        <f t="shared" si="97"/>
         <v>3.7022397891963106E-2</v>
       </c>
-      <c r="F22" s="10">
-        <f t="shared" si="95"/>
+      <c r="F23" s="10">
+        <f t="shared" si="97"/>
         <v>3.5139816877010642E-2</v>
       </c>
-      <c r="G22" s="10">
-        <f t="shared" si="95"/>
+      <c r="G23" s="10">
+        <f t="shared" si="97"/>
         <v>4.5723014256619142E-2</v>
       </c>
-      <c r="H22" s="10">
-        <f t="shared" si="95"/>
+      <c r="H23" s="10">
+        <f t="shared" si="97"/>
         <v>2.8762080073630927E-2</v>
       </c>
-      <c r="I22" s="10">
-        <f t="shared" si="95"/>
+      <c r="I23" s="10">
+        <f t="shared" si="97"/>
         <v>3.2807215332581734E-2</v>
       </c>
-      <c r="J22" s="10">
-        <f t="shared" si="95"/>
+      <c r="J23" s="10">
+        <f t="shared" si="97"/>
         <v>3.8486374790133025E-2</v>
       </c>
-      <c r="K22" s="10">
-        <f t="shared" si="95"/>
+      <c r="K23" s="10">
+        <f t="shared" si="97"/>
         <v>4.298329609532929E-2</v>
       </c>
-      <c r="L22" s="10">
-        <f t="shared" si="95"/>
+      <c r="L23" s="10">
+        <f t="shared" si="97"/>
         <v>3.3657638706284514E-2</v>
       </c>
-      <c r="M22" s="10">
-        <f t="shared" si="95"/>
+      <c r="M23" s="10">
+        <f t="shared" si="97"/>
         <v>2.899761336515513E-2</v>
       </c>
-      <c r="N22" s="10">
-        <f t="shared" si="95"/>
+      <c r="N23" s="10">
+        <f t="shared" si="97"/>
         <v>3.8456720531128648E-2</v>
       </c>
-      <c r="O22" s="10">
-        <f t="shared" si="95"/>
+      <c r="O23" s="10">
+        <f t="shared" si="97"/>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="P22" s="10">
-        <f t="shared" si="95"/>
+      <c r="P23" s="10">
+        <f t="shared" si="97"/>
         <v>3.2737051327019762E-2</v>
       </c>
-      <c r="Q22" s="10">
-        <f t="shared" ref="Q22" si="96">Q12/Q4</f>
+      <c r="Q23" s="10">
+        <f t="shared" ref="Q23" si="98">Q12/Q4</f>
         <v>2.9434292592187328E-2</v>
       </c>
-      <c r="R22" s="10">
+      <c r="R23" s="10">
         <f>R12/R4</f>
         <v>4.1266453219494841E-2</v>
       </c>
-      <c r="S22" s="10">
+      <c r="S23" s="10">
         <f>S12/S4</f>
         <v>4.2747955918947741E-2</v>
       </c>
-      <c r="T22" s="10">
+      <c r="T23" s="10">
         <f>T12/T4</f>
         <v>3.3561218147917959E-2</v>
       </c>
-      <c r="Z22" s="10">
-        <f t="shared" ref="Z22:AE22" si="97">Z12/Z4</f>
+      <c r="U23" s="10">
+        <f>U12/U4</f>
+        <v>3.070133358917778E-2</v>
+      </c>
+      <c r="Z23" s="10">
+        <f t="shared" ref="Z23:AE23" si="99">Z12/Z4</f>
         <v>2.0351930159596236E-2</v>
       </c>
-      <c r="AA22" s="10">
-        <f t="shared" si="97"/>
+      <c r="AA23" s="10">
+        <f t="shared" si="99"/>
         <v>2.1643925777789029E-2</v>
       </c>
-      <c r="AB22" s="10">
-        <f t="shared" si="97"/>
+      <c r="AB23" s="10">
+        <f t="shared" si="99"/>
         <v>3.6713348074830648E-2</v>
       </c>
-      <c r="AC22" s="10">
-        <f t="shared" si="97"/>
+      <c r="AC23" s="10">
+        <f t="shared" si="99"/>
         <v>3.6916998487514278E-2</v>
       </c>
-      <c r="AD22" s="10">
-        <f t="shared" si="97"/>
+      <c r="AD23" s="10">
+        <f t="shared" si="99"/>
         <v>3.5846011987090823E-2</v>
       </c>
-      <c r="AE22" s="10">
-        <f t="shared" si="97"/>
+      <c r="AE23" s="10">
+        <f t="shared" si="99"/>
         <v>3.3889483272127922E-2</v>
       </c>
-      <c r="AF22" s="10">
-        <f t="shared" ref="AF22:AP22" si="98">AF12/AF4</f>
+      <c r="AF23" s="10">
+        <f t="shared" ref="AF23:AP23" si="100">AF12/AF4</f>
         <v>3.6867592369639081E-2</v>
       </c>
-      <c r="AG22" s="22">
-        <f t="shared" si="98"/>
-        <v>3.926565618408813E-2</v>
-      </c>
-      <c r="AH22" s="10">
-        <f t="shared" si="98"/>
-        <v>4.1215124700819561E-2</v>
-      </c>
-      <c r="AI22" s="10">
-        <f t="shared" si="98"/>
-        <v>4.3139648425424178E-2</v>
-      </c>
-      <c r="AJ22" s="10">
-        <f t="shared" si="98"/>
-        <v>4.5039369946794042E-2</v>
-      </c>
-      <c r="AK22" s="10">
-        <f t="shared" si="98"/>
-        <v>4.6914429196294148E-2</v>
-      </c>
-      <c r="AL22" s="10">
-        <f t="shared" si="98"/>
-        <v>4.8764963454262067E-2</v>
-      </c>
-      <c r="AM22" s="10">
-        <f t="shared" si="98"/>
-        <v>5.0591107356183808E-2</v>
-      </c>
-      <c r="AN22" s="10">
-        <f t="shared" si="98"/>
-        <v>5.2392992898545633E-2</v>
-      </c>
-      <c r="AO22" s="10">
-        <f t="shared" si="98"/>
-        <v>5.4170749444358783E-2</v>
-      </c>
-      <c r="AP22" s="10">
-        <f t="shared" si="98"/>
-        <v>5.5924503728359491E-2</v>
-      </c>
-      <c r="AR22" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS22" s="9">
-        <v>112.38409299999999</v>
-      </c>
-    </row>
-    <row r="23" spans="3:45" x14ac:dyDescent="0.25">
-      <c r="C23" s="2" t="s">
+      <c r="AG23" s="22">
+        <f t="shared" si="100"/>
+        <v>3.2079288568032188E-2</v>
+      </c>
+      <c r="AH23" s="10">
+        <f t="shared" si="100"/>
+        <v>4.4022474866949164E-2</v>
+      </c>
+      <c r="AI23" s="10">
+        <f t="shared" si="100"/>
+        <v>4.5941062359057101E-2</v>
+      </c>
+      <c r="AJ23" s="10">
+        <f t="shared" si="100"/>
+        <v>4.7835194426581705E-2</v>
+      </c>
+      <c r="AK23" s="10">
+        <f t="shared" si="100"/>
+        <v>4.9705011844152429E-2</v>
+      </c>
+      <c r="AL23" s="10">
+        <f t="shared" si="100"/>
+        <v>5.1550652785643705E-2</v>
+      </c>
+      <c r="AM23" s="10">
+        <f t="shared" si="100"/>
+        <v>5.3372252830700663E-2</v>
+      </c>
+      <c r="AN23" s="10">
+        <f t="shared" si="100"/>
+        <v>5.5169944970948771E-2</v>
+      </c>
+      <c r="AO23" s="10">
+        <f t="shared" si="100"/>
+        <v>5.6943859615885294E-2</v>
+      </c>
+      <c r="AP23" s="10">
+        <f t="shared" si="100"/>
+        <v>5.8694124598454224E-2</v>
+      </c>
+      <c r="AR23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS23" s="9">
+        <f>AS21/AS22</f>
+        <v>226.95364586917728</v>
+      </c>
+    </row>
+    <row r="24" spans="2:45" x14ac:dyDescent="0.25">
+      <c r="C24" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="25"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="25">
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25">
         <f>Z16/3075</f>
         <v>0.17203252032520325</v>
       </c>
-      <c r="AA23" s="25">
+      <c r="AA24" s="25">
         <f>AA16/3384</f>
         <v>0.17464539007092197</v>
       </c>
-      <c r="AB23" s="25">
+      <c r="AB24" s="25">
         <f>AB16/3530</f>
         <v>0.21529745042492918</v>
       </c>
-      <c r="AC23" s="25">
-        <f>AC16/H40</f>
+      <c r="AC24" s="25">
+        <f>AC16/H41</f>
         <v>0.201423487544484</v>
       </c>
-      <c r="AD23" s="25">
-        <f>AD16/K40</f>
+      <c r="AD24" s="25">
+        <f>AD16/K41</f>
         <v>0.19056693663649357</v>
       </c>
-      <c r="AE23" s="25">
-        <f>AE16/O40</f>
+      <c r="AE24" s="25">
+        <f>AE16/O41</f>
         <v>0.17518083182640146</v>
       </c>
-      <c r="AF23" s="10">
-        <f>AF16/S40</f>
+      <c r="AF24" s="10">
+        <f>AF16/S41</f>
         <v>0.19334948249284298</v>
       </c>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="10"/>
-      <c r="AI23" s="10"/>
-      <c r="AJ23" s="10"/>
-      <c r="AK23" s="10"/>
-      <c r="AL23" s="10"/>
-      <c r="AM23" s="10"/>
-      <c r="AN23" s="10"/>
-      <c r="AO23" s="10"/>
-      <c r="AP23" s="10"/>
-      <c r="AR23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS23" s="9">
-        <f>AS21/AS22</f>
-        <v>216.90873465518325</v>
-      </c>
-    </row>
-    <row r="24" spans="3:45" x14ac:dyDescent="0.25">
+      <c r="AG24" s="22"/>
+      <c r="AH24" s="10"/>
+      <c r="AI24" s="10"/>
+      <c r="AJ24" s="10"/>
+      <c r="AK24" s="10"/>
+      <c r="AL24" s="10"/>
+      <c r="AM24" s="10"/>
+      <c r="AN24" s="10"/>
+      <c r="AO24" s="10"/>
+      <c r="AP24" s="10"/>
       <c r="AR24" s="1" t="s">
         <v>114</v>
       </c>
       <c r="AS24" s="30">
         <f>(AS23-B4)/B4</f>
-        <v>0.34725922146076554</v>
-      </c>
-    </row>
-    <row r="25" spans="3:45" x14ac:dyDescent="0.25">
-      <c r="C25" s="3" t="s">
+        <v>0.46421707012372437</v>
+      </c>
+    </row>
+    <row r="26" spans="2:45" x14ac:dyDescent="0.25">
+      <c r="C26" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="3:45" x14ac:dyDescent="0.25">
-      <c r="C26" s="2" t="s">
+    <row r="27" spans="2:45" x14ac:dyDescent="0.25">
+      <c r="C27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D27" s="14">
         <v>466</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14">
-        <v>553</v>
-      </c>
-      <c r="I26" s="14">
-        <v>549</v>
-      </c>
-      <c r="J26" s="14">
-        <v>511</v>
-      </c>
-      <c r="K26" s="14">
-        <v>514</v>
-      </c>
-      <c r="L26" s="14">
-        <v>518</v>
-      </c>
-      <c r="M26" s="14">
-        <v>503</v>
-      </c>
-      <c r="N26" s="14">
-        <v>501</v>
-      </c>
-      <c r="O26" s="14">
-        <v>498</v>
-      </c>
-      <c r="P26" s="14">
-        <v>474</v>
-      </c>
-      <c r="Q26" s="14">
-        <v>476</v>
-      </c>
-      <c r="R26" s="14">
-        <v>531</v>
-      </c>
-      <c r="S26" s="14">
-        <v>563</v>
-      </c>
-      <c r="T26" s="14">
-        <v>561</v>
-      </c>
-      <c r="U26" s="12"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="12"/>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="12"/>
-      <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-      <c r="AD26" s="14"/>
-    </row>
-    <row r="27" spans="3:45" x14ac:dyDescent="0.25">
-      <c r="C27" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1201</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14">
-        <v>1296</v>
+        <v>553</v>
       </c>
       <c r="I27" s="14">
-        <v>1269</v>
+        <v>549</v>
       </c>
       <c r="J27" s="14">
-        <v>1313</v>
+        <v>511</v>
       </c>
       <c r="K27" s="14">
-        <v>1314</v>
+        <v>514</v>
       </c>
       <c r="L27" s="14">
-        <v>1368</v>
+        <v>518</v>
       </c>
       <c r="M27" s="14">
-        <v>1407</v>
+        <v>503</v>
       </c>
       <c r="N27" s="14">
-        <v>1419</v>
+        <v>501</v>
       </c>
       <c r="O27" s="14">
-        <v>1448</v>
+        <v>498</v>
       </c>
       <c r="P27" s="14">
-        <v>1436</v>
+        <v>474</v>
       </c>
       <c r="Q27" s="14">
-        <v>1518</v>
+        <v>476</v>
       </c>
       <c r="R27" s="14">
-        <v>1447</v>
+        <v>531</v>
       </c>
       <c r="S27" s="14">
-        <v>1396</v>
+        <v>563</v>
       </c>
       <c r="T27" s="14">
-        <v>1391</v>
-      </c>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="14"/>
-      <c r="AD27" s="14"/>
-    </row>
-    <row r="28" spans="3:45" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+      <c r="U27" s="14">
+        <v>583</v>
+      </c>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AD27" s="14">
+        <v>514</v>
+      </c>
+      <c r="AE27" s="14">
+        <v>498</v>
+      </c>
+      <c r="AF27" s="14">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="28" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D28" s="14">
-        <v>278</v>
+        <v>1201</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
       <c r="H28" s="14">
-        <v>211</v>
+        <v>1296</v>
       </c>
       <c r="I28" s="14">
-        <v>201</v>
+        <v>1269</v>
       </c>
       <c r="J28" s="14">
-        <v>186</v>
+        <v>1313</v>
       </c>
       <c r="K28" s="14">
-        <v>209</v>
+        <v>1314</v>
       </c>
       <c r="L28" s="14">
-        <v>223</v>
+        <v>1368</v>
       </c>
       <c r="M28" s="14">
-        <v>239</v>
+        <v>1407</v>
       </c>
       <c r="N28" s="14">
-        <v>198</v>
+        <v>1419</v>
       </c>
       <c r="O28" s="14">
-        <v>170</v>
+        <v>1448</v>
       </c>
       <c r="P28" s="14">
-        <v>182</v>
+        <v>1436</v>
       </c>
       <c r="Q28" s="14">
-        <v>199</v>
+        <v>1518</v>
       </c>
       <c r="R28" s="14">
-        <v>212</v>
+        <v>1447</v>
       </c>
       <c r="S28" s="14">
-        <v>126</v>
+        <v>1396</v>
       </c>
       <c r="T28" s="14">
-        <v>130</v>
-      </c>
-      <c r="U28" s="14"/>
+        <v>1391</v>
+      </c>
+      <c r="U28" s="14">
+        <v>1446</v>
+      </c>
       <c r="V28" s="14"/>
       <c r="W28" s="14"/>
       <c r="X28" s="14"/>
       <c r="Y28" s="14"/>
-      <c r="AD28" s="14"/>
-    </row>
-    <row r="29" spans="3:45" x14ac:dyDescent="0.25">
+      <c r="AD28" s="14">
+        <v>1314</v>
+      </c>
+      <c r="AE28" s="14">
+        <v>1448</v>
+      </c>
+      <c r="AF28" s="14">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="29" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D29" s="14">
-        <v>3858</v>
+        <v>278</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
       <c r="H29" s="14">
-        <v>4367</v>
+        <v>211</v>
       </c>
       <c r="I29" s="14">
-        <v>4417</v>
+        <v>201</v>
       </c>
       <c r="J29" s="14">
-        <v>4307</v>
+        <v>186</v>
       </c>
       <c r="K29" s="14">
-        <v>4336</v>
+        <v>209</v>
       </c>
       <c r="L29" s="14">
-        <v>4429</v>
+        <v>223</v>
       </c>
       <c r="M29" s="14">
-        <v>4360</v>
+        <v>239</v>
       </c>
       <c r="N29" s="14">
-        <v>4469</v>
+        <v>198</v>
       </c>
       <c r="O29" s="14">
-        <v>4465</v>
+        <v>170</v>
       </c>
       <c r="P29" s="14">
-        <v>4403</v>
+        <v>182</v>
       </c>
       <c r="Q29" s="14">
-        <v>4499</v>
+        <v>199</v>
       </c>
       <c r="R29" s="14">
-        <v>4475</v>
+        <v>212</v>
       </c>
       <c r="S29" s="14">
-        <v>4526</v>
+        <v>126</v>
       </c>
       <c r="T29" s="14">
-        <v>4334</v>
-      </c>
-      <c r="U29" s="14"/>
+        <v>130</v>
+      </c>
+      <c r="U29" s="14">
+        <v>138</v>
+      </c>
       <c r="V29" s="14"/>
       <c r="W29" s="14"/>
       <c r="X29" s="14"/>
       <c r="Y29" s="14"/>
-      <c r="AD29" s="14"/>
-    </row>
-    <row r="30" spans="3:45" x14ac:dyDescent="0.25">
+      <c r="AD29" s="14">
+        <v>209</v>
+      </c>
+      <c r="AE29" s="14">
+        <v>170</v>
+      </c>
+      <c r="AF29" s="14">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D30" s="14">
-        <v>332</v>
+        <v>3858</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
       <c r="H30" s="14">
-        <v>501</v>
+        <v>4367</v>
       </c>
       <c r="I30" s="14">
-        <v>538</v>
+        <v>4417</v>
       </c>
       <c r="J30" s="14">
-        <v>541</v>
+        <v>4307</v>
       </c>
       <c r="K30" s="14">
-        <v>572</v>
+        <v>4336</v>
       </c>
       <c r="L30" s="14">
-        <v>590</v>
+        <v>4429</v>
       </c>
       <c r="M30" s="14">
-        <v>617</v>
+        <v>4360</v>
       </c>
       <c r="N30" s="14">
-        <v>661</v>
+        <v>4469</v>
       </c>
       <c r="O30" s="14">
-        <v>712</v>
+        <v>4465</v>
       </c>
       <c r="P30" s="14">
-        <v>747</v>
+        <v>4403</v>
       </c>
       <c r="Q30" s="14">
-        <v>791</v>
+        <v>4499</v>
       </c>
       <c r="R30" s="14">
-        <v>729</v>
+        <v>4475</v>
       </c>
       <c r="S30" s="14">
-        <v>753</v>
+        <v>4526</v>
       </c>
       <c r="T30" s="14">
-        <v>683</v>
-      </c>
-      <c r="U30" s="14"/>
+        <v>4334</v>
+      </c>
+      <c r="U30" s="14">
+        <v>4350</v>
+      </c>
       <c r="V30" s="14"/>
       <c r="W30" s="14"/>
       <c r="X30" s="14"/>
       <c r="Y30" s="14"/>
-      <c r="AD30" s="14"/>
-    </row>
-    <row r="31" spans="3:45" x14ac:dyDescent="0.25">
+      <c r="AD30" s="14">
+        <v>4336</v>
+      </c>
+      <c r="AE30" s="14">
+        <v>4465</v>
+      </c>
+      <c r="AF30" s="14">
+        <v>4526</v>
+      </c>
+    </row>
+    <row r="31" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C31" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D31" s="14">
-        <v>72</v>
+        <v>332</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="14">
-        <v>168</v>
+        <v>501</v>
       </c>
       <c r="I31" s="14">
-        <v>208</v>
+        <v>538</v>
       </c>
       <c r="J31" s="14">
-        <v>206</v>
+        <v>541</v>
       </c>
       <c r="K31" s="14">
-        <v>182</v>
+        <v>572</v>
       </c>
       <c r="L31" s="14">
-        <v>195</v>
+        <v>590</v>
       </c>
       <c r="M31" s="14">
-        <v>180</v>
+        <v>617</v>
       </c>
       <c r="N31" s="14">
-        <v>183</v>
+        <v>661</v>
       </c>
       <c r="O31" s="14">
-        <v>168</v>
+        <v>712</v>
       </c>
       <c r="P31" s="14">
-        <v>195</v>
+        <v>747</v>
       </c>
       <c r="Q31" s="14">
-        <v>191</v>
+        <v>791</v>
       </c>
       <c r="R31" s="14">
-        <v>186</v>
+        <v>729</v>
       </c>
       <c r="S31" s="14">
-        <v>174</v>
+        <v>753</v>
       </c>
       <c r="T31" s="14">
-        <v>177</v>
-      </c>
-      <c r="U31" s="14"/>
+        <v>683</v>
+      </c>
+      <c r="U31" s="14">
+        <f>711+71</f>
+        <v>782</v>
+      </c>
       <c r="V31" s="14"/>
       <c r="W31" s="14"/>
       <c r="X31" s="14"/>
       <c r="Y31" s="14"/>
-      <c r="AD31" s="14"/>
-    </row>
-    <row r="32" spans="3:45" x14ac:dyDescent="0.25">
+      <c r="AD31" s="14">
+        <v>572</v>
+      </c>
+      <c r="AE31" s="14">
+        <v>712</v>
+      </c>
+      <c r="AF31" s="14">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="32" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32" s="14">
-        <v>1491</v>
+        <v>72</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
       <c r="H32" s="14">
-        <v>1266</v>
+        <v>168</v>
       </c>
       <c r="I32" s="14">
-        <v>1232</v>
+        <v>208</v>
       </c>
       <c r="J32" s="14">
-        <v>834</v>
+        <v>206</v>
       </c>
       <c r="K32" s="14">
-        <v>785</v>
+        <v>182</v>
       </c>
       <c r="L32" s="14">
-        <v>894</v>
+        <v>195</v>
       </c>
       <c r="M32" s="14">
-        <v>998</v>
+        <v>180</v>
       </c>
       <c r="N32" s="14">
-        <v>946</v>
+        <v>183</v>
       </c>
       <c r="O32" s="14">
-        <v>974</v>
+        <v>168</v>
       </c>
       <c r="P32" s="14">
-        <v>1104</v>
+        <v>195</v>
       </c>
       <c r="Q32" s="14">
-        <v>1266</v>
+        <v>191</v>
       </c>
       <c r="R32" s="14">
-        <v>1037</v>
+        <v>186</v>
       </c>
       <c r="S32" s="14">
-        <v>974</v>
+        <v>174</v>
       </c>
       <c r="T32" s="14">
-        <v>1428</v>
-      </c>
-      <c r="U32" s="14"/>
+        <v>177</v>
+      </c>
+      <c r="U32" s="14">
+        <v>180</v>
+      </c>
       <c r="V32" s="14"/>
       <c r="W32" s="14"/>
       <c r="X32" s="14"/>
       <c r="Y32" s="14"/>
-      <c r="AD32" s="14"/>
-    </row>
-    <row r="33" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD32" s="14">
+        <v>182</v>
+      </c>
+      <c r="AE32" s="14">
+        <v>168</v>
+      </c>
+      <c r="AF32" s="14">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C33" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D33" s="14">
-        <v>3120</v>
+        <v>1491</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14">
-        <v>4676</v>
+        <v>1266</v>
       </c>
       <c r="I33" s="14">
-        <v>6151</v>
+        <v>1232</v>
       </c>
       <c r="J33" s="14">
-        <v>3996</v>
+        <v>834</v>
       </c>
       <c r="K33" s="14">
-        <v>6946</v>
+        <v>785</v>
       </c>
       <c r="L33" s="14">
-        <v>4522</v>
+        <v>894</v>
       </c>
       <c r="M33" s="14">
-        <v>5968</v>
+        <v>998</v>
       </c>
       <c r="N33" s="14">
-        <v>4308</v>
+        <v>946</v>
       </c>
       <c r="O33" s="14">
-        <v>8074</v>
+        <v>974</v>
       </c>
       <c r="P33" s="14">
-        <v>4994</v>
+        <v>1104</v>
       </c>
       <c r="Q33" s="14">
-        <v>7566</v>
+        <v>1266</v>
       </c>
       <c r="R33" s="14">
-        <v>4549</v>
+        <v>1037</v>
       </c>
       <c r="S33" s="14">
-        <v>8721</v>
+        <v>974</v>
       </c>
       <c r="T33" s="14">
-        <v>6134</v>
-      </c>
-      <c r="U33" s="14"/>
+        <v>1428</v>
+      </c>
+      <c r="U33" s="14">
+        <v>2466</v>
+      </c>
       <c r="V33" s="14"/>
       <c r="W33" s="14"/>
       <c r="X33" s="14"/>
       <c r="Y33" s="14"/>
-      <c r="AD33" s="14"/>
-    </row>
-    <row r="34" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD33" s="14">
+        <v>785</v>
+      </c>
+      <c r="AE33" s="14">
+        <v>974</v>
+      </c>
+      <c r="AF33" s="14">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="34" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C34" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D34" s="14">
-        <v>2040</v>
+        <v>3120</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
       <c r="H34" s="14">
-        <v>2746</v>
+        <v>4676</v>
       </c>
       <c r="I34" s="14">
-        <v>2571</v>
+        <v>6151</v>
       </c>
       <c r="J34" s="14">
-        <v>2523</v>
+        <v>3996</v>
       </c>
       <c r="K34" s="14">
-        <v>2191</v>
+        <v>6946</v>
       </c>
       <c r="L34" s="14">
-        <v>2546</v>
+        <v>4522</v>
       </c>
       <c r="M34" s="14">
-        <v>2579</v>
+        <v>5968</v>
       </c>
       <c r="N34" s="14">
-        <v>2444</v>
+        <v>4308</v>
       </c>
       <c r="O34" s="14">
-        <v>2596</v>
+        <v>8074</v>
       </c>
       <c r="P34" s="14">
-        <v>2667</v>
+        <v>4994</v>
       </c>
       <c r="Q34" s="14">
-        <v>3126</v>
+        <v>7566</v>
       </c>
       <c r="R34" s="14">
-        <v>2934</v>
+        <v>4549</v>
       </c>
       <c r="S34" s="14">
-        <v>2515</v>
+        <v>8721</v>
       </c>
       <c r="T34" s="14">
-        <v>2740</v>
-      </c>
-      <c r="U34" s="14"/>
+        <v>6134</v>
+      </c>
+      <c r="U34" s="14">
+        <v>8485</v>
+      </c>
       <c r="V34" s="14"/>
       <c r="W34" s="14"/>
       <c r="X34" s="14"/>
       <c r="Y34" s="14"/>
-      <c r="AD34" s="14"/>
-    </row>
-    <row r="35" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD34" s="14">
+        <v>6946</v>
+      </c>
+      <c r="AE34" s="14">
+        <v>8074</v>
+      </c>
+      <c r="AF34" s="14">
+        <v>8721</v>
+      </c>
+    </row>
+    <row r="35" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C35" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="14">
-        <v>629</v>
+        <v>2040</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
       <c r="H35" s="14">
-        <v>1053</v>
+        <v>2746</v>
       </c>
       <c r="I35" s="14">
-        <v>1161</v>
+        <v>2571</v>
       </c>
       <c r="J35" s="14">
-        <v>1019</v>
+        <v>2523</v>
       </c>
       <c r="K35" s="14">
-        <v>1587</v>
+        <v>2191</v>
       </c>
       <c r="L35" s="14">
-        <v>830</v>
+        <v>2546</v>
       </c>
       <c r="M35" s="14">
-        <v>1190</v>
+        <v>2579</v>
       </c>
       <c r="N35" s="14">
-        <v>1034</v>
+        <v>2444</v>
       </c>
       <c r="O35" s="14">
-        <v>2004</v>
+        <v>2596</v>
       </c>
       <c r="P35" s="14">
-        <v>879</v>
+        <v>2667</v>
       </c>
       <c r="Q35" s="14">
-        <v>1066</v>
+        <v>3126</v>
       </c>
       <c r="R35" s="14">
-        <v>907</v>
+        <v>2934</v>
       </c>
       <c r="S35" s="14">
-        <v>1594</v>
+        <v>2515</v>
       </c>
       <c r="T35" s="14">
-        <v>790</v>
-      </c>
-      <c r="U35" s="14"/>
+        <v>2740</v>
+      </c>
+      <c r="U35" s="14">
+        <v>2951</v>
+      </c>
       <c r="V35" s="14"/>
       <c r="W35" s="14"/>
       <c r="X35" s="14"/>
       <c r="Y35" s="14"/>
-      <c r="AD35" s="14"/>
-    </row>
-    <row r="36" spans="3:30" x14ac:dyDescent="0.25">
-      <c r="C36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="12">
-        <f t="shared" ref="D36:O36" si="99">SUM(D26:D35)</f>
-        <v>13487</v>
-      </c>
-      <c r="E36" s="12">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="12">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="12">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="12">
-        <f t="shared" si="99"/>
-        <v>16837</v>
-      </c>
-      <c r="I36" s="12">
-        <f t="shared" si="99"/>
-        <v>18297</v>
-      </c>
-      <c r="J36" s="12">
-        <f t="shared" si="99"/>
-        <v>15436</v>
-      </c>
-      <c r="K36" s="12">
-        <f t="shared" si="99"/>
-        <v>18636</v>
-      </c>
-      <c r="L36" s="12">
-        <f t="shared" si="99"/>
-        <v>16115</v>
-      </c>
-      <c r="M36" s="12">
-        <f t="shared" si="99"/>
-        <v>18041</v>
-      </c>
-      <c r="N36" s="12">
-        <f t="shared" si="99"/>
-        <v>16163</v>
-      </c>
-      <c r="O36" s="12">
-        <f t="shared" si="99"/>
-        <v>21109</v>
-      </c>
-      <c r="P36" s="12">
-        <f>SUM(P26:P35)</f>
-        <v>17081</v>
-      </c>
-      <c r="Q36" s="12">
-        <f>SUM(Q26:Q35)</f>
-        <v>20698</v>
-      </c>
-      <c r="R36" s="12">
-        <f>SUM(R26:R35)</f>
-        <v>17007</v>
-      </c>
-      <c r="S36" s="12">
-        <f>SUM(S26:S35)</f>
-        <v>21342</v>
-      </c>
-      <c r="T36" s="12">
-        <f>SUM(T26:T35)</f>
-        <v>18368</v>
-      </c>
-      <c r="U36" s="14"/>
+      <c r="AD35" s="14">
+        <v>2191</v>
+      </c>
+      <c r="AE35" s="14">
+        <v>2596</v>
+      </c>
+      <c r="AF35" s="14">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="36" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="14">
+        <v>629</v>
+      </c>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14">
+        <v>1053</v>
+      </c>
+      <c r="I36" s="14">
+        <v>1161</v>
+      </c>
+      <c r="J36" s="14">
+        <v>1019</v>
+      </c>
+      <c r="K36" s="14">
+        <v>1587</v>
+      </c>
+      <c r="L36" s="14">
+        <v>830</v>
+      </c>
+      <c r="M36" s="14">
+        <v>1190</v>
+      </c>
+      <c r="N36" s="14">
+        <v>1034</v>
+      </c>
+      <c r="O36" s="14">
+        <v>2004</v>
+      </c>
+      <c r="P36" s="14">
+        <v>879</v>
+      </c>
+      <c r="Q36" s="14">
+        <v>1066</v>
+      </c>
+      <c r="R36" s="14">
+        <v>907</v>
+      </c>
+      <c r="S36" s="14">
+        <v>1594</v>
+      </c>
+      <c r="T36" s="14">
+        <v>790</v>
+      </c>
+      <c r="U36" s="14">
+        <v>629</v>
+      </c>
       <c r="V36" s="14"/>
       <c r="W36" s="14"/>
       <c r="X36" s="14"/>
       <c r="Y36" s="14"/>
-      <c r="AD36" s="14"/>
-    </row>
-    <row r="37" spans="3:30" x14ac:dyDescent="0.25">
-      <c r="C37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="14">
-        <v>680</v>
-      </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14">
-        <v>680</v>
-      </c>
-      <c r="I37" s="14">
-        <v>680</v>
-      </c>
-      <c r="J37" s="14">
-        <v>680</v>
-      </c>
-      <c r="K37" s="14">
-        <v>680</v>
-      </c>
-      <c r="L37" s="14">
-        <v>680</v>
-      </c>
-      <c r="M37" s="14">
-        <v>681</v>
-      </c>
-      <c r="N37" s="14">
-        <v>681</v>
-      </c>
-      <c r="O37" s="14">
-        <v>681</v>
-      </c>
-      <c r="P37" s="14">
-        <v>681</v>
-      </c>
-      <c r="Q37" s="14">
-        <v>681</v>
-      </c>
-      <c r="R37" s="14">
-        <v>681</v>
-      </c>
-      <c r="S37" s="14">
-        <v>680</v>
-      </c>
-      <c r="T37" s="14">
-        <v>680</v>
-      </c>
-      <c r="U37" s="14"/>
+      <c r="AD36" s="14">
+        <v>1587</v>
+      </c>
+      <c r="AE36" s="14">
+        <v>2004</v>
+      </c>
+      <c r="AF36" s="14">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="37" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="12">
+        <f t="shared" ref="D37:O37" si="101">SUM(D27:D36)</f>
+        <v>13487</v>
+      </c>
+      <c r="E37" s="12">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="12">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="12">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="12">
+        <f t="shared" si="101"/>
+        <v>16837</v>
+      </c>
+      <c r="I37" s="12">
+        <f t="shared" si="101"/>
+        <v>18297</v>
+      </c>
+      <c r="J37" s="12">
+        <f t="shared" si="101"/>
+        <v>15436</v>
+      </c>
+      <c r="K37" s="12">
+        <f t="shared" si="101"/>
+        <v>18636</v>
+      </c>
+      <c r="L37" s="12">
+        <f t="shared" si="101"/>
+        <v>16115</v>
+      </c>
+      <c r="M37" s="12">
+        <f t="shared" si="101"/>
+        <v>18041</v>
+      </c>
+      <c r="N37" s="12">
+        <f t="shared" si="101"/>
+        <v>16163</v>
+      </c>
+      <c r="O37" s="12">
+        <f t="shared" si="101"/>
+        <v>21109</v>
+      </c>
+      <c r="P37" s="12">
+        <f>SUM(P27:P36)</f>
+        <v>17081</v>
+      </c>
+      <c r="Q37" s="12">
+        <f>SUM(Q27:Q36)</f>
+        <v>20698</v>
+      </c>
+      <c r="R37" s="12">
+        <f>SUM(R27:R36)</f>
+        <v>17007</v>
+      </c>
+      <c r="S37" s="12">
+        <f>SUM(S27:S36)</f>
+        <v>21342</v>
+      </c>
+      <c r="T37" s="12">
+        <f>SUM(T27:T36)</f>
+        <v>18368</v>
+      </c>
+      <c r="U37" s="12">
+        <f>SUM(U27:U36)</f>
+        <v>22010</v>
+      </c>
       <c r="V37" s="14"/>
       <c r="W37" s="14"/>
       <c r="X37" s="14"/>
       <c r="Y37" s="14"/>
-      <c r="AD37" s="14"/>
-    </row>
-    <row r="38" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD37" s="12">
+        <f t="shared" ref="AD37" si="102">SUM(AD27:AD36)</f>
+        <v>18636</v>
+      </c>
+      <c r="AE37" s="12">
+        <f t="shared" ref="AE37" si="103">SUM(AE27:AE36)</f>
+        <v>21109</v>
+      </c>
+      <c r="AF37" s="12">
+        <f>SUM(AF27:AF36)</f>
+        <v>21342</v>
+      </c>
+    </row>
+    <row r="38" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C38" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D38" s="14">
-        <v>1324</v>
+        <v>680</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
       <c r="H38" s="14">
-        <v>1828</v>
+        <v>680</v>
       </c>
       <c r="I38" s="14">
-        <v>1899</v>
+        <v>680</v>
       </c>
       <c r="J38" s="14">
-        <v>1763</v>
+        <v>680</v>
       </c>
       <c r="K38" s="14">
-        <v>1806</v>
+        <v>680</v>
       </c>
       <c r="L38" s="14">
-        <v>1923</v>
+        <v>680</v>
       </c>
       <c r="M38" s="14">
-        <v>1832</v>
+        <v>681</v>
       </c>
       <c r="N38" s="14">
-        <v>1975</v>
+        <v>681</v>
       </c>
       <c r="O38" s="14">
-        <v>1957</v>
+        <v>681</v>
       </c>
       <c r="P38" s="14">
-        <v>1883</v>
+        <v>681</v>
       </c>
       <c r="Q38" s="14">
-        <v>2021</v>
+        <v>681</v>
       </c>
       <c r="R38" s="14">
-        <v>1988</v>
+        <v>681</v>
       </c>
       <c r="S38" s="14">
-        <v>2061</v>
+        <v>680</v>
       </c>
       <c r="T38" s="14">
-        <v>1786</v>
-      </c>
-      <c r="U38" s="14"/>
+        <v>680</v>
+      </c>
+      <c r="U38" s="14">
+        <v>680</v>
+      </c>
       <c r="V38" s="14"/>
       <c r="W38" s="14"/>
       <c r="X38" s="14"/>
       <c r="Y38" s="14"/>
-      <c r="AD38" s="14"/>
-    </row>
-    <row r="39" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD38" s="14">
+        <v>680</v>
+      </c>
+      <c r="AE38" s="14">
+        <v>681</v>
+      </c>
+      <c r="AF38" s="14">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="39" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C39" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D39" s="14">
-        <v>1486</v>
+        <v>1324</v>
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="14"/>
       <c r="G39" s="14"/>
       <c r="H39" s="14">
-        <v>1707</v>
+        <v>1828</v>
       </c>
       <c r="I39" s="14">
-        <v>1563</v>
+        <v>1899</v>
       </c>
       <c r="J39" s="14">
-        <v>1770</v>
+        <v>1763</v>
       </c>
       <c r="K39" s="14">
-        <v>1712</v>
+        <v>1806</v>
       </c>
       <c r="L39" s="14">
-        <v>1908</v>
+        <v>1923</v>
       </c>
       <c r="M39" s="14">
-        <v>1670</v>
+        <v>1832</v>
       </c>
       <c r="N39" s="14">
-        <v>1498</v>
+        <v>1975</v>
       </c>
       <c r="O39" s="14">
+        <v>1957</v>
+      </c>
+      <c r="P39" s="14">
+        <v>1883</v>
+      </c>
+      <c r="Q39" s="14">
+        <v>2021</v>
+      </c>
+      <c r="R39" s="14">
+        <v>1988</v>
+      </c>
+      <c r="S39" s="14">
+        <v>2061</v>
+      </c>
+      <c r="T39" s="14">
         <v>1786</v>
       </c>
-      <c r="P39" s="14">
-        <v>1893</v>
-      </c>
-      <c r="Q39" s="14">
-        <v>1301</v>
-      </c>
-      <c r="R39" s="14">
-        <v>1483</v>
-      </c>
-      <c r="S39" s="14">
+      <c r="U39" s="14">
         <v>1800</v>
       </c>
-      <c r="T39" s="14">
-        <v>2116</v>
-      </c>
-      <c r="U39" s="14"/>
       <c r="V39" s="14"/>
       <c r="W39" s="14"/>
       <c r="X39" s="14"/>
       <c r="Y39" s="14"/>
-      <c r="AD39" s="14"/>
-    </row>
-    <row r="40" spans="3:30" x14ac:dyDescent="0.25">
-      <c r="C40" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="16">
-        <f t="shared" ref="D40:O40" si="100">SUM(D37:D39)</f>
-        <v>3490</v>
-      </c>
-      <c r="E40" s="16">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="16">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="16">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="16">
-        <f t="shared" si="100"/>
-        <v>4215</v>
-      </c>
-      <c r="I40" s="16">
-        <f t="shared" si="100"/>
-        <v>4142</v>
-      </c>
-      <c r="J40" s="16">
-        <f t="shared" si="100"/>
-        <v>4213</v>
-      </c>
-      <c r="K40" s="16">
-        <f t="shared" si="100"/>
-        <v>4198</v>
-      </c>
-      <c r="L40" s="16">
-        <f t="shared" si="100"/>
-        <v>4511</v>
-      </c>
-      <c r="M40" s="16">
-        <f t="shared" si="100"/>
-        <v>4183</v>
-      </c>
-      <c r="N40" s="16">
-        <f t="shared" si="100"/>
-        <v>4154</v>
-      </c>
-      <c r="O40" s="16">
-        <f t="shared" si="100"/>
-        <v>4424</v>
-      </c>
-      <c r="P40" s="16">
-        <f>SUM(P37:P39)</f>
-        <v>4457</v>
-      </c>
-      <c r="Q40" s="16">
-        <f>SUM(Q37:Q39)</f>
-        <v>4003</v>
-      </c>
-      <c r="R40" s="16">
-        <f>SUM(R37:R39)</f>
-        <v>4152</v>
-      </c>
-      <c r="S40" s="16">
-        <f>SUM(S37:S39)</f>
-        <v>4541</v>
-      </c>
-      <c r="T40" s="16">
-        <f>SUM(T37:T39)</f>
-        <v>4582</v>
-      </c>
-      <c r="U40" s="14"/>
+      <c r="AD39" s="14">
+        <v>1806</v>
+      </c>
+      <c r="AE39" s="14">
+        <v>1957</v>
+      </c>
+      <c r="AF39" s="14">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="40" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="14">
+        <v>1486</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14">
+        <v>1707</v>
+      </c>
+      <c r="I40" s="14">
+        <v>1563</v>
+      </c>
+      <c r="J40" s="14">
+        <v>1770</v>
+      </c>
+      <c r="K40" s="14">
+        <v>1712</v>
+      </c>
+      <c r="L40" s="14">
+        <v>1908</v>
+      </c>
+      <c r="M40" s="14">
+        <v>1670</v>
+      </c>
+      <c r="N40" s="14">
+        <v>1498</v>
+      </c>
+      <c r="O40" s="14">
+        <v>1786</v>
+      </c>
+      <c r="P40" s="14">
+        <v>1893</v>
+      </c>
+      <c r="Q40" s="14">
+        <v>1301</v>
+      </c>
+      <c r="R40" s="14">
+        <v>1483</v>
+      </c>
+      <c r="S40" s="14">
+        <v>1800</v>
+      </c>
+      <c r="T40" s="14">
+        <v>2116</v>
+      </c>
+      <c r="U40" s="14">
+        <v>1524</v>
+      </c>
       <c r="V40" s="14"/>
       <c r="W40" s="14"/>
       <c r="X40" s="14"/>
       <c r="Y40" s="14"/>
-      <c r="AD40" s="53"/>
-    </row>
-    <row r="41" spans="3:30" x14ac:dyDescent="0.25">
-      <c r="C41" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" s="14">
-        <v>475</v>
-      </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14">
+      <c r="AD40" s="14">
+        <v>1712</v>
+      </c>
+      <c r="AE40" s="14">
+        <v>1786</v>
+      </c>
+      <c r="AF40" s="14">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="41" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C41" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="16">
+        <f t="shared" ref="D41:O41" si="104">SUM(D38:D40)</f>
+        <v>3490</v>
+      </c>
+      <c r="E41" s="16">
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
-      <c r="I41" s="14">
-        <v>588</v>
-      </c>
-      <c r="J41" s="14">
-        <v>588</v>
-      </c>
-      <c r="K41" s="14">
-        <v>588</v>
-      </c>
-      <c r="L41" s="14">
-        <v>588</v>
-      </c>
-      <c r="M41" s="14">
-        <v>588</v>
-      </c>
-      <c r="N41" s="14">
-        <v>588</v>
-      </c>
-      <c r="O41" s="14">
-        <v>588</v>
-      </c>
-      <c r="P41" s="14">
-        <v>588</v>
-      </c>
-      <c r="Q41" s="14">
-        <v>588</v>
-      </c>
-      <c r="R41" s="14">
-        <v>588</v>
-      </c>
-      <c r="S41" s="14">
-        <v>588</v>
-      </c>
-      <c r="T41" s="14">
-        <v>588</v>
-      </c>
-      <c r="U41" s="14"/>
+      <c r="F41" s="16">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="16">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="16">
+        <f t="shared" si="104"/>
+        <v>4215</v>
+      </c>
+      <c r="I41" s="16">
+        <f t="shared" si="104"/>
+        <v>4142</v>
+      </c>
+      <c r="J41" s="16">
+        <f t="shared" si="104"/>
+        <v>4213</v>
+      </c>
+      <c r="K41" s="16">
+        <f t="shared" si="104"/>
+        <v>4198</v>
+      </c>
+      <c r="L41" s="16">
+        <f t="shared" si="104"/>
+        <v>4511</v>
+      </c>
+      <c r="M41" s="16">
+        <f t="shared" si="104"/>
+        <v>4183</v>
+      </c>
+      <c r="N41" s="16">
+        <f t="shared" si="104"/>
+        <v>4154</v>
+      </c>
+      <c r="O41" s="16">
+        <f t="shared" si="104"/>
+        <v>4424</v>
+      </c>
+      <c r="P41" s="16">
+        <f>SUM(P38:P40)</f>
+        <v>4457</v>
+      </c>
+      <c r="Q41" s="16">
+        <f>SUM(Q38:Q40)</f>
+        <v>4003</v>
+      </c>
+      <c r="R41" s="16">
+        <f>SUM(R38:R40)</f>
+        <v>4152</v>
+      </c>
+      <c r="S41" s="16">
+        <f>SUM(S38:S40)</f>
+        <v>4541</v>
+      </c>
+      <c r="T41" s="16">
+        <f>SUM(T38:T40)</f>
+        <v>4582</v>
+      </c>
+      <c r="U41" s="16">
+        <f>SUM(U38:U40)</f>
+        <v>4004</v>
+      </c>
       <c r="V41" s="14"/>
       <c r="W41" s="14"/>
       <c r="X41" s="14"/>
       <c r="Y41" s="14"/>
-    </row>
-    <row r="42" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD41" s="16">
+        <f t="shared" ref="AD41" si="105">SUM(AD38:AD40)</f>
+        <v>4198</v>
+      </c>
+      <c r="AE41" s="16">
+        <f t="shared" ref="AE41" si="106">SUM(AE38:AE40)</f>
+        <v>4424</v>
+      </c>
+      <c r="AF41" s="16">
+        <f>SUM(AF38:AF40)</f>
+        <v>4541</v>
+      </c>
+    </row>
+    <row r="42" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C42" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D42" s="14">
-        <v>1050</v>
+        <v>475</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14">
-        <v>1110</v>
+        <v>0</v>
       </c>
       <c r="I42" s="14">
-        <v>1100</v>
+        <v>588</v>
       </c>
       <c r="J42" s="14">
-        <v>1149</v>
+        <v>588</v>
       </c>
       <c r="K42" s="14">
-        <v>1093</v>
+        <v>588</v>
       </c>
       <c r="L42" s="14">
-        <v>1144</v>
+        <v>588</v>
       </c>
       <c r="M42" s="14">
-        <v>1183</v>
+        <v>588</v>
       </c>
       <c r="N42" s="14">
-        <v>1186</v>
+        <v>588</v>
       </c>
       <c r="O42" s="14">
-        <v>1151</v>
+        <v>588</v>
       </c>
       <c r="P42" s="14">
-        <v>1167</v>
+        <v>588</v>
       </c>
       <c r="Q42" s="14">
-        <v>1233</v>
+        <v>588</v>
       </c>
       <c r="R42" s="14">
-        <v>1175</v>
+        <v>588</v>
       </c>
       <c r="S42" s="14">
-        <v>1126</v>
+        <v>588</v>
       </c>
       <c r="T42" s="14">
-        <v>1125</v>
-      </c>
-      <c r="U42" s="14"/>
+        <v>588</v>
+      </c>
+      <c r="U42" s="14">
+        <v>588</v>
+      </c>
       <c r="V42" s="14"/>
       <c r="W42" s="14"/>
       <c r="X42" s="14"/>
       <c r="Y42" s="14"/>
-    </row>
-    <row r="43" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD42" s="14">
+        <v>588</v>
+      </c>
+      <c r="AE42" s="14">
+        <v>588</v>
+      </c>
+      <c r="AF42" s="14">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="43" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C43" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D43" s="14">
-        <v>144</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16">
-        <v>148</v>
-      </c>
-      <c r="I43" s="16">
-        <v>177</v>
-      </c>
-      <c r="J43" s="16">
-        <v>148</v>
-      </c>
-      <c r="K43" s="16">
-        <v>168</v>
-      </c>
-      <c r="L43" s="16">
-        <v>176</v>
-      </c>
-      <c r="M43" s="16">
-        <v>165</v>
-      </c>
-      <c r="N43" s="16">
-        <v>187</v>
-      </c>
-      <c r="O43" s="16">
-        <v>198</v>
+        <v>1050</v>
+      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14">
+        <v>1110</v>
+      </c>
+      <c r="I43" s="14">
+        <v>1100</v>
+      </c>
+      <c r="J43" s="14">
+        <v>1149</v>
+      </c>
+      <c r="K43" s="14">
+        <v>1093</v>
+      </c>
+      <c r="L43" s="14">
+        <v>1144</v>
+      </c>
+      <c r="M43" s="14">
+        <v>1183</v>
+      </c>
+      <c r="N43" s="14">
+        <v>1186</v>
+      </c>
+      <c r="O43" s="14">
+        <v>1151</v>
       </c>
       <c r="P43" s="14">
-        <v>191</v>
+        <v>1167</v>
       </c>
       <c r="Q43" s="14">
-        <v>192</v>
+        <v>1233</v>
       </c>
       <c r="R43" s="14">
-        <v>195</v>
+        <v>1175</v>
       </c>
       <c r="S43" s="14">
-        <v>185</v>
+        <v>1126</v>
       </c>
       <c r="T43" s="14">
-        <v>175</v>
-      </c>
-      <c r="U43" s="14"/>
+        <v>1125</v>
+      </c>
+      <c r="U43" s="14">
+        <v>1186</v>
+      </c>
       <c r="V43" s="14"/>
       <c r="W43" s="14"/>
       <c r="X43" s="14"/>
       <c r="Y43" s="14"/>
-    </row>
-    <row r="44" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD43" s="14">
+        <v>1093</v>
+      </c>
+      <c r="AE43" s="14">
+        <v>1151</v>
+      </c>
+      <c r="AF43" s="14">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="44" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C44" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" s="16">
-        <v>135</v>
-      </c>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14">
-        <v>155</v>
-      </c>
-      <c r="I44" s="14">
-        <v>154</v>
-      </c>
-      <c r="J44" s="14">
-        <v>150</v>
-      </c>
-      <c r="K44" s="14">
-        <v>151</v>
-      </c>
-      <c r="L44" s="14">
-        <v>153</v>
-      </c>
-      <c r="M44" s="14">
-        <v>150</v>
-      </c>
-      <c r="N44" s="14">
-        <v>156</v>
-      </c>
-      <c r="O44" s="14">
+        <v>80</v>
+      </c>
+      <c r="D44" s="14">
+        <v>144</v>
+      </c>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16">
+        <v>148</v>
+      </c>
+      <c r="I44" s="16">
+        <v>177</v>
+      </c>
+      <c r="J44" s="16">
+        <v>148</v>
+      </c>
+      <c r="K44" s="16">
         <v>168</v>
       </c>
+      <c r="L44" s="16">
+        <v>176</v>
+      </c>
+      <c r="M44" s="16">
+        <v>165</v>
+      </c>
+      <c r="N44" s="16">
+        <v>187</v>
+      </c>
+      <c r="O44" s="16">
+        <v>198</v>
+      </c>
       <c r="P44" s="14">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="Q44" s="14">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="R44" s="14">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="S44" s="14">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="T44" s="14">
-        <v>163</v>
-      </c>
-      <c r="U44" s="14"/>
+        <v>175</v>
+      </c>
+      <c r="U44" s="14">
+        <v>166</v>
+      </c>
       <c r="V44" s="14"/>
       <c r="W44" s="14"/>
       <c r="X44" s="14"/>
       <c r="Y44" s="14"/>
-    </row>
-    <row r="45" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD44" s="16">
+        <v>168</v>
+      </c>
+      <c r="AE44" s="16">
+        <v>198</v>
+      </c>
+      <c r="AF44" s="14">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C45" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" s="14">
-        <v>4874</v>
+        <v>81</v>
+      </c>
+      <c r="D45" s="16">
+        <v>135</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
       <c r="G45" s="14"/>
       <c r="H45" s="14">
-        <v>6999</v>
+        <v>155</v>
       </c>
       <c r="I45" s="14">
-        <v>7521</v>
+        <v>154</v>
       </c>
       <c r="J45" s="14">
-        <v>5007</v>
+        <v>150</v>
       </c>
       <c r="K45" s="14">
-        <v>8045</v>
+        <v>151</v>
       </c>
       <c r="L45" s="14">
-        <v>5148</v>
+        <v>153</v>
       </c>
       <c r="M45" s="14">
-        <v>7118</v>
+        <v>150</v>
       </c>
       <c r="N45" s="14">
-        <v>4905</v>
+        <v>156</v>
       </c>
       <c r="O45" s="14">
-        <v>9746</v>
+        <v>168</v>
       </c>
       <c r="P45" s="14">
-        <v>5950</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="14">
-        <v>8314</v>
+        <v>170</v>
       </c>
       <c r="R45" s="14">
-        <v>5249</v>
+        <v>170</v>
       </c>
       <c r="S45" s="14">
-        <v>9670</v>
+        <v>174</v>
       </c>
       <c r="T45" s="14">
-        <v>7389</v>
-      </c>
-      <c r="U45" s="14"/>
+        <v>163</v>
+      </c>
+      <c r="U45" s="14">
+        <v>163</v>
+      </c>
       <c r="V45" s="14"/>
       <c r="W45" s="14"/>
       <c r="X45" s="14"/>
       <c r="Y45" s="14"/>
-    </row>
-    <row r="46" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD45" s="14">
+        <v>151</v>
+      </c>
+      <c r="AE45" s="14">
+        <v>168</v>
+      </c>
+      <c r="AF45" s="14">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="46" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C46" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D46" s="14">
-        <v>265</v>
+        <v>4874</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="14"/>
       <c r="H46" s="14">
-        <v>484</v>
+        <v>6999</v>
       </c>
       <c r="I46" s="14">
-        <v>585</v>
+        <v>7521</v>
       </c>
       <c r="J46" s="14">
-        <v>570</v>
+        <v>5007</v>
       </c>
       <c r="K46" s="14">
-        <v>5</v>
+        <v>8045</v>
       </c>
       <c r="L46" s="14">
-        <v>327</v>
+        <v>5148</v>
       </c>
       <c r="M46" s="14">
-        <v>655</v>
+        <v>7118</v>
       </c>
       <c r="N46" s="14">
-        <v>520</v>
+        <v>4905</v>
       </c>
       <c r="O46" s="14">
-        <v>4</v>
+        <v>9746</v>
       </c>
       <c r="P46" s="14">
-        <v>13</v>
+        <v>5950</v>
       </c>
       <c r="Q46" s="14">
-        <v>891</v>
+        <v>8314</v>
       </c>
       <c r="R46" s="14">
-        <v>730</v>
+        <v>5249</v>
       </c>
       <c r="S46" s="14">
-        <v>4</v>
+        <v>9670</v>
       </c>
       <c r="T46" s="14">
-        <v>15</v>
-      </c>
-      <c r="U46" s="14"/>
+        <v>7389</v>
+      </c>
+      <c r="U46" s="14">
+        <v>9130</v>
+      </c>
       <c r="V46" s="14"/>
       <c r="W46" s="14"/>
       <c r="X46" s="14"/>
       <c r="Y46" s="14"/>
-    </row>
-    <row r="47" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD46" s="14">
+        <v>8045</v>
+      </c>
+      <c r="AE46" s="14">
+        <v>9746</v>
+      </c>
+      <c r="AF46" s="14">
+        <v>9670</v>
+      </c>
+    </row>
+    <row r="47" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C47" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D47" s="14">
-        <v>337</v>
+        <v>265</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14"/>
       <c r="H47" s="14">
-        <v>411</v>
+        <v>484</v>
       </c>
       <c r="I47" s="14">
-        <v>448</v>
+        <v>585</v>
       </c>
       <c r="J47" s="14">
-        <v>423</v>
+        <v>570</v>
       </c>
       <c r="K47" s="14">
-        <v>418</v>
+        <v>5</v>
       </c>
       <c r="L47" s="14">
-        <v>470</v>
+        <v>327</v>
       </c>
       <c r="M47" s="14">
-        <v>458</v>
+        <v>655</v>
       </c>
       <c r="N47" s="14">
-        <v>447</v>
+        <v>520</v>
       </c>
       <c r="O47" s="14">
-        <v>456</v>
+        <v>4</v>
       </c>
       <c r="P47" s="14">
-        <v>470</v>
+        <v>13</v>
       </c>
       <c r="Q47" s="14">
-        <v>491</v>
+        <v>891</v>
       </c>
       <c r="R47" s="14">
-        <v>475</v>
+        <v>730</v>
       </c>
       <c r="S47" s="14">
-        <v>470</v>
+        <v>4</v>
       </c>
       <c r="T47" s="14">
-        <v>467</v>
-      </c>
-      <c r="U47" s="14"/>
+        <v>15</v>
+      </c>
+      <c r="U47" s="14">
+        <v>1305</v>
+      </c>
       <c r="V47" s="14"/>
       <c r="W47" s="14"/>
       <c r="X47" s="14"/>
       <c r="Y47" s="14"/>
-    </row>
-    <row r="48" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AD47" s="14">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="14">
+        <v>4</v>
+      </c>
+      <c r="AF47" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C48" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D48" s="14">
-        <v>50</v>
+        <v>337</v>
       </c>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
       <c r="H48" s="14">
-        <v>71</v>
+        <v>411</v>
       </c>
       <c r="I48" s="14">
-        <v>116</v>
+        <v>448</v>
       </c>
       <c r="J48" s="14">
-        <v>150</v>
+        <v>423</v>
       </c>
       <c r="K48" s="14">
-        <v>200</v>
+        <v>418</v>
       </c>
       <c r="L48" s="14">
-        <v>103</v>
+        <v>470</v>
       </c>
       <c r="M48" s="14">
-        <v>159</v>
+        <v>458</v>
       </c>
       <c r="N48" s="14">
-        <v>160</v>
+        <v>447</v>
       </c>
       <c r="O48" s="14">
-        <v>144</v>
+        <v>456</v>
       </c>
       <c r="P48" s="14">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="Q48" s="14">
-        <v>144</v>
+        <v>491</v>
       </c>
       <c r="R48" s="14">
-        <v>221</v>
+        <v>475</v>
       </c>
       <c r="S48" s="14">
-        <v>48</v>
+        <v>470</v>
       </c>
       <c r="T48" s="14">
-        <v>115</v>
-      </c>
-      <c r="U48" s="14"/>
+        <v>467</v>
+      </c>
+      <c r="U48" s="14">
+        <v>458</v>
+      </c>
       <c r="V48" s="14"/>
       <c r="W48" s="14"/>
       <c r="X48" s="14"/>
       <c r="Y48" s="14"/>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AD48" s="14">
+        <v>418</v>
+      </c>
+      <c r="AE48" s="14">
+        <v>456</v>
+      </c>
+      <c r="AF48" s="14">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="C49" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D49" s="14">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
       <c r="H49" s="14">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="I49" s="14">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="J49" s="14">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="K49" s="14">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="L49" s="14">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="M49" s="14">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="N49" s="14">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="O49" s="14">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="P49" s="14">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="Q49" s="14">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="R49" s="14">
-        <v>53</v>
+        <v>221</v>
       </c>
       <c r="S49" s="14">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="T49" s="14">
-        <v>60</v>
-      </c>
-      <c r="U49" s="14"/>
+        <v>115</v>
+      </c>
+      <c r="U49" s="14">
+        <v>172</v>
+      </c>
       <c r="V49" s="14"/>
       <c r="W49" s="14"/>
       <c r="X49" s="14"/>
       <c r="Y49" s="14"/>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AD49" s="14">
+        <v>200</v>
+      </c>
+      <c r="AE49" s="14">
+        <v>144</v>
+      </c>
+      <c r="AF49" s="14">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="C50" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D50" s="14">
-        <v>2552</v>
+        <v>118</v>
       </c>
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14"/>
       <c r="H50" s="14">
-        <v>3199</v>
+        <v>45</v>
       </c>
       <c r="I50" s="14">
-        <v>3427</v>
+        <v>40</v>
       </c>
       <c r="J50" s="14">
-        <v>2989</v>
+        <v>49</v>
       </c>
       <c r="K50" s="14">
-        <v>3715</v>
+        <v>55</v>
       </c>
       <c r="L50" s="14">
-        <v>3442</v>
+        <v>54</v>
       </c>
       <c r="M50" s="14">
-        <v>3343</v>
+        <v>38</v>
       </c>
       <c r="N50" s="14">
-        <v>3821</v>
+        <v>39</v>
       </c>
       <c r="O50" s="14">
-        <v>4141</v>
+        <v>90</v>
       </c>
       <c r="P50" s="14">
-        <v>3932</v>
+        <v>64</v>
       </c>
       <c r="Q50" s="14">
-        <v>4617</v>
+        <v>58</v>
       </c>
       <c r="R50" s="14">
-        <v>3998</v>
+        <v>53</v>
       </c>
       <c r="S50" s="14">
-        <v>4460</v>
+        <v>75</v>
       </c>
       <c r="T50" s="14">
-        <v>3761</v>
-      </c>
-      <c r="U50" s="14"/>
+        <v>60</v>
+      </c>
+      <c r="U50" s="14">
+        <v>86</v>
+      </c>
       <c r="V50" s="14"/>
       <c r="W50" s="14"/>
       <c r="X50" s="14"/>
       <c r="Y50" s="14"/>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C51" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D51" s="16">
-        <f t="shared" ref="D51:O51" si="101">SUM(D41:D50)</f>
-        <v>10000</v>
-      </c>
-      <c r="E51" s="16">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="16">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="16">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="16">
-        <f t="shared" si="101"/>
-        <v>12622</v>
-      </c>
-      <c r="I51" s="16">
-        <f t="shared" si="101"/>
-        <v>14156</v>
-      </c>
-      <c r="J51" s="16">
-        <f t="shared" si="101"/>
-        <v>11223</v>
-      </c>
-      <c r="K51" s="16">
-        <f t="shared" si="101"/>
-        <v>14438</v>
-      </c>
-      <c r="L51" s="16">
-        <f t="shared" si="101"/>
-        <v>11605</v>
-      </c>
-      <c r="M51" s="16">
-        <f t="shared" si="101"/>
-        <v>13857</v>
-      </c>
-      <c r="N51" s="16">
-        <f t="shared" si="101"/>
-        <v>12009</v>
-      </c>
-      <c r="O51" s="16">
-        <f t="shared" si="101"/>
-        <v>16686</v>
-      </c>
-      <c r="P51" s="16">
-        <f>SUM(P41:P50)</f>
-        <v>12625</v>
-      </c>
-      <c r="Q51" s="16">
-        <f>SUM(Q41:Q50)</f>
-        <v>16698</v>
-      </c>
-      <c r="R51" s="16">
-        <f>SUM(R41:R50)</f>
-        <v>12854</v>
-      </c>
-      <c r="S51" s="16">
-        <f>SUM(S41:S50)</f>
-        <v>16800</v>
-      </c>
-      <c r="T51" s="16">
-        <f>SUM(T41:T50)</f>
-        <v>13858</v>
-      </c>
-      <c r="U51" s="14"/>
+      <c r="AD50" s="14">
+        <v>55</v>
+      </c>
+      <c r="AE50" s="14">
+        <v>90</v>
+      </c>
+      <c r="AF50" s="14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="C51" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="14">
+        <v>2552</v>
+      </c>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14">
+        <v>3199</v>
+      </c>
+      <c r="I51" s="14">
+        <v>3427</v>
+      </c>
+      <c r="J51" s="14">
+        <v>2989</v>
+      </c>
+      <c r="K51" s="14">
+        <v>3715</v>
+      </c>
+      <c r="L51" s="14">
+        <v>3442</v>
+      </c>
+      <c r="M51" s="14">
+        <v>3343</v>
+      </c>
+      <c r="N51" s="14">
+        <v>3821</v>
+      </c>
+      <c r="O51" s="14">
+        <v>4141</v>
+      </c>
+      <c r="P51" s="14">
+        <v>3932</v>
+      </c>
+      <c r="Q51" s="14">
+        <v>4617</v>
+      </c>
+      <c r="R51" s="14">
+        <v>3998</v>
+      </c>
+      <c r="S51" s="14">
+        <v>4460</v>
+      </c>
+      <c r="T51" s="14">
+        <v>3761</v>
+      </c>
+      <c r="U51" s="14">
+        <v>4333</v>
+      </c>
       <c r="V51" s="14"/>
       <c r="W51" s="14"/>
       <c r="X51" s="14"/>
       <c r="Y51" s="14"/>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C52" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D52" s="12">
-        <f t="shared" ref="D52:O52" si="102">D40+D51</f>
-        <v>13490</v>
-      </c>
-      <c r="E52" s="12">
-        <f t="shared" si="102"/>
+      <c r="AD51" s="14">
+        <v>3715</v>
+      </c>
+      <c r="AE51" s="14">
+        <v>4141</v>
+      </c>
+      <c r="AF51" s="14">
+        <v>4460</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="C52" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="16">
+        <f t="shared" ref="D52:O52" si="107">SUM(D42:D51)</f>
+        <v>10000</v>
+      </c>
+      <c r="E52" s="16">
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
-      <c r="F52" s="12">
-        <f t="shared" si="102"/>
+      <c r="F52" s="16">
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
-      <c r="G52" s="12">
-        <f t="shared" si="102"/>
+      <c r="G52" s="16">
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
-      <c r="H52" s="12">
-        <f t="shared" si="102"/>
-        <v>16837</v>
-      </c>
-      <c r="I52" s="12">
-        <f t="shared" si="102"/>
-        <v>18298</v>
-      </c>
-      <c r="J52" s="12">
-        <f t="shared" si="102"/>
-        <v>15436</v>
-      </c>
-      <c r="K52" s="12">
-        <f t="shared" si="102"/>
-        <v>18636</v>
-      </c>
-      <c r="L52" s="12">
-        <f t="shared" si="102"/>
-        <v>16116</v>
-      </c>
-      <c r="M52" s="12">
-        <f t="shared" si="102"/>
-        <v>18040</v>
-      </c>
-      <c r="N52" s="12">
-        <f t="shared" si="102"/>
-        <v>16163</v>
-      </c>
-      <c r="O52" s="12">
-        <f t="shared" si="102"/>
-        <v>21110</v>
-      </c>
-      <c r="P52" s="12">
-        <f>P40+P51</f>
-        <v>17082</v>
-      </c>
-      <c r="Q52" s="12">
-        <f>Q40+Q51</f>
-        <v>20701</v>
-      </c>
-      <c r="R52" s="12">
-        <f>R40+R51</f>
-        <v>17006</v>
-      </c>
-      <c r="S52" s="12">
-        <f>S40+S51</f>
-        <v>21341</v>
-      </c>
-      <c r="T52" s="12">
-        <f>T40+T51</f>
-        <v>18440</v>
-      </c>
-      <c r="U52" s="14"/>
+      <c r="H52" s="16">
+        <f t="shared" si="107"/>
+        <v>12622</v>
+      </c>
+      <c r="I52" s="16">
+        <f t="shared" si="107"/>
+        <v>14156</v>
+      </c>
+      <c r="J52" s="16">
+        <f t="shared" si="107"/>
+        <v>11223</v>
+      </c>
+      <c r="K52" s="16">
+        <f t="shared" si="107"/>
+        <v>14438</v>
+      </c>
+      <c r="L52" s="16">
+        <f t="shared" si="107"/>
+        <v>11605</v>
+      </c>
+      <c r="M52" s="16">
+        <f t="shared" si="107"/>
+        <v>13857</v>
+      </c>
+      <c r="N52" s="16">
+        <f t="shared" si="107"/>
+        <v>12009</v>
+      </c>
+      <c r="O52" s="16">
+        <f t="shared" si="107"/>
+        <v>16686</v>
+      </c>
+      <c r="P52" s="16">
+        <f>SUM(P42:P51)</f>
+        <v>12625</v>
+      </c>
+      <c r="Q52" s="16">
+        <f>SUM(Q42:Q51)</f>
+        <v>16698</v>
+      </c>
+      <c r="R52" s="16">
+        <f>SUM(R42:R51)</f>
+        <v>12854</v>
+      </c>
+      <c r="S52" s="16">
+        <f>SUM(S42:S51)</f>
+        <v>16800</v>
+      </c>
+      <c r="T52" s="16">
+        <f>SUM(T42:T51)</f>
+        <v>13858</v>
+      </c>
+      <c r="U52" s="16">
+        <f>SUM(U42:U51)</f>
+        <v>17587</v>
+      </c>
       <c r="V52" s="14"/>
       <c r="W52" s="14"/>
       <c r="X52" s="14"/>
       <c r="Y52" s="14"/>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="14"/>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C54" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="AD52" s="16">
+        <f t="shared" ref="AD52" si="108">SUM(AD42:AD51)</f>
+        <v>14438</v>
+      </c>
+      <c r="AE52" s="16">
+        <f t="shared" ref="AE52" si="109">SUM(AE42:AE51)</f>
+        <v>16686</v>
+      </c>
+      <c r="AF52" s="16">
+        <f>SUM(AF42:AF51)</f>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="C53" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="12">
+        <f t="shared" ref="D53:O53" si="110">D41+D52</f>
+        <v>13490</v>
+      </c>
+      <c r="E53" s="12">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="12">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="12">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="12">
+        <f t="shared" si="110"/>
+        <v>16837</v>
+      </c>
+      <c r="I53" s="12">
+        <f t="shared" si="110"/>
+        <v>18298</v>
+      </c>
+      <c r="J53" s="12">
+        <f t="shared" si="110"/>
+        <v>15436</v>
+      </c>
+      <c r="K53" s="12">
+        <f t="shared" si="110"/>
+        <v>18636</v>
+      </c>
+      <c r="L53" s="12">
+        <f t="shared" si="110"/>
+        <v>16116</v>
+      </c>
+      <c r="M53" s="12">
+        <f t="shared" si="110"/>
+        <v>18040</v>
+      </c>
+      <c r="N53" s="12">
+        <f t="shared" si="110"/>
+        <v>16163</v>
+      </c>
+      <c r="O53" s="12">
+        <f t="shared" si="110"/>
+        <v>21110</v>
+      </c>
+      <c r="P53" s="12">
+        <f>P41+P52</f>
+        <v>17082</v>
+      </c>
+      <c r="Q53" s="12">
+        <f>Q41+Q52</f>
+        <v>20701</v>
+      </c>
+      <c r="R53" s="12">
+        <f>R41+R52</f>
+        <v>17006</v>
+      </c>
+      <c r="S53" s="12">
+        <f>S41+S52</f>
+        <v>21341</v>
+      </c>
+      <c r="T53" s="12">
+        <f>T41+T52</f>
+        <v>18440</v>
+      </c>
+      <c r="U53" s="12">
+        <f>U41+U52</f>
+        <v>21591</v>
+      </c>
+      <c r="V53" s="14"/>
+      <c r="W53" s="14"/>
+      <c r="X53" s="14"/>
+      <c r="Y53" s="14"/>
+      <c r="AD53" s="12">
+        <f t="shared" ref="AD53" si="111">AD41+AD52</f>
+        <v>18636</v>
+      </c>
+      <c r="AE53" s="12">
+        <f t="shared" ref="AE53" si="112">AE41+AE52</f>
+        <v>21110</v>
+      </c>
+      <c r="AF53" s="12">
+        <f>AF41+AF52</f>
+        <v>21341</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -5754,1769 +6315,1798 @@
       <c r="L54" s="14"/>
       <c r="M54" s="14"/>
       <c r="N54" s="14"/>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C55" s="2" t="s">
+      <c r="O54" s="14"/>
+      <c r="P54" s="14"/>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="C55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
+    </row>
+    <row r="56" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D55" s="14">
-        <f t="shared" ref="D55:Q55" si="103">D14</f>
+      <c r="D56" s="14">
+        <f t="shared" ref="D56:Q56" si="113">D14</f>
         <v>164</v>
       </c>
-      <c r="E55" s="14">
-        <f t="shared" si="103"/>
+      <c r="E56" s="14">
+        <f t="shared" si="113"/>
         <v>282</v>
       </c>
-      <c r="F55" s="14">
-        <f t="shared" si="103"/>
+      <c r="F56" s="14">
+        <f t="shared" si="113"/>
         <v>248</v>
       </c>
-      <c r="G55" s="14">
-        <f t="shared" si="103"/>
+      <c r="G56" s="14">
+        <f t="shared" si="113"/>
         <v>391</v>
       </c>
-      <c r="H55" s="14">
-        <f t="shared" si="103"/>
+      <c r="H56" s="14">
+        <f t="shared" si="113"/>
         <v>224</v>
       </c>
-      <c r="I55" s="14">
-        <f t="shared" si="103"/>
+      <c r="I56" s="14">
+        <f t="shared" si="113"/>
         <v>249</v>
       </c>
-      <c r="J55" s="14">
-        <f t="shared" si="103"/>
+      <c r="J56" s="14">
+        <f t="shared" si="113"/>
         <v>237</v>
       </c>
-      <c r="K55" s="14">
-        <f t="shared" si="103"/>
+      <c r="K56" s="14">
+        <f t="shared" si="113"/>
         <v>310</v>
       </c>
-      <c r="L55" s="14">
-        <f t="shared" si="103"/>
+      <c r="L56" s="14">
+        <f t="shared" si="113"/>
         <v>246</v>
       </c>
-      <c r="M55" s="14">
-        <f t="shared" si="103"/>
+      <c r="M56" s="14">
+        <f t="shared" si="113"/>
         <v>178</v>
       </c>
-      <c r="N55" s="14">
-        <f t="shared" si="103"/>
+      <c r="N56" s="14">
+        <f t="shared" si="113"/>
         <v>250</v>
       </c>
-      <c r="O55" s="14">
-        <f t="shared" si="103"/>
+      <c r="O56" s="14">
+        <f t="shared" si="113"/>
         <v>329</v>
       </c>
-      <c r="P55" s="14">
-        <f t="shared" si="103"/>
+      <c r="P56" s="14">
+        <f t="shared" si="113"/>
         <v>208</v>
       </c>
-      <c r="Q55" s="14">
-        <f t="shared" si="103"/>
+      <c r="Q56" s="14">
+        <f t="shared" si="113"/>
         <v>203</v>
       </c>
-      <c r="R55" s="14">
+      <c r="R56" s="14">
         <f>R14</f>
         <v>292</v>
       </c>
-      <c r="S55" s="14">
+      <c r="S56" s="14">
         <f>S14</f>
         <v>438</v>
       </c>
-      <c r="T55" s="14">
+      <c r="T56" s="14">
         <f>T14</f>
         <v>308</v>
       </c>
-      <c r="V55" s="14"/>
-      <c r="Z55" s="2">
-        <f t="shared" ref="Z55:AF55" si="104">Z14</f>
+      <c r="U56" s="14">
+        <f>U14</f>
+        <v>283</v>
+      </c>
+      <c r="Z56" s="14">
+        <f t="shared" ref="Z56:AF56" si="114">Z14</f>
         <v>656</v>
       </c>
-      <c r="AA55" s="2">
-        <f t="shared" si="104"/>
+      <c r="AA56" s="14">
+        <f t="shared" si="114"/>
         <v>750</v>
       </c>
-      <c r="AB55" s="2">
-        <f t="shared" si="104"/>
+      <c r="AB56" s="14">
+        <f t="shared" si="114"/>
         <v>942</v>
       </c>
-      <c r="AC55" s="2">
-        <f t="shared" si="104"/>
+      <c r="AC56" s="14">
+        <f t="shared" si="114"/>
         <v>1084</v>
       </c>
-      <c r="AD55" s="2">
-        <f t="shared" si="104"/>
+      <c r="AD56" s="14">
+        <f t="shared" si="114"/>
         <v>1021</v>
       </c>
-      <c r="AE55" s="2">
-        <f t="shared" si="104"/>
+      <c r="AE56" s="14">
+        <f t="shared" si="114"/>
         <v>1002</v>
       </c>
-      <c r="AF55" s="2">
-        <f t="shared" si="104"/>
+      <c r="AF56" s="14">
+        <f t="shared" si="114"/>
         <v>1141</v>
       </c>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C56" s="2" t="s">
+      <c r="AG56" s="15"/>
+    </row>
+    <row r="57" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D56" s="14">
+      <c r="D57" s="14">
         <v>163</v>
       </c>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14">
+      <c r="H57" s="14">
         <v>224</v>
       </c>
-      <c r="I56" s="14">
+      <c r="I57" s="14">
         <v>249</v>
       </c>
-      <c r="J56" s="14">
+      <c r="J57" s="14">
         <v>237</v>
       </c>
-      <c r="K56" s="14">
+      <c r="K57" s="14">
         <v>311</v>
       </c>
-      <c r="L56" s="14">
+      <c r="L57" s="14">
         <v>245</v>
       </c>
-      <c r="M56" s="14">
+      <c r="M57" s="14">
         <v>178</v>
       </c>
-      <c r="N56" s="14">
+      <c r="N57" s="14">
         <v>250</v>
       </c>
-      <c r="O56" s="14">
+      <c r="O57" s="14">
         <v>329</v>
       </c>
-      <c r="P56" s="14">
+      <c r="P57" s="14">
         <v>209</v>
       </c>
-      <c r="Q56" s="14">
+      <c r="Q57" s="14">
         <v>203</v>
       </c>
-      <c r="R56" s="14">
+      <c r="R57" s="14">
         <v>292</v>
       </c>
-      <c r="S56" s="2">
+      <c r="S57" s="2">
         <v>437</v>
       </c>
-      <c r="T56" s="2">
+      <c r="T57" s="2">
         <v>460</v>
       </c>
-      <c r="V56" s="14"/>
-      <c r="AB56" s="2">
+      <c r="U57" s="14">
+        <v>283</v>
+      </c>
+      <c r="AB57" s="14">
         <v>942</v>
       </c>
-      <c r="AC56" s="2">
+      <c r="AC57" s="14">
         <v>1084</v>
       </c>
-      <c r="AD56" s="14">
-        <f t="shared" ref="AD56:AD63" si="105">SUM(H56:K56)</f>
+      <c r="AD57" s="14">
+        <f t="shared" ref="AD57:AD64" si="115">SUM(H57:K57)</f>
         <v>1021</v>
       </c>
-      <c r="AE56" s="14">
-        <f t="shared" ref="AE56:AE63" si="106">SUM(L56:O56)</f>
+      <c r="AE57" s="14">
+        <f t="shared" ref="AE57:AE64" si="116">SUM(L57:O57)</f>
         <v>1002</v>
       </c>
-      <c r="AF56" s="2">
+      <c r="AF57" s="14">
         <v>1141</v>
       </c>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C57" s="2" t="s">
+      <c r="AG57" s="15"/>
+    </row>
+    <row r="58" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="14">
+      <c r="D58" s="14">
         <v>147</v>
       </c>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14">
+      <c r="H58" s="14">
         <v>168</v>
       </c>
-      <c r="I57" s="14">
+      <c r="I58" s="14">
         <v>175</v>
       </c>
-      <c r="J57" s="14">
+      <c r="J58" s="14">
         <v>170</v>
       </c>
-      <c r="K57" s="14">
+      <c r="K58" s="14">
         <v>175</v>
       </c>
-      <c r="L57" s="14">
+      <c r="L58" s="14">
         <v>180</v>
       </c>
-      <c r="M57" s="14">
+      <c r="M58" s="14">
         <v>179</v>
       </c>
-      <c r="N57" s="14">
+      <c r="N58" s="14">
         <v>185</v>
       </c>
-      <c r="O57" s="14">
+      <c r="O58" s="14">
         <v>192</v>
       </c>
-      <c r="P57" s="14">
+      <c r="P58" s="14">
         <v>188</v>
       </c>
-      <c r="Q57" s="14">
+      <c r="Q58" s="14">
         <v>194</v>
       </c>
-      <c r="R57" s="14">
+      <c r="R58" s="14">
         <v>197</v>
       </c>
-      <c r="S57" s="2">
+      <c r="S58" s="2">
         <v>200</v>
       </c>
-      <c r="T57" s="2">
+      <c r="T58" s="2">
         <v>194</v>
       </c>
-      <c r="V57" s="14"/>
-      <c r="AB57" s="2">
+      <c r="U58" s="14">
+        <v>188</v>
+      </c>
+      <c r="AB58" s="14">
         <v>84</v>
       </c>
-      <c r="AC57" s="2">
+      <c r="AC58" s="14">
         <v>133</v>
       </c>
-      <c r="AD57" s="14">
-        <f t="shared" si="105"/>
+      <c r="AD58" s="14">
+        <f t="shared" si="115"/>
         <v>688</v>
       </c>
-      <c r="AE57" s="14">
-        <f t="shared" si="106"/>
+      <c r="AE58" s="14">
+        <f t="shared" si="116"/>
         <v>736</v>
       </c>
-      <c r="AF57" s="2">
+      <c r="AF58" s="14">
         <v>779</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C58" s="2" t="s">
+      <c r="AG58" s="15"/>
+    </row>
+    <row r="59" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D58" s="14">
+      <c r="D59" s="14">
         <v>7</v>
       </c>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14">
+      <c r="H59" s="14">
         <v>12</v>
       </c>
-      <c r="I58" s="14">
+      <c r="I59" s="14">
         <v>16</v>
       </c>
-      <c r="J58" s="14">
+      <c r="J59" s="14">
         <v>18</v>
       </c>
-      <c r="K58" s="14">
+      <c r="K59" s="14">
         <v>17</v>
       </c>
-      <c r="L58" s="14">
+      <c r="L59" s="14">
         <v>15</v>
       </c>
-      <c r="M58" s="14">
+      <c r="M59" s="14">
         <v>20</v>
       </c>
-      <c r="N58" s="14">
+      <c r="N59" s="14">
         <v>22</v>
       </c>
-      <c r="O58" s="14">
+      <c r="O59" s="14">
         <v>21</v>
       </c>
-      <c r="P58" s="14">
+      <c r="P59" s="14">
         <v>11</v>
       </c>
-      <c r="Q58" s="14">
+      <c r="Q59" s="14">
         <v>28</v>
       </c>
-      <c r="R58" s="14">
+      <c r="R59" s="14">
         <v>21</v>
       </c>
-      <c r="S58" s="2">
+      <c r="S59" s="2">
         <v>21</v>
       </c>
-      <c r="T58" s="2">
+      <c r="T59" s="2">
         <v>20</v>
       </c>
-      <c r="V58" s="14"/>
-      <c r="AB58" s="2">
+      <c r="U59" s="14">
+        <v>26</v>
+      </c>
+      <c r="AB59" s="14">
         <v>614</v>
       </c>
-      <c r="AC58" s="2">
+      <c r="AC59" s="14">
         <v>615</v>
       </c>
-      <c r="AD58" s="14">
-        <f t="shared" si="105"/>
+      <c r="AD59" s="14">
+        <f t="shared" si="115"/>
         <v>63</v>
       </c>
-      <c r="AE58" s="14">
-        <f t="shared" si="106"/>
+      <c r="AE59" s="14">
+        <f t="shared" si="116"/>
         <v>78</v>
       </c>
-      <c r="AF58" s="2">
+      <c r="AF59" s="14">
         <v>81</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C59" s="2" t="s">
+      <c r="AG59" s="15"/>
+    </row>
+    <row r="60" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D59" s="14">
+      <c r="D60" s="14">
         <v>0</v>
       </c>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14">
+      <c r="H60" s="14">
         <v>0</v>
       </c>
-      <c r="I59" s="14">
+      <c r="I60" s="14">
         <v>0</v>
       </c>
-      <c r="J59" s="14">
+      <c r="J60" s="14">
         <v>0</v>
       </c>
-      <c r="K59" s="14">
+      <c r="K60" s="14">
         <v>0</v>
       </c>
-      <c r="L59" s="14">
+      <c r="L60" s="14">
         <v>-2</v>
       </c>
-      <c r="M59" s="14">
+      <c r="M60" s="14">
         <v>0</v>
       </c>
-      <c r="N59" s="14">
+      <c r="N60" s="14">
         <v>-2</v>
       </c>
-      <c r="O59" s="14">
+      <c r="O60" s="14">
         <v>1</v>
       </c>
-      <c r="P59" s="14">
+      <c r="P60" s="14">
         <v>0</v>
       </c>
-      <c r="Q59" s="14">
+      <c r="Q60" s="14">
         <v>-2</v>
       </c>
-      <c r="R59" s="14">
+      <c r="R60" s="14">
         <v>0</v>
       </c>
-      <c r="S59" s="2">
+      <c r="S60" s="2">
         <v>1</v>
       </c>
-      <c r="T59" s="2">
+      <c r="T60" s="2">
         <v>-1</v>
       </c>
-      <c r="V59" s="14"/>
-      <c r="AB59" s="2">
+      <c r="U60" s="14">
+        <v>-5</v>
+      </c>
+      <c r="AB60" s="14">
         <v>49</v>
       </c>
-      <c r="AC59" s="2">
+      <c r="AC60" s="14">
         <v>53</v>
       </c>
-      <c r="AD59" s="14">
-        <f t="shared" si="105"/>
+      <c r="AD60" s="14">
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
-      <c r="AE59" s="14">
-        <f t="shared" si="106"/>
+      <c r="AE60" s="14">
+        <f t="shared" si="116"/>
         <v>-3</v>
       </c>
-      <c r="AF59" s="2">
+      <c r="AF60" s="14">
         <v>-1</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C60" s="2" t="s">
+      <c r="AG60" s="15"/>
+    </row>
+    <row r="61" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D60" s="14">
+      <c r="D61" s="14">
         <v>23</v>
       </c>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14">
+      <c r="H61" s="14">
         <v>43</v>
       </c>
-      <c r="I60" s="14">
+      <c r="I61" s="14">
         <v>48</v>
       </c>
-      <c r="J60" s="14">
+      <c r="J61" s="14">
         <v>51</v>
       </c>
-      <c r="K60" s="14">
+      <c r="K61" s="14">
         <v>54</v>
       </c>
-      <c r="L60" s="14">
+      <c r="L61" s="14">
         <v>36</v>
       </c>
-      <c r="M60" s="14">
+      <c r="M61" s="14">
         <v>52</v>
       </c>
-      <c r="N60" s="14">
+      <c r="N61" s="14">
         <v>51</v>
       </c>
-      <c r="O60" s="14">
+      <c r="O61" s="14">
         <v>41</v>
       </c>
-      <c r="P60" s="14">
+      <c r="P61" s="14">
         <v>34</v>
       </c>
-      <c r="Q60" s="14">
+      <c r="Q61" s="14">
         <v>45</v>
       </c>
-      <c r="R60" s="14">
+      <c r="R61" s="14">
         <v>45</v>
       </c>
-      <c r="S60" s="2">
+      <c r="S61" s="2">
         <v>41</v>
       </c>
-      <c r="T60" s="2">
+      <c r="T61" s="2">
         <v>-152</v>
       </c>
-      <c r="V60" s="14"/>
-      <c r="AB60" s="2">
+      <c r="U61" s="14">
+        <v>43</v>
+      </c>
+      <c r="AB61" s="14">
         <v>-44</v>
       </c>
-      <c r="AC60" s="2">
+      <c r="AC61" s="14">
         <v>-72</v>
       </c>
-      <c r="AD60" s="14">
-        <f t="shared" si="105"/>
+      <c r="AD61" s="14">
+        <f t="shared" si="115"/>
         <v>196</v>
       </c>
-      <c r="AE60" s="14">
-        <f t="shared" si="106"/>
+      <c r="AE61" s="14">
+        <f t="shared" si="116"/>
         <v>180</v>
       </c>
-      <c r="AF60" s="2">
+      <c r="AF61" s="14">
         <v>165</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C61" s="2" t="s">
+      <c r="AG61" s="15"/>
+    </row>
+    <row r="62" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D61" s="14">
+      <c r="D62" s="14">
         <v>-95</v>
       </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14">
+      <c r="H62" s="14">
         <v>-82</v>
       </c>
-      <c r="I61" s="14">
+      <c r="I62" s="14">
         <v>-39</v>
       </c>
-      <c r="J61" s="14">
+      <c r="J62" s="14">
         <v>-46</v>
       </c>
-      <c r="K61" s="14">
+      <c r="K62" s="14">
         <v>-85</v>
       </c>
-      <c r="L61" s="14">
+      <c r="L62" s="14">
         <v>-99</v>
       </c>
-      <c r="M61" s="14">
+      <c r="M62" s="14">
         <v>-55</v>
       </c>
-      <c r="N61" s="14">
+      <c r="N62" s="14">
         <v>-63</v>
       </c>
-      <c r="O61" s="14">
+      <c r="O62" s="14">
         <v>-47</v>
       </c>
-      <c r="P61" s="14">
+      <c r="P62" s="14">
         <v>-10</v>
       </c>
-      <c r="Q61" s="14">
+      <c r="Q62" s="14">
         <v>-42</v>
       </c>
-      <c r="R61" s="14">
+      <c r="R62" s="14">
         <v>-42</v>
       </c>
-      <c r="S61" s="2">
+      <c r="S62" s="2">
         <v>-86</v>
       </c>
-      <c r="T61" s="2">
+      <c r="T62" s="2">
         <v>-27</v>
       </c>
-      <c r="U61" s="1"/>
-      <c r="V61" s="14"/>
-      <c r="W61" s="1"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="1"/>
-      <c r="AB61" s="2">
+      <c r="U62" s="14">
+        <v>-53</v>
+      </c>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
+      <c r="AB62" s="14">
         <v>-151</v>
       </c>
-      <c r="AC61" s="2">
+      <c r="AC62" s="14">
         <v>-240</v>
       </c>
-      <c r="AD61" s="14">
-        <f t="shared" si="105"/>
+      <c r="AD62" s="14">
+        <f t="shared" si="115"/>
         <v>-252</v>
       </c>
-      <c r="AE61" s="14">
-        <f t="shared" si="106"/>
+      <c r="AE62" s="14">
+        <f t="shared" si="116"/>
         <v>-264</v>
       </c>
-      <c r="AF61" s="2">
+      <c r="AF62" s="14">
         <v>-180</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C62" s="2" t="s">
+      <c r="AG62" s="15"/>
+    </row>
+    <row r="63" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D62" s="14">
+      <c r="D63" s="14">
         <v>-20</v>
       </c>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14">
+      <c r="H63" s="14">
         <v>-43</v>
       </c>
-      <c r="I62" s="14">
+      <c r="I63" s="14">
         <v>-46</v>
       </c>
-      <c r="J62" s="14">
+      <c r="J63" s="14">
         <v>-43</v>
       </c>
-      <c r="K62" s="14">
+      <c r="K63" s="14">
         <v>-64</v>
       </c>
-      <c r="L62" s="14">
+      <c r="L63" s="14">
         <v>-36</v>
       </c>
-      <c r="M62" s="14">
+      <c r="M63" s="14">
         <v>-52</v>
       </c>
-      <c r="N62" s="14">
+      <c r="N63" s="14">
         <v>-52</v>
       </c>
-      <c r="O62" s="14">
+      <c r="O63" s="14">
         <v>-41</v>
       </c>
-      <c r="P62" s="14">
+      <c r="P63" s="14">
         <v>-34</v>
       </c>
-      <c r="Q62" s="14">
+      <c r="Q63" s="14">
         <v>-45</v>
       </c>
-      <c r="R62" s="14">
+      <c r="R63" s="14">
         <v>-45</v>
       </c>
-      <c r="S62" s="2">
+      <c r="S63" s="2">
         <v>-41</v>
       </c>
-      <c r="T62" s="2">
+      <c r="T63" s="2">
         <v>-35</v>
       </c>
-      <c r="U62" s="1"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
-      <c r="AB62" s="2">
+      <c r="U63" s="14">
+        <v>-43</v>
+      </c>
+      <c r="W63" s="12"/>
+      <c r="X63" s="12"/>
+      <c r="Y63" s="12"/>
+      <c r="AB63" s="14">
         <v>-80</v>
       </c>
-      <c r="AC62" s="2">
+      <c r="AC63" s="14">
         <f>-140+7</f>
         <v>-133</v>
       </c>
-      <c r="AD62" s="14">
-        <f t="shared" si="105"/>
+      <c r="AD63" s="14">
+        <f t="shared" si="115"/>
         <v>-196</v>
       </c>
-      <c r="AE62" s="14">
-        <f t="shared" si="106"/>
+      <c r="AE63" s="14">
+        <f t="shared" si="116"/>
         <v>-181</v>
       </c>
-      <c r="AF62" s="2">
+      <c r="AF63" s="14">
         <v>-165</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C63" s="2" t="s">
+      <c r="AG63" s="15"/>
+    </row>
+    <row r="64" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D63" s="14">
+      <c r="D64" s="14">
         <f>1923-340-1545-959</f>
         <v>-921</v>
       </c>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14">
+      <c r="H64" s="14">
         <f>2407+14-1541-996</f>
         <v>-116</v>
       </c>
-      <c r="I63" s="14">
+      <c r="I64" s="14">
         <f>-1449+28+891+465</f>
         <v>-65</v>
       </c>
-      <c r="J63" s="14">
+      <c r="J64" s="14">
         <f>2045+377-2770-341</f>
         <v>-689</v>
       </c>
-      <c r="K63" s="14">
+      <c r="K64" s="14">
         <f>-2810+69+2919+1048</f>
         <v>1226</v>
       </c>
-      <c r="L63" s="14">
+      <c r="L64" s="14">
         <f>2482-96-2964-664</f>
         <v>-1242</v>
       </c>
-      <c r="M63" s="14">
+      <c r="M64" s="14">
         <f>-1530-116+2037-48</f>
         <v>343</v>
       </c>
-      <c r="N63" s="14">
+      <c r="N64" s="14">
         <f>1818+90-2385+197</f>
         <v>-280</v>
       </c>
-      <c r="O63" s="14">
+      <c r="O64" s="14">
         <f>-3762-35+4839+617</f>
         <v>1659</v>
       </c>
-      <c r="P63" s="14">
+      <c r="P64" s="14">
         <f>3088-125-3791-452</f>
         <v>-1280</v>
       </c>
-      <c r="Q63" s="14">
+      <c r="Q64" s="14">
         <f>-2470-147+2281-156</f>
         <v>-492</v>
       </c>
-      <c r="R63" s="14">
+      <c r="R64" s="14">
         <f>3004+226-3051-427</f>
         <v>-248</v>
       </c>
-      <c r="S63" s="14">
+      <c r="S64" s="14">
         <f>-4004+89+4279+1039</f>
         <v>1403</v>
       </c>
-      <c r="T63" s="2">
+      <c r="T64" s="2">
         <v>-942</v>
       </c>
-      <c r="U63" s="1"/>
-      <c r="V63" s="14"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
-      <c r="AB63" s="2">
+      <c r="U64" s="14">
+        <f>-2365-1014+1834+380</f>
+        <v>-1165</v>
+      </c>
+      <c r="W64" s="12"/>
+      <c r="X64" s="12"/>
+      <c r="Y64" s="12"/>
+      <c r="AB64" s="14">
         <f>-446+306-40-136</f>
         <v>-316</v>
       </c>
-      <c r="AC63" s="2">
+      <c r="AC64" s="14">
         <f>-10-1537+1510-372</f>
         <v>-409</v>
       </c>
-      <c r="AD63" s="14">
-        <f t="shared" si="105"/>
+      <c r="AD64" s="14">
+        <f t="shared" si="115"/>
         <v>356</v>
       </c>
-      <c r="AE63" s="14">
-        <f t="shared" si="106"/>
+      <c r="AE64" s="14">
+        <f t="shared" si="116"/>
         <v>480</v>
       </c>
-      <c r="AF63" s="2">
+      <c r="AF64" s="14">
         <v>-617</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C64" s="1" t="s">
+      <c r="AG64" s="15"/>
+    </row>
+    <row r="65" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D64" s="12">
-        <f t="shared" ref="D64:O64" si="107">SUM(D56:D63)</f>
+      <c r="D65" s="12">
+        <f t="shared" ref="D65:O65" si="117">SUM(D57:D64)</f>
         <v>-696</v>
       </c>
-      <c r="E64" s="12">
-        <f t="shared" si="107"/>
+      <c r="E65" s="12">
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="F64" s="12">
-        <f t="shared" si="107"/>
+      <c r="F65" s="12">
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="G64" s="12">
-        <f t="shared" si="107"/>
+      <c r="G65" s="12">
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="H64" s="12">
-        <f t="shared" si="107"/>
+      <c r="H65" s="12">
+        <f t="shared" si="117"/>
         <v>206</v>
       </c>
-      <c r="I64" s="12">
-        <f t="shared" si="107"/>
+      <c r="I65" s="12">
+        <f t="shared" si="117"/>
         <v>338</v>
       </c>
-      <c r="J64" s="12">
-        <f t="shared" si="107"/>
+      <c r="J65" s="12">
+        <f t="shared" si="117"/>
         <v>-302</v>
       </c>
-      <c r="K64" s="12">
-        <f t="shared" si="107"/>
+      <c r="K65" s="12">
+        <f t="shared" si="117"/>
         <v>1634</v>
       </c>
-      <c r="L64" s="12">
-        <f t="shared" si="107"/>
+      <c r="L65" s="12">
+        <f t="shared" si="117"/>
         <v>-903</v>
       </c>
-      <c r="M64" s="12">
-        <f t="shared" si="107"/>
+      <c r="M65" s="12">
+        <f t="shared" si="117"/>
         <v>665</v>
       </c>
-      <c r="N64" s="12">
-        <f t="shared" si="107"/>
+      <c r="N65" s="12">
+        <f t="shared" si="117"/>
         <v>111</v>
       </c>
-      <c r="O64" s="12">
-        <f t="shared" si="107"/>
+      <c r="O65" s="12">
+        <f t="shared" si="117"/>
         <v>2155</v>
       </c>
-      <c r="P64" s="12">
-        <f>SUM(P56:P63)</f>
+      <c r="P65" s="12">
+        <f>SUM(P57:P64)</f>
         <v>-882</v>
       </c>
-      <c r="Q64" s="12">
-        <f>SUM(Q56:Q63)</f>
+      <c r="Q65" s="12">
+        <f>SUM(Q57:Q64)</f>
         <v>-111</v>
       </c>
-      <c r="R64" s="12">
-        <f>SUM(R56:R63)</f>
+      <c r="R65" s="12">
+        <f>SUM(R57:R64)</f>
         <v>220</v>
       </c>
-      <c r="S64" s="12">
-        <f>SUM(S56:S63)</f>
+      <c r="S65" s="12">
+        <f>SUM(S57:S64)</f>
         <v>1976</v>
       </c>
-      <c r="T64" s="12">
-        <f>SUM(T56:T63)</f>
+      <c r="T65" s="12">
+        <f>SUM(T57:T64)</f>
         <v>-483</v>
       </c>
-      <c r="U64" s="1"/>
-      <c r="V64" s="14"/>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
-      <c r="Z64" s="1">
-        <f t="shared" ref="Z64" si="108">SUM(Z56:Z63)</f>
+      <c r="U65" s="12">
+        <f>SUM(U57:U64)</f>
+        <v>-726</v>
+      </c>
+      <c r="W65" s="12"/>
+      <c r="X65" s="12"/>
+      <c r="Y65" s="12"/>
+      <c r="Z65" s="12">
+        <f t="shared" ref="Z65" si="118">SUM(Z57:Z64)</f>
         <v>0</v>
       </c>
-      <c r="AA64" s="1">
-        <f t="shared" ref="AA64" si="109">SUM(AA56:AA63)</f>
+      <c r="AA65" s="12">
+        <f t="shared" ref="AA65" si="119">SUM(AA57:AA64)</f>
         <v>0</v>
       </c>
-      <c r="AB64" s="1">
-        <f t="shared" ref="AB64" si="110">SUM(AB56:AB63)</f>
+      <c r="AB65" s="12">
+        <f t="shared" ref="AB65" si="120">SUM(AB57:AB64)</f>
         <v>1098</v>
       </c>
-      <c r="AC64" s="1">
-        <f t="shared" ref="AC64" si="111">SUM(AC56:AC63)</f>
+      <c r="AC65" s="12">
+        <f t="shared" ref="AC65" si="121">SUM(AC57:AC64)</f>
         <v>1031</v>
       </c>
-      <c r="AD64" s="1">
-        <f t="shared" ref="AD64" si="112">SUM(AD56:AD63)</f>
+      <c r="AD65" s="12">
+        <f t="shared" ref="AD65" si="122">SUM(AD57:AD64)</f>
         <v>1876</v>
       </c>
-      <c r="AE64" s="1">
-        <f t="shared" ref="AE64:AF64" si="113">SUM(AE56:AE63)</f>
+      <c r="AE65" s="12">
+        <f t="shared" ref="AE65:AF65" si="123">SUM(AE57:AE64)</f>
         <v>2028</v>
       </c>
-      <c r="AF64" s="1">
-        <f t="shared" si="113"/>
+      <c r="AF65" s="12">
+        <f t="shared" si="123"/>
         <v>1203</v>
       </c>
-    </row>
-    <row r="65" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C65" s="1"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="12"/>
-      <c r="N65" s="12"/>
-      <c r="O65" s="12"/>
-      <c r="P65" s="12"/>
-      <c r="Q65" s="12"/>
-      <c r="R65" s="12"/>
-      <c r="S65" s="1"/>
-      <c r="T65" s="1"/>
-      <c r="U65" s="1"/>
-      <c r="V65" s="14"/>
-      <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
-      <c r="AA65" s="1"/>
-    </row>
-    <row r="66" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C66" s="2" t="s">
+      <c r="AG65" s="15"/>
+    </row>
+    <row r="66" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
+      <c r="P66" s="12"/>
+      <c r="Q66" s="12"/>
+      <c r="R66" s="12"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="12"/>
+      <c r="W66" s="12"/>
+      <c r="X66" s="12"/>
+      <c r="Y66" s="12"/>
+      <c r="Z66" s="12"/>
+      <c r="AA66" s="12"/>
+      <c r="AG66" s="15"/>
+    </row>
+    <row r="67" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D66" s="14">
+      <c r="D67" s="14">
         <v>-68</v>
       </c>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14">
+      <c r="H67" s="14">
         <v>-73</v>
       </c>
-      <c r="I66" s="14">
+      <c r="I67" s="14">
         <v>-108</v>
       </c>
-      <c r="J66" s="14">
+      <c r="J67" s="14">
         <v>-41</v>
       </c>
-      <c r="K66" s="14">
+      <c r="K67" s="14">
         <v>-100</v>
       </c>
-      <c r="L66" s="14">
+      <c r="L67" s="14">
         <v>-82</v>
       </c>
-      <c r="M66" s="14">
+      <c r="M67" s="14">
         <v>-112</v>
       </c>
-      <c r="N66" s="14">
+      <c r="N67" s="14">
         <v>-89</v>
       </c>
-      <c r="O66" s="14">
+      <c r="O67" s="14">
         <v>-144</v>
       </c>
-      <c r="P66" s="14">
+      <c r="P67" s="14">
         <v>-103</v>
       </c>
-      <c r="Q66" s="14">
+      <c r="Q67" s="14">
         <v>-108</v>
       </c>
-      <c r="R66" s="14">
+      <c r="R67" s="14">
         <v>-93</v>
       </c>
-      <c r="S66" s="2">
+      <c r="S67" s="2">
         <v>-127</v>
       </c>
-      <c r="T66" s="2">
+      <c r="T67" s="2">
         <v>-110</v>
       </c>
-      <c r="U66" s="1"/>
-      <c r="V66" s="14"/>
-      <c r="W66" s="1"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="1"/>
-      <c r="Z66" s="1"/>
-      <c r="AA66" s="1"/>
-      <c r="AB66" s="2">
+      <c r="U67" s="14">
+        <v>-122</v>
+      </c>
+      <c r="W67" s="12"/>
+      <c r="X67" s="12"/>
+      <c r="Y67" s="12"/>
+      <c r="Z67" s="12"/>
+      <c r="AA67" s="12"/>
+      <c r="AB67" s="14">
         <v>-329</v>
       </c>
-      <c r="AC66" s="2">
+      <c r="AC67" s="14">
         <f>-119-397</f>
         <v>-516</v>
       </c>
-      <c r="AD66" s="14">
-        <f>SUM(H66:K66)</f>
-        <v>-322</v>
-      </c>
-      <c r="AE66" s="14">
-        <f>SUM(L66:O66)</f>
-        <v>-427</v>
-      </c>
-      <c r="AF66" s="2">
-        <v>-431</v>
-      </c>
-    </row>
-    <row r="67" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C67" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D67" s="14">
-        <v>1</v>
-      </c>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14">
-        <v>0</v>
-      </c>
-      <c r="I67" s="14">
-        <v>1</v>
-      </c>
-      <c r="J67" s="14">
-        <v>0</v>
-      </c>
-      <c r="K67" s="14">
-        <v>1</v>
-      </c>
-      <c r="L67" s="14">
-        <v>2</v>
-      </c>
-      <c r="M67" s="14">
-        <v>1</v>
-      </c>
-      <c r="N67" s="14">
-        <v>2</v>
-      </c>
-      <c r="O67" s="14">
-        <v>0</v>
-      </c>
-      <c r="P67" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="14">
-        <v>3</v>
-      </c>
-      <c r="R67" s="14">
-        <v>9</v>
-      </c>
-      <c r="S67" s="2">
-        <v>1</v>
-      </c>
-      <c r="T67" s="2">
-        <v>63</v>
-      </c>
-      <c r="U67" s="1"/>
-      <c r="V67" s="14"/>
-      <c r="W67" s="1"/>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
-      <c r="AA67" s="1"/>
-      <c r="AB67" s="2">
-        <v>56</v>
-      </c>
-      <c r="AC67" s="2">
-        <v>76</v>
-      </c>
       <c r="AD67" s="14">
         <f>SUM(H67:K67)</f>
-        <v>2</v>
+        <v>-322</v>
       </c>
       <c r="AE67" s="14">
         <f>SUM(L67:O67)</f>
+        <v>-427</v>
+      </c>
+      <c r="AF67" s="14">
+        <v>-431</v>
+      </c>
+      <c r="AG67" s="15"/>
+    </row>
+    <row r="68" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" s="14">
+        <v>1</v>
+      </c>
+      <c r="H68" s="14">
+        <v>0</v>
+      </c>
+      <c r="I68" s="14">
+        <v>1</v>
+      </c>
+      <c r="J68" s="14">
+        <v>0</v>
+      </c>
+      <c r="K68" s="14">
+        <v>1</v>
+      </c>
+      <c r="L68" s="14">
+        <v>2</v>
+      </c>
+      <c r="M68" s="14">
+        <v>1</v>
+      </c>
+      <c r="N68" s="14">
+        <v>2</v>
+      </c>
+      <c r="O68" s="14">
+        <v>0</v>
+      </c>
+      <c r="P68" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="14">
+        <v>3</v>
+      </c>
+      <c r="R68" s="14">
+        <v>9</v>
+      </c>
+      <c r="S68" s="2">
+        <v>1</v>
+      </c>
+      <c r="T68" s="2">
+        <v>63</v>
+      </c>
+      <c r="U68" s="14">
+        <v>0</v>
+      </c>
+      <c r="W68" s="12"/>
+      <c r="X68" s="12"/>
+      <c r="Y68" s="12"/>
+      <c r="Z68" s="12"/>
+      <c r="AA68" s="12"/>
+      <c r="AB68" s="14">
+        <v>56</v>
+      </c>
+      <c r="AC68" s="14">
+        <v>76</v>
+      </c>
+      <c r="AD68" s="14">
+        <f>SUM(H68:K68)</f>
+        <v>2</v>
+      </c>
+      <c r="AE68" s="14">
+        <f>SUM(L68:O68)</f>
         <v>5</v>
       </c>
-      <c r="AF67" s="2">
+      <c r="AF68" s="14">
         <v>13</v>
       </c>
-    </row>
-    <row r="68" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C68" s="1" t="s">
+      <c r="AG68" s="15"/>
+    </row>
+    <row r="69" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D68" s="12">
-        <f t="shared" ref="D68:O68" si="114">SUM(D66:D67)</f>
+      <c r="D69" s="12">
+        <f t="shared" ref="D69:O69" si="124">SUM(D67:D68)</f>
         <v>-67</v>
       </c>
-      <c r="E68" s="12">
-        <f t="shared" si="114"/>
+      <c r="E69" s="12">
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
-      <c r="F68" s="12">
-        <f t="shared" si="114"/>
+      <c r="F69" s="12">
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
-      <c r="G68" s="12">
-        <f t="shared" si="114"/>
+      <c r="G69" s="12">
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
-      <c r="H68" s="12">
-        <f t="shared" si="114"/>
+      <c r="H69" s="12">
+        <f t="shared" si="124"/>
         <v>-73</v>
       </c>
-      <c r="I68" s="12">
-        <f t="shared" si="114"/>
+      <c r="I69" s="12">
+        <f t="shared" si="124"/>
         <v>-107</v>
       </c>
-      <c r="J68" s="12">
-        <f t="shared" si="114"/>
+      <c r="J69" s="12">
+        <f t="shared" si="124"/>
         <v>-41</v>
       </c>
-      <c r="K68" s="12">
-        <f t="shared" si="114"/>
+      <c r="K69" s="12">
+        <f t="shared" si="124"/>
         <v>-99</v>
       </c>
-      <c r="L68" s="12">
-        <f t="shared" si="114"/>
+      <c r="L69" s="12">
+        <f t="shared" si="124"/>
         <v>-80</v>
       </c>
-      <c r="M68" s="12">
-        <f t="shared" si="114"/>
+      <c r="M69" s="12">
+        <f t="shared" si="124"/>
         <v>-111</v>
       </c>
-      <c r="N68" s="12">
-        <f t="shared" si="114"/>
+      <c r="N69" s="12">
+        <f t="shared" si="124"/>
         <v>-87</v>
       </c>
-      <c r="O68" s="12">
-        <f t="shared" si="114"/>
+      <c r="O69" s="12">
+        <f t="shared" si="124"/>
         <v>-144</v>
       </c>
-      <c r="P68" s="12">
-        <f>SUM(P66:P67)</f>
+      <c r="P69" s="12">
+        <f>SUM(P67:P68)</f>
         <v>-103</v>
       </c>
-      <c r="Q68" s="12">
-        <f>SUM(Q66:Q67)</f>
+      <c r="Q69" s="12">
+        <f>SUM(Q67:Q68)</f>
         <v>-105</v>
       </c>
-      <c r="R68" s="12">
-        <f>SUM(R66:R67)</f>
+      <c r="R69" s="12">
+        <f>SUM(R67:R68)</f>
         <v>-84</v>
       </c>
-      <c r="S68" s="12">
-        <f>SUM(S66:S67)</f>
+      <c r="S69" s="12">
+        <f>SUM(S67:S68)</f>
         <v>-126</v>
       </c>
-      <c r="T68" s="12">
-        <f>SUM(T66:T67)</f>
+      <c r="T69" s="12">
+        <f>SUM(T67:T68)</f>
         <v>-47</v>
       </c>
-      <c r="V68" s="14"/>
-      <c r="Z68" s="1">
-        <f t="shared" ref="Z68:AC68" si="115">SUM(Z66:Z67)</f>
+      <c r="U69" s="12">
+        <f>SUM(U67:U68)</f>
+        <v>-122</v>
+      </c>
+      <c r="Z69" s="12">
+        <f t="shared" ref="Z69:AC69" si="125">SUM(Z67:Z68)</f>
         <v>0</v>
       </c>
-      <c r="AA68" s="1">
-        <f t="shared" si="115"/>
+      <c r="AA69" s="12">
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
-      <c r="AB68" s="1">
-        <f t="shared" si="115"/>
+      <c r="AB69" s="12">
+        <f t="shared" si="125"/>
         <v>-273</v>
       </c>
-      <c r="AC68" s="1">
-        <f t="shared" si="115"/>
+      <c r="AC69" s="12">
+        <f t="shared" si="125"/>
         <v>-440</v>
       </c>
-      <c r="AD68" s="1">
-        <f t="shared" ref="AD68" si="116">SUM(AD66:AD67)</f>
+      <c r="AD69" s="12">
+        <f t="shared" ref="AD69" si="126">SUM(AD67:AD68)</f>
         <v>-320</v>
       </c>
-      <c r="AE68" s="1">
-        <f t="shared" ref="AE68:AF68" si="117">SUM(AE66:AE67)</f>
+      <c r="AE69" s="12">
+        <f t="shared" ref="AE69:AF69" si="127">SUM(AE67:AE68)</f>
         <v>-422</v>
       </c>
-      <c r="AF68" s="1">
-        <f t="shared" si="117"/>
+      <c r="AF69" s="12">
+        <f t="shared" si="127"/>
         <v>-418</v>
       </c>
-    </row>
-    <row r="69" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="14"/>
-      <c r="P69" s="14"/>
-      <c r="Q69" s="14"/>
-      <c r="R69" s="14"/>
-      <c r="V69" s="14"/>
-    </row>
-    <row r="70" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C70" s="2" t="s">
+      <c r="AG69" s="15"/>
+    </row>
+    <row r="70" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="2"/>
+      <c r="AG70" s="15"/>
+    </row>
+    <row r="71" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D70" s="14">
+      <c r="D71" s="14">
         <v>0</v>
       </c>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14">
-        <v>0</v>
-      </c>
-      <c r="I70" s="14">
-        <v>-346</v>
-      </c>
-      <c r="J70" s="14">
-        <v>0</v>
-      </c>
-      <c r="K70" s="14">
-        <v>-347</v>
-      </c>
-      <c r="L70" s="14">
-        <v>0</v>
-      </c>
-      <c r="M70" s="14">
-        <v>-391</v>
-      </c>
-      <c r="N70" s="14">
-        <v>0</v>
-      </c>
-      <c r="O70" s="14">
-        <v>-391</v>
-      </c>
-      <c r="P70" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="14">
-        <v>-390</v>
-      </c>
-      <c r="R70" s="14">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
-        <v>-390</v>
-      </c>
-      <c r="T70" s="2">
-        <v>0</v>
-      </c>
-      <c r="V70" s="14"/>
-      <c r="AB70" s="2">
-        <v>-555</v>
-      </c>
-      <c r="AC70" s="2">
-        <v>-612</v>
-      </c>
-      <c r="AD70" s="14">
-        <f>SUM(H70:K70)</f>
-        <v>-693</v>
-      </c>
-      <c r="AE70" s="14">
-        <f>SUM(L70:O70)</f>
-        <v>-782</v>
-      </c>
-      <c r="AF70" s="2">
-        <v>-780</v>
-      </c>
-    </row>
-    <row r="71" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C71" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D71" s="14">
-        <v>-81</v>
-      </c>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
       <c r="H71" s="14">
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <v>6</v>
+        <v>-346</v>
       </c>
       <c r="J71" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K71" s="14">
-        <v>10</v>
+        <v>-347</v>
       </c>
       <c r="L71" s="14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M71" s="14">
-        <v>9</v>
+        <v>-391</v>
       </c>
       <c r="N71" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O71" s="14">
-        <v>-6</v>
+        <v>-391</v>
       </c>
       <c r="P71" s="14">
-        <v>-65</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="14">
-        <v>9</v>
+        <v>-390</v>
       </c>
       <c r="R71" s="14">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="S71" s="2">
-        <v>-3</v>
+        <v>-390</v>
       </c>
       <c r="T71" s="2">
-        <v>-63</v>
-      </c>
-      <c r="V71" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="U71" s="14">
+        <v>-418</v>
+      </c>
+      <c r="AB71" s="14">
+        <v>-555</v>
+      </c>
+      <c r="AC71" s="14">
+        <v>-612</v>
+      </c>
       <c r="AD71" s="14">
         <f>SUM(H71:K71)</f>
-        <v>26</v>
+        <v>-693</v>
       </c>
       <c r="AE71" s="14">
         <f>SUM(L71:O71)</f>
-        <v>22</v>
-      </c>
-      <c r="AF71" s="2">
-        <v>-89</v>
-      </c>
-    </row>
-    <row r="72" spans="3:32" x14ac:dyDescent="0.25">
+        <v>-782</v>
+      </c>
+      <c r="AF71" s="14">
+        <v>-780</v>
+      </c>
+      <c r="AG71" s="15"/>
+    </row>
+    <row r="72" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="4"/>
       <c r="C72" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D72" s="14">
-        <v>-78</v>
-      </c>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
+        <v>-81</v>
+      </c>
       <c r="H72" s="14">
-        <v>-82</v>
+        <v>0</v>
       </c>
       <c r="I72" s="14">
-        <v>-87</v>
+        <v>6</v>
       </c>
       <c r="J72" s="14">
-        <v>-93</v>
+        <v>10</v>
       </c>
       <c r="K72" s="14">
-        <v>-100</v>
+        <v>10</v>
       </c>
       <c r="L72" s="14">
-        <v>-95</v>
+        <v>9</v>
       </c>
       <c r="M72" s="14">
-        <v>-94</v>
+        <v>9</v>
       </c>
       <c r="N72" s="14">
-        <v>-100</v>
+        <v>10</v>
       </c>
       <c r="O72" s="14">
-        <v>-109</v>
+        <v>-6</v>
       </c>
       <c r="P72" s="14">
-        <v>-103</v>
+        <v>-65</v>
       </c>
       <c r="Q72" s="14">
-        <v>-104</v>
+        <v>9</v>
       </c>
       <c r="R72" s="14">
-        <v>-109</v>
+        <v>-30</v>
       </c>
       <c r="S72" s="2">
-        <v>-108</v>
+        <v>-3</v>
       </c>
       <c r="T72" s="2">
-        <v>-109</v>
-      </c>
-      <c r="V72" s="14"/>
+        <v>-63</v>
+      </c>
+      <c r="U72" s="14">
+        <v>7</v>
+      </c>
       <c r="AD72" s="14">
         <f>SUM(H72:K72)</f>
-        <v>-362</v>
+        <v>26</v>
       </c>
       <c r="AE72" s="14">
         <f>SUM(L72:O72)</f>
-        <v>-398</v>
-      </c>
-      <c r="AF72" s="2">
-        <v>-424</v>
-      </c>
-    </row>
-    <row r="73" spans="3:32" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="AF72" s="14">
+        <v>-89</v>
+      </c>
+      <c r="AG72" s="15"/>
+    </row>
+    <row r="73" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="4"/>
       <c r="C73" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D73" s="14">
-        <v>267</v>
-      </c>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
+        <v>-78</v>
+      </c>
       <c r="H73" s="14">
-        <v>-97</v>
+        <v>-82</v>
       </c>
       <c r="I73" s="14">
-        <v>317</v>
+        <v>-87</v>
       </c>
       <c r="J73" s="14">
-        <v>317</v>
+        <v>-93</v>
       </c>
       <c r="K73" s="14">
-        <v>-592</v>
+        <v>-100</v>
       </c>
       <c r="L73" s="14">
-        <v>306</v>
+        <v>-95</v>
       </c>
       <c r="M73" s="14">
-        <v>314</v>
+        <v>-94</v>
       </c>
       <c r="N73" s="14">
-        <v>-153</v>
+        <v>-100</v>
       </c>
       <c r="O73" s="14">
-        <v>-540</v>
+        <v>-109</v>
       </c>
       <c r="P73" s="14">
-        <v>4</v>
+        <v>-103</v>
       </c>
       <c r="Q73" s="14">
-        <v>880</v>
+        <v>-104</v>
       </c>
       <c r="R73" s="14">
-        <v>-158</v>
+        <v>-109</v>
       </c>
       <c r="S73" s="2">
-        <v>-721</v>
+        <v>-108</v>
       </c>
       <c r="T73" s="2">
-        <v>15</v>
-      </c>
-      <c r="V73" s="14"/>
+        <v>-109</v>
+      </c>
+      <c r="U73" s="14">
+        <v>-105</v>
+      </c>
       <c r="AD73" s="14">
         <f>SUM(H73:K73)</f>
-        <v>-55</v>
+        <v>-362</v>
       </c>
       <c r="AE73" s="14">
         <f>SUM(L73:O73)</f>
+        <v>-398</v>
+      </c>
+      <c r="AF73" s="14">
+        <v>-424</v>
+      </c>
+      <c r="AG73" s="15"/>
+    </row>
+    <row r="74" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" s="14">
+        <v>267</v>
+      </c>
+      <c r="H74" s="14">
+        <v>-97</v>
+      </c>
+      <c r="I74" s="14">
+        <v>317</v>
+      </c>
+      <c r="J74" s="14">
+        <v>317</v>
+      </c>
+      <c r="K74" s="14">
+        <v>-592</v>
+      </c>
+      <c r="L74" s="14">
+        <v>306</v>
+      </c>
+      <c r="M74" s="14">
+        <v>314</v>
+      </c>
+      <c r="N74" s="14">
+        <v>-153</v>
+      </c>
+      <c r="O74" s="14">
+        <v>-540</v>
+      </c>
+      <c r="P74" s="14">
+        <v>4</v>
+      </c>
+      <c r="Q74" s="14">
+        <v>880</v>
+      </c>
+      <c r="R74" s="14">
+        <v>-158</v>
+      </c>
+      <c r="S74" s="2">
+        <v>-721</v>
+      </c>
+      <c r="T74" s="2">
+        <v>15</v>
+      </c>
+      <c r="U74" s="14">
+        <v>1264</v>
+      </c>
+      <c r="AD74" s="14">
+        <f>SUM(H74:K74)</f>
+        <v>-55</v>
+      </c>
+      <c r="AE74" s="14">
+        <f>SUM(L74:O74)</f>
         <v>-73</v>
       </c>
-      <c r="AF73" s="2">
+      <c r="AF74" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="74" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C74" s="1" t="s">
+      <c r="AG74" s="15"/>
+    </row>
+    <row r="75" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="15"/>
+      <c r="C75" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D74" s="12">
-        <f t="shared" ref="D74:O74" si="118">SUM(D70:D73)</f>
+      <c r="D75" s="12">
+        <f t="shared" ref="D75:O75" si="128">SUM(D71:D74)</f>
         <v>108</v>
       </c>
-      <c r="E74" s="12">
-        <f t="shared" si="118"/>
+      <c r="E75" s="12">
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
-      <c r="F74" s="12">
-        <f t="shared" si="118"/>
+      <c r="F75" s="12">
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
-      <c r="G74" s="12">
-        <f t="shared" si="118"/>
+      <c r="G75" s="12">
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
-      <c r="H74" s="12">
-        <f t="shared" si="118"/>
+      <c r="H75" s="12">
+        <f t="shared" si="128"/>
         <v>-179</v>
       </c>
-      <c r="I74" s="12">
-        <f t="shared" si="118"/>
+      <c r="I75" s="12">
+        <f t="shared" si="128"/>
         <v>-110</v>
       </c>
-      <c r="J74" s="12">
-        <f t="shared" si="118"/>
+      <c r="J75" s="12">
+        <f t="shared" si="128"/>
         <v>234</v>
       </c>
-      <c r="K74" s="12">
-        <f t="shared" si="118"/>
+      <c r="K75" s="12">
+        <f t="shared" si="128"/>
         <v>-1029</v>
       </c>
-      <c r="L74" s="12">
-        <f t="shared" si="118"/>
+      <c r="L75" s="12">
+        <f t="shared" si="128"/>
         <v>220</v>
       </c>
-      <c r="M74" s="12">
-        <f t="shared" si="118"/>
+      <c r="M75" s="12">
+        <f t="shared" si="128"/>
         <v>-162</v>
       </c>
-      <c r="N74" s="12">
-        <f t="shared" si="118"/>
+      <c r="N75" s="12">
+        <f t="shared" si="128"/>
         <v>-243</v>
       </c>
-      <c r="O74" s="12">
-        <f t="shared" si="118"/>
+      <c r="O75" s="12">
+        <f t="shared" si="128"/>
         <v>-1046</v>
       </c>
-      <c r="P74" s="12">
-        <f>SUM(P70:P73)</f>
+      <c r="P75" s="12">
+        <f>SUM(P71:P74)</f>
         <v>-164</v>
       </c>
-      <c r="Q74" s="12">
-        <f>SUM(Q70:Q73)</f>
+      <c r="Q75" s="12">
+        <f>SUM(Q71:Q74)</f>
         <v>395</v>
       </c>
-      <c r="R74" s="12">
-        <f>SUM(R70:R73)</f>
+      <c r="R75" s="12">
+        <f>SUM(R71:R74)</f>
         <v>-297</v>
       </c>
-      <c r="S74" s="12">
-        <f>SUM(S70:S73)</f>
+      <c r="S75" s="12">
+        <f>SUM(S71:S74)</f>
         <v>-1222</v>
       </c>
-      <c r="T74" s="12">
-        <f>SUM(T70:T73)</f>
+      <c r="T75" s="12">
+        <f>SUM(T71:T74)</f>
         <v>-157</v>
       </c>
-      <c r="V74" s="14"/>
-      <c r="Z74" s="1">
-        <f t="shared" ref="Z74:AA74" si="119">SUM(Z70:Z73)</f>
+      <c r="U75" s="12">
+        <f>SUM(U71:U74)</f>
+        <v>748</v>
+      </c>
+      <c r="Z75" s="12">
+        <f t="shared" ref="Z75:AA75" si="129">SUM(Z71:Z74)</f>
         <v>0</v>
       </c>
-      <c r="AA74" s="1">
-        <f t="shared" si="119"/>
+      <c r="AA75" s="12">
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
-      <c r="AB74" s="1">
+      <c r="AB75" s="12">
         <v>-870</v>
       </c>
-      <c r="AC74" s="1">
+      <c r="AC75" s="12">
         <v>-989</v>
       </c>
-      <c r="AD74" s="1">
-        <f t="shared" ref="AD74" si="120">SUM(AD70:AD73)</f>
+      <c r="AD75" s="12">
+        <f t="shared" ref="AD75" si="130">SUM(AD71:AD74)</f>
         <v>-1084</v>
       </c>
-      <c r="AE74" s="1">
-        <f t="shared" ref="AE74:AF74" si="121">SUM(AE70:AE73)</f>
+      <c r="AE75" s="12">
+        <f t="shared" ref="AE75:AF75" si="131">SUM(AE71:AE74)</f>
         <v>-1231</v>
       </c>
-      <c r="AF74" s="1">
-        <f t="shared" si="121"/>
+      <c r="AF75" s="12">
+        <f t="shared" si="131"/>
         <v>-1288</v>
       </c>
-    </row>
-    <row r="75" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
-      <c r="K75" s="14"/>
-      <c r="L75" s="14"/>
-      <c r="M75" s="14"/>
-      <c r="N75" s="14"/>
-      <c r="O75" s="14"/>
-      <c r="P75" s="14"/>
-      <c r="Q75" s="14"/>
-      <c r="R75" s="14"/>
-      <c r="V75" s="14"/>
-    </row>
-    <row r="76" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C76" s="2" t="s">
+      <c r="AG75" s="15"/>
+    </row>
+    <row r="76" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="2"/>
+      <c r="S76" s="2"/>
+      <c r="T76" s="2"/>
+      <c r="AG76" s="15"/>
+    </row>
+    <row r="77" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D76" s="14">
+      <c r="D77" s="14">
         <v>-92</v>
       </c>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14">
+      <c r="H77" s="14">
         <v>179</v>
       </c>
-      <c r="I76" s="14">
+      <c r="I77" s="14">
         <v>-15</v>
       </c>
-      <c r="J76" s="14">
+      <c r="J77" s="14">
         <v>-36</v>
       </c>
-      <c r="K76" s="14">
+      <c r="K77" s="14">
         <v>62</v>
       </c>
-      <c r="L76" s="14">
+      <c r="L77" s="14">
         <v>6</v>
       </c>
-      <c r="M76" s="14">
+      <c r="M77" s="14">
         <v>-32</v>
       </c>
-      <c r="N76" s="14">
+      <c r="N77" s="14">
         <v>62</v>
       </c>
-      <c r="O76" s="14">
+      <c r="O77" s="14">
         <v>5</v>
       </c>
-      <c r="P76" s="14">
+      <c r="P77" s="14">
         <v>22</v>
       </c>
-      <c r="Q76" s="14">
+      <c r="Q77" s="14">
         <v>10</v>
       </c>
-      <c r="R76" s="14">
+      <c r="R77" s="14">
         <v>2</v>
       </c>
-      <c r="S76" s="2">
+      <c r="S77" s="2">
         <v>58</v>
       </c>
-      <c r="T76" s="2">
+      <c r="T77" s="2">
         <v>-152</v>
       </c>
-      <c r="V76" s="14"/>
-      <c r="AB76" s="2">
+      <c r="U77" s="14">
+        <v>-60</v>
+      </c>
+      <c r="AB77" s="14">
         <v>-205</v>
       </c>
-      <c r="AC76" s="2">
+      <c r="AC77" s="14">
         <v>-31</v>
       </c>
-      <c r="AD76" s="2">
+      <c r="AD77" s="14">
         <v>190</v>
       </c>
-      <c r="AE76" s="2">
+      <c r="AE77" s="14">
         <v>41</v>
       </c>
-      <c r="AF76" s="2">
+      <c r="AF77" s="14">
         <v>92</v>
       </c>
-    </row>
-    <row r="77" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
-      <c r="N77" s="14"/>
-      <c r="O77" s="14"/>
-      <c r="P77" s="14"/>
-      <c r="Q77" s="14"/>
-      <c r="R77" s="14"/>
-      <c r="V77" s="14"/>
-    </row>
-    <row r="78" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C78" s="2" t="s">
+      <c r="AG77" s="15"/>
+    </row>
+    <row r="78" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="2"/>
+      <c r="S78" s="2"/>
+      <c r="T78" s="2"/>
+      <c r="AG78" s="15"/>
+    </row>
+    <row r="79" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D78" s="14">
-        <f t="shared" ref="D78:O78" si="122">D64+D68+D74+D76</f>
+      <c r="D79" s="14">
+        <f t="shared" ref="D79:O79" si="132">D65+D69+D75+D77</f>
         <v>-747</v>
       </c>
-      <c r="E78" s="14">
-        <f t="shared" si="122"/>
+      <c r="E79" s="14">
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="F78" s="14">
-        <f t="shared" si="122"/>
+      <c r="F79" s="14">
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="G78" s="14">
-        <f t="shared" si="122"/>
+      <c r="G79" s="14">
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
-      <c r="H78" s="14">
-        <f t="shared" si="122"/>
+      <c r="H79" s="14">
+        <f t="shared" si="132"/>
         <v>133</v>
       </c>
-      <c r="I78" s="14">
-        <f t="shared" si="122"/>
+      <c r="I79" s="14">
+        <f t="shared" si="132"/>
         <v>106</v>
       </c>
-      <c r="J78" s="14">
-        <f t="shared" si="122"/>
+      <c r="J79" s="14">
+        <f t="shared" si="132"/>
         <v>-145</v>
       </c>
-      <c r="K78" s="14">
-        <f t="shared" si="122"/>
+      <c r="K79" s="14">
+        <f t="shared" si="132"/>
         <v>568</v>
       </c>
-      <c r="L78" s="14">
-        <f t="shared" si="122"/>
+      <c r="L79" s="14">
+        <f t="shared" si="132"/>
         <v>-757</v>
       </c>
-      <c r="M78" s="14">
-        <f t="shared" si="122"/>
+      <c r="M79" s="14">
+        <f t="shared" si="132"/>
         <v>360</v>
       </c>
-      <c r="N78" s="14">
-        <f t="shared" si="122"/>
+      <c r="N79" s="14">
+        <f t="shared" si="132"/>
         <v>-157</v>
       </c>
-      <c r="O78" s="14">
-        <f t="shared" si="122"/>
+      <c r="O79" s="14">
+        <f t="shared" si="132"/>
         <v>970</v>
       </c>
-      <c r="P78" s="14">
-        <f>P64+P68+P74+P76</f>
+      <c r="P79" s="14">
+        <f>P65+P69+P75+P77</f>
         <v>-1127</v>
       </c>
-      <c r="Q78" s="14">
-        <f>Q64+Q68+Q74+Q76</f>
+      <c r="Q79" s="14">
+        <f>Q65+Q69+Q75+Q77</f>
         <v>189</v>
       </c>
-      <c r="R78" s="14">
-        <f>R64+R68+R74+R76</f>
+      <c r="R79" s="14">
+        <f>R65+R69+R75+R77</f>
         <v>-159</v>
       </c>
-      <c r="S78" s="14">
-        <f>S64+S68+S74+S76</f>
+      <c r="S79" s="14">
+        <f>S65+S69+S75+S77</f>
         <v>686</v>
       </c>
-      <c r="T78" s="14">
-        <f>T64+T68+T74+T76</f>
+      <c r="T79" s="14">
+        <f>T65+T69+T75+T77</f>
         <v>-839</v>
       </c>
-      <c r="V78" s="14"/>
-      <c r="Z78" s="14">
-        <f t="shared" ref="Z78:AC78" si="123">Z64+Z68+Z74+Z76</f>
+      <c r="U79" s="14">
+        <f>U65+U69+U75+U77</f>
+        <v>-160</v>
+      </c>
+      <c r="Z79" s="14">
+        <f t="shared" ref="Z79:AC79" si="133">Z65+Z69+Z75+Z77</f>
         <v>0</v>
       </c>
-      <c r="AA78" s="14">
-        <f t="shared" si="123"/>
+      <c r="AA79" s="14">
+        <f t="shared" si="133"/>
         <v>0</v>
       </c>
-      <c r="AB78" s="14">
-        <f t="shared" si="123"/>
+      <c r="AB79" s="14">
+        <f t="shared" si="133"/>
         <v>-250</v>
       </c>
-      <c r="AC78" s="14">
-        <f t="shared" si="123"/>
+      <c r="AC79" s="14">
+        <f t="shared" si="133"/>
         <v>-429</v>
       </c>
-      <c r="AD78" s="14">
-        <f>AD64+AD68+AD74+AD76</f>
+      <c r="AD79" s="14">
+        <f>AD65+AD69+AD75+AD77</f>
         <v>662</v>
       </c>
-      <c r="AE78" s="14">
-        <f t="shared" ref="AE78:AF78" si="124">AE64+AE68+AE74+AE76</f>
+      <c r="AE79" s="14">
+        <f t="shared" ref="AE79:AF79" si="134">AE65+AE69+AE75+AE77</f>
         <v>416</v>
       </c>
-      <c r="AF78" s="14">
-        <f t="shared" si="124"/>
+      <c r="AF79" s="14">
+        <f t="shared" si="134"/>
         <v>-411</v>
       </c>
-    </row>
-    <row r="79" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="14"/>
-      <c r="O79" s="14"/>
-      <c r="P79" s="14"/>
-      <c r="Q79" s="14"/>
-      <c r="R79" s="14"/>
-      <c r="S79" s="14"/>
-      <c r="T79" s="14"/>
-      <c r="V79" s="14"/>
-      <c r="Z79" s="14"/>
-      <c r="AA79" s="14"/>
-      <c r="AB79" s="14"/>
-      <c r="AC79" s="14"/>
-      <c r="AD79" s="14"/>
-      <c r="AE79" s="14"/>
-      <c r="AF79" s="14"/>
-    </row>
-    <row r="80" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C80" s="2" t="s">
+      <c r="AG79" s="15"/>
+    </row>
+    <row r="80" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="2"/>
+      <c r="AG80" s="15"/>
+    </row>
+    <row r="81" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D80" s="14">
-        <f t="shared" ref="D80:O80" si="125">D64+D66</f>
+      <c r="D81" s="14">
+        <f t="shared" ref="D81:O81" si="135">D65+D67</f>
         <v>-764</v>
       </c>
-      <c r="E80" s="14">
-        <f t="shared" si="125"/>
+      <c r="E81" s="14">
+        <f t="shared" si="135"/>
         <v>0</v>
       </c>
-      <c r="F80" s="14">
-        <f t="shared" si="125"/>
+      <c r="F81" s="14">
+        <f t="shared" si="135"/>
         <v>0</v>
       </c>
-      <c r="G80" s="14">
-        <f t="shared" si="125"/>
+      <c r="G81" s="14">
+        <f t="shared" si="135"/>
         <v>0</v>
       </c>
-      <c r="H80" s="14">
-        <f t="shared" si="125"/>
+      <c r="H81" s="14">
+        <f t="shared" si="135"/>
         <v>133</v>
       </c>
-      <c r="I80" s="14">
-        <f t="shared" si="125"/>
+      <c r="I81" s="14">
+        <f t="shared" si="135"/>
         <v>230</v>
       </c>
-      <c r="J80" s="14">
-        <f t="shared" si="125"/>
+      <c r="J81" s="14">
+        <f t="shared" si="135"/>
         <v>-343</v>
       </c>
-      <c r="K80" s="14">
-        <f t="shared" si="125"/>
+      <c r="K81" s="14">
+        <f t="shared" si="135"/>
         <v>1534</v>
       </c>
-      <c r="L80" s="14">
-        <f t="shared" si="125"/>
+      <c r="L81" s="14">
+        <f t="shared" si="135"/>
         <v>-985</v>
       </c>
-      <c r="M80" s="14">
-        <f t="shared" si="125"/>
+      <c r="M81" s="14">
+        <f t="shared" si="135"/>
         <v>553</v>
       </c>
-      <c r="N80" s="14">
-        <f t="shared" si="125"/>
+      <c r="N81" s="14">
+        <f t="shared" si="135"/>
         <v>22</v>
       </c>
-      <c r="O80" s="14">
-        <f t="shared" si="125"/>
+      <c r="O81" s="14">
+        <f t="shared" si="135"/>
         <v>2011</v>
       </c>
-      <c r="P80" s="14">
-        <f>P64+P66</f>
+      <c r="P81" s="14">
+        <f>P65+P67</f>
         <v>-985</v>
       </c>
-      <c r="Q80" s="14">
-        <f>Q64+Q66</f>
+      <c r="Q81" s="14">
+        <f>Q65+Q67</f>
         <v>-219</v>
       </c>
-      <c r="R80" s="14">
-        <f>R64+R66</f>
+      <c r="R81" s="14">
+        <f>R65+R67</f>
         <v>127</v>
       </c>
-      <c r="S80" s="14">
-        <f>S64+S66</f>
+      <c r="S81" s="14">
+        <f>S65+S67</f>
         <v>1849</v>
       </c>
-      <c r="T80" s="14">
-        <f>T64+T66</f>
+      <c r="T81" s="14">
+        <f>T65+T67</f>
         <v>-593</v>
       </c>
-      <c r="V80" s="14"/>
-      <c r="Z80" s="14">
-        <f t="shared" ref="Z80:AC80" si="126">Z64+Z66</f>
+      <c r="U81" s="14">
+        <f>U65+U67</f>
+        <v>-848</v>
+      </c>
+      <c r="Z81" s="14">
+        <f t="shared" ref="Z81:AC81" si="136">Z65+Z67</f>
         <v>0</v>
       </c>
-      <c r="AA80" s="14">
-        <f t="shared" si="126"/>
+      <c r="AA81" s="14">
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
-      <c r="AB80" s="14">
-        <f t="shared" si="126"/>
+      <c r="AB81" s="14">
+        <f t="shared" si="136"/>
         <v>769</v>
       </c>
-      <c r="AC80" s="14">
-        <f t="shared" si="126"/>
+      <c r="AC81" s="14">
+        <f t="shared" si="136"/>
         <v>515</v>
       </c>
-      <c r="AD80" s="14">
-        <f t="shared" ref="AD80:AE80" si="127">AD64+AD66</f>
+      <c r="AD81" s="14">
+        <f t="shared" ref="AD81:AE81" si="137">AD65+AD67</f>
         <v>1554</v>
       </c>
-      <c r="AE80" s="14">
-        <f t="shared" si="127"/>
+      <c r="AE81" s="14">
+        <f t="shared" si="137"/>
         <v>1601</v>
       </c>
-      <c r="AF80" s="14">
-        <f t="shared" ref="AF80" si="128">AF64+AF66</f>
+      <c r="AF81" s="14">
+        <f t="shared" ref="AF81" si="138">AF65+AF67</f>
         <v>772</v>
       </c>
+      <c r="AG81" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -7701,12 +8291,14 @@
       <c r="W4" s="14">
         <v>1858</v>
       </c>
-      <c r="X4" s="14"/>
+      <c r="X4" s="14">
+        <v>1801</v>
+      </c>
       <c r="Y4" s="14"/>
       <c r="Z4" s="14"/>
       <c r="AA4" s="47">
         <f>SUM(W4:Z4)</f>
-        <v>1858</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.25">
@@ -7780,12 +8372,14 @@
       <c r="W5" s="14">
         <v>660</v>
       </c>
-      <c r="X5" s="14"/>
+      <c r="X5" s="14">
+        <v>675</v>
+      </c>
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
       <c r="AA5" s="47">
         <f>SUM(W5:Z5)</f>
-        <v>660</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.25">
@@ -7873,12 +8467,12 @@
         <v>9396</v>
       </c>
       <c r="W6" s="12">
-        <f t="shared" ref="W6:AA6" si="2">SUM(W4:W5)</f>
+        <f t="shared" ref="W6" si="2">SUM(W4:W5)</f>
         <v>2518</v>
       </c>
       <c r="X6" s="12">
         <f>SUM(X4:X5)</f>
-        <v>0</v>
+        <v>2476</v>
       </c>
       <c r="Y6" s="12">
         <f t="shared" ref="Y6:Z6" si="3">SUM(Y4:Y5)</f>
@@ -7890,7 +8484,7 @@
       </c>
       <c r="AA6" s="48">
         <f>SUM(AA4:AA5)</f>
-        <v>2518</v>
+        <v>4994</v>
       </c>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
@@ -7968,7 +8562,7 @@
       </c>
       <c r="X7" s="38">
         <f>(X6-S6)/S6</f>
-        <v>-1</v>
+        <v>0.16080637599624942</v>
       </c>
       <c r="Y7" s="38">
         <f>(Y6-T6)/T6</f>
@@ -7980,7 +8574,7 @@
       </c>
       <c r="AA7" s="42">
         <f>(AA6-V6)/V6</f>
-        <v>-0.73201362281822047</v>
+        <v>-0.46849723286504896</v>
       </c>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.25">
@@ -8054,12 +8648,14 @@
       <c r="W8" s="14">
         <v>774</v>
       </c>
-      <c r="X8" s="14"/>
+      <c r="X8" s="14">
+        <v>779</v>
+      </c>
       <c r="Y8" s="14"/>
       <c r="Z8" s="14"/>
       <c r="AA8" s="48">
         <f>SUM(W8:Z8)</f>
-        <v>774</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.25">
@@ -8133,12 +8729,14 @@
       <c r="W9" s="25">
         <v>0.307</v>
       </c>
-      <c r="X9" s="25"/>
+      <c r="X9" s="25">
+        <v>0.315</v>
+      </c>
       <c r="Y9" s="25"/>
       <c r="Z9" s="25"/>
       <c r="AA9" s="43">
         <f>AA8/AA6</f>
-        <v>0.3073868149324861</v>
+        <v>0.31097316780136164</v>
       </c>
     </row>
     <row r="10" spans="2:27" x14ac:dyDescent="0.25">
@@ -8212,12 +8810,14 @@
       <c r="W10" s="14">
         <v>683</v>
       </c>
-      <c r="X10" s="14"/>
+      <c r="X10" s="14">
+        <v>671</v>
+      </c>
       <c r="Y10" s="14"/>
       <c r="Z10" s="14"/>
       <c r="AA10" s="48">
         <f>SUM(W10:Z10)</f>
-        <v>683</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.25">
@@ -8295,7 +8895,7 @@
       </c>
       <c r="X11" s="38">
         <f>(X10-S10)/S10</f>
-        <v>-1</v>
+        <v>6.5079365079365084E-2</v>
       </c>
       <c r="Y11" s="38">
         <f>(Y10-T10)/T10</f>
@@ -8307,7 +8907,7 @@
       </c>
       <c r="AA11" s="42">
         <f>(AA10-V10)/V10</f>
-        <v>-0.72993277975484383</v>
+        <v>-0.46461051799130093</v>
       </c>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
@@ -8381,9 +8981,12 @@
       <c r="W12" s="2">
         <v>91</v>
       </c>
+      <c r="X12" s="2">
+        <v>108</v>
+      </c>
       <c r="AA12" s="41">
         <f>SUM(W12:Z12)</f>
-        <v>91</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
@@ -8458,12 +9061,14 @@
       <c r="W13" s="32">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="X13" s="32"/>
+      <c r="X13" s="32">
+        <v>4.3999999999999997E-2</v>
+      </c>
       <c r="Y13" s="32"/>
       <c r="Z13" s="32"/>
       <c r="AA13" s="45">
         <f>AA12/AA6</f>
-        <v>3.6139793486894362E-2</v>
+        <v>3.9847817380857027E-2</v>
       </c>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.25">
@@ -8547,12 +9152,14 @@
       <c r="W15" s="14">
         <v>2667</v>
       </c>
-      <c r="X15" s="14"/>
+      <c r="X15" s="14">
+        <v>3287</v>
+      </c>
       <c r="Y15" s="14"/>
       <c r="Z15" s="14"/>
       <c r="AA15" s="47">
         <f>SUM(W15:Z15)</f>
-        <v>2667</v>
+        <v>5954</v>
       </c>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.25">
@@ -8626,12 +9233,14 @@
       <c r="W16" s="14">
         <v>860</v>
       </c>
-      <c r="X16" s="14"/>
+      <c r="X16" s="14">
+        <v>956</v>
+      </c>
       <c r="Y16" s="14"/>
       <c r="Z16" s="14"/>
       <c r="AA16" s="47">
         <f>SUM(W16:Z16)</f>
-        <v>860</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.25">
@@ -8719,12 +9328,12 @@
         <v>13438</v>
       </c>
       <c r="W17" s="12">
-        <f t="shared" ref="W17:AA17" si="12">SUM(W15:W16)</f>
+        <f t="shared" ref="W17" si="12">SUM(W15:W16)</f>
         <v>3527</v>
       </c>
       <c r="X17" s="12">
         <f>SUM(X15:X16)</f>
-        <v>0</v>
+        <v>4243</v>
       </c>
       <c r="Y17" s="12">
         <f t="shared" ref="Y17:Z17" si="13">SUM(Y15:Y16)</f>
@@ -8736,7 +9345,7 @@
       </c>
       <c r="AA17" s="48">
         <f>SUM(AA15:AA16)</f>
-        <v>3527</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.25">
@@ -8813,7 +9422,7 @@
       </c>
       <c r="X18" s="38">
         <f>(X17-S17)/S17</f>
-        <v>-1</v>
+        <v>0.27878239903556357</v>
       </c>
       <c r="Y18" s="38">
         <f t="shared" ref="Y18" si="23">(Y17-T17)/T17</f>
@@ -8825,7 +9434,7 @@
       </c>
       <c r="AA18" s="42">
         <f>(AA17-V17)/V17</f>
-        <v>-0.73753534752195271</v>
+        <v>-0.42178895668998362</v>
       </c>
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.25">
@@ -8899,12 +9508,14 @@
       <c r="W19" s="14">
         <v>987</v>
       </c>
-      <c r="X19" s="14"/>
+      <c r="X19" s="14">
+        <v>1051</v>
+      </c>
       <c r="Y19" s="14"/>
       <c r="Z19" s="14"/>
       <c r="AA19" s="48">
         <f>SUM(W19:Z19)</f>
-        <v>987</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.25">
@@ -8978,12 +9589,14 @@
       <c r="W20" s="25">
         <v>0.28000000000000003</v>
       </c>
-      <c r="X20" s="25"/>
+      <c r="X20" s="25">
+        <v>0.248</v>
+      </c>
       <c r="Y20" s="25"/>
       <c r="Z20" s="25"/>
       <c r="AA20" s="43">
         <f>AA19/AA17</f>
-        <v>0.27984122483697194</v>
+        <v>0.26229086229086229</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.25">
@@ -9057,12 +9670,14 @@
       <c r="W21" s="14">
         <v>800</v>
       </c>
-      <c r="X21" s="14"/>
+      <c r="X21" s="14">
+        <v>896</v>
+      </c>
       <c r="Y21" s="14"/>
       <c r="Z21" s="14"/>
       <c r="AA21" s="48">
         <f>SUM(W21:Z21)</f>
-        <v>800</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.25">
@@ -9140,7 +9755,7 @@
       </c>
       <c r="X22" s="38">
         <f>(X21-S21)/S21</f>
-        <v>-1</v>
+        <v>2.0501138952164009E-2</v>
       </c>
       <c r="Y22" s="38">
         <f>(Y21-T21)/T21</f>
@@ -9152,7 +9767,7 @@
       </c>
       <c r="AA22" s="42">
         <f>(AA21-V21)/V21</f>
-        <v>-0.74739501105146822</v>
+        <v>-0.46447742342911275</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.25">
@@ -9226,9 +9841,12 @@
       <c r="W23" s="2">
         <v>187</v>
       </c>
+      <c r="X23" s="2">
+        <v>156</v>
+      </c>
       <c r="AA23" s="41">
         <f>SUM(W23:Z23)</f>
-        <v>187</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.25">
@@ -9306,12 +9924,14 @@
       <c r="W24" s="32">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="X24" s="32"/>
+      <c r="X24" s="32">
+        <v>3.6999999999999998E-2</v>
+      </c>
       <c r="Y24" s="32"/>
       <c r="Z24" s="32"/>
       <c r="AA24" s="45">
         <f>AA23/AA17</f>
-        <v>5.3019563368301673E-2</v>
+        <v>4.4144144144144144E-2</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.25">
@@ -9395,12 +10015,14 @@
       <c r="W26" s="14">
         <v>1011</v>
       </c>
-      <c r="X26" s="14"/>
+      <c r="X26" s="14">
+        <v>1187</v>
+      </c>
       <c r="Y26" s="14"/>
       <c r="Z26" s="14"/>
       <c r="AA26" s="47">
         <f>SUM(W26:Z26)</f>
-        <v>1011</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.25">
@@ -9474,12 +10096,14 @@
       <c r="W27" s="14">
         <v>374</v>
       </c>
-      <c r="X27" s="14"/>
+      <c r="X27" s="14">
+        <v>357</v>
+      </c>
       <c r="Y27" s="14"/>
       <c r="Z27" s="14"/>
       <c r="AA27" s="47">
         <f>SUM(W27:Z27)</f>
-        <v>374</v>
+        <v>731</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.25">
@@ -9572,7 +10196,7 @@
       </c>
       <c r="X28" s="12">
         <f>SUM(X26:X27)</f>
-        <v>0</v>
+        <v>1544</v>
       </c>
       <c r="Y28" s="12">
         <f t="shared" ref="Y28:Z28" si="43">SUM(Y26:Y27)</f>
@@ -9584,7 +10208,7 @@
       </c>
       <c r="AA28" s="48">
         <f>SUM(AA26:AA27)</f>
-        <v>1385</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
@@ -9661,7 +10285,7 @@
       </c>
       <c r="X29" s="38">
         <f>(X28-S28)/S28</f>
-        <v>-1</v>
+        <v>0.17952635599694422</v>
       </c>
       <c r="Y29" s="38">
         <f t="shared" ref="Y29" si="53">(Y28-T28)/T28</f>
@@ -9673,7 +10297,7 @@
       </c>
       <c r="AA29" s="42">
         <f>(AA28-V28)/V28</f>
-        <v>-0.73877781969068279</v>
+        <v>-0.44756695586571105</v>
       </c>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.25">
@@ -9747,12 +10371,14 @@
       <c r="W30" s="14">
         <v>356</v>
       </c>
-      <c r="X30" s="14"/>
+      <c r="X30" s="14">
+        <v>378</v>
+      </c>
       <c r="Y30" s="14"/>
       <c r="Z30" s="14"/>
       <c r="AA30" s="48">
         <f>SUM(W30:Z30)</f>
-        <v>356</v>
+        <v>734</v>
       </c>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.25">
@@ -9826,12 +10452,14 @@
       <c r="W31" s="25">
         <v>0.25700000000000001</v>
       </c>
-      <c r="X31" s="25"/>
+      <c r="X31" s="25">
+        <v>0.245</v>
+      </c>
       <c r="Y31" s="25"/>
       <c r="Z31" s="25"/>
       <c r="AA31" s="43">
         <f>AA30/AA28</f>
-        <v>0.25703971119133573</v>
+        <v>0.25059747354045747</v>
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.25">
@@ -9905,12 +10533,14 @@
       <c r="W32" s="14">
         <v>349</v>
       </c>
-      <c r="X32" s="14"/>
+      <c r="X32" s="14">
+        <v>364</v>
+      </c>
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
       <c r="AA32" s="48">
         <f>SUM(W32:Z32)</f>
-        <v>349</v>
+        <v>713</v>
       </c>
     </row>
     <row r="33" spans="2:27" x14ac:dyDescent="0.25">
@@ -9987,7 +10617,7 @@
       </c>
       <c r="X33" s="38">
         <f>(X32-S32)/S32</f>
-        <v>-1</v>
+        <v>0.13395638629283488</v>
       </c>
       <c r="Y33" s="38">
         <f t="shared" ref="Y33" si="64">(Y32-T32)/T32</f>
@@ -9999,7 +10629,7 @@
       </c>
       <c r="AA33" s="42">
         <f>(AA32-V32)/V32</f>
-        <v>-0.73133179368745194</v>
+        <v>-0.45111624326404925</v>
       </c>
     </row>
     <row r="34" spans="2:27" x14ac:dyDescent="0.25">
@@ -10073,9 +10703,12 @@
       <c r="W34" s="2">
         <v>7</v>
       </c>
+      <c r="X34" s="2">
+        <v>14</v>
+      </c>
       <c r="AA34" s="41">
         <f>SUM(W34:Z34)</f>
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="2:27" x14ac:dyDescent="0.25">
@@ -10151,12 +10784,14 @@
       <c r="W35" s="32">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="X35" s="32"/>
+      <c r="X35" s="32">
+        <v>8.9999999999999993E-3</v>
+      </c>
       <c r="Y35" s="32"/>
       <c r="Z35" s="32"/>
       <c r="AA35" s="45">
         <f>AA34/AA28</f>
-        <v>5.0541516245487363E-3</v>
+        <v>7.1696824854899279E-3</v>
       </c>
     </row>
     <row r="36" spans="2:27" x14ac:dyDescent="0.25">
@@ -10259,12 +10894,14 @@
       <c r="W37" s="24">
         <v>66.599999999999994</v>
       </c>
-      <c r="X37" s="24"/>
+      <c r="X37" s="24">
+        <v>77.7</v>
+      </c>
       <c r="Y37" s="24"/>
       <c r="Z37" s="24"/>
       <c r="AA37" s="47">
         <f>SUM(W37:Z37)</f>
-        <v>66.599999999999994</v>
+        <v>144.30000000000001</v>
       </c>
     </row>
     <row r="38" spans="2:27" x14ac:dyDescent="0.25">
@@ -10338,12 +10975,14 @@
       <c r="W38" s="24">
         <v>11</v>
       </c>
-      <c r="X38" s="24"/>
+      <c r="X38" s="24">
+        <v>11.1</v>
+      </c>
       <c r="Y38" s="24"/>
       <c r="Z38" s="24"/>
       <c r="AA38" s="47">
         <f>SUM(W38:Z38)</f>
-        <v>11</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.25">
@@ -10436,7 +11075,7 @@
       </c>
       <c r="X39" s="12">
         <f>SUM(X37:X38)</f>
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="Y39" s="12">
         <f t="shared" ref="Y39:Z39" si="81">SUM(Y37:Y38)</f>
@@ -10448,7 +11087,7 @@
       </c>
       <c r="AA39" s="48">
         <f>SUM(AA37:AA38)</f>
-        <v>77.599999999999994</v>
+        <v>166.4</v>
       </c>
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
@@ -10526,7 +11165,7 @@
       </c>
       <c r="X40" s="38">
         <f>(X39-S39)/S39</f>
-        <v>-1</v>
+        <v>8.0291970802919638E-2</v>
       </c>
       <c r="Y40" s="38">
         <f t="shared" ref="Y40" si="91">(Y39-T39)/T39</f>
@@ -10538,7 +11177,7 @@
       </c>
       <c r="AA40" s="42">
         <f>(AA39-V39)/V39</f>
-        <v>-0.7430463576158941</v>
+        <v>-0.44900662251655626</v>
       </c>
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.25">
@@ -10612,12 +11251,14 @@
       <c r="W41" s="49">
         <v>17.899999999999999</v>
       </c>
-      <c r="X41" s="49"/>
+      <c r="X41" s="49">
+        <v>18.7</v>
+      </c>
       <c r="Y41" s="49"/>
       <c r="Z41" s="49"/>
       <c r="AA41" s="50">
         <f>SUM(W41:Z41)</f>
-        <v>17.899999999999999</v>
+        <v>36.599999999999994</v>
       </c>
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.25">
@@ -10691,12 +11332,14 @@
       <c r="W42" s="35">
         <v>0.23</v>
       </c>
-      <c r="X42" s="35"/>
+      <c r="X42" s="35">
+        <v>0.21</v>
+      </c>
       <c r="Y42" s="35"/>
       <c r="Z42" s="35"/>
       <c r="AA42" s="43">
         <f>AA41/AA39</f>
-        <v>0.23067010309278349</v>
+        <v>0.21995192307692304</v>
       </c>
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.25">
@@ -10770,12 +11413,14 @@
       <c r="W43" s="49">
         <v>15.8</v>
       </c>
-      <c r="X43" s="49"/>
+      <c r="X43" s="49">
+        <v>15.7</v>
+      </c>
       <c r="Y43" s="49"/>
       <c r="Z43" s="49"/>
       <c r="AA43" s="50">
         <f>SUM(W43:Z43)</f>
-        <v>15.8</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.25">
@@ -10853,7 +11498,7 @@
       </c>
       <c r="X44" s="38">
         <f t="shared" ref="X44" si="95">(X43-S43)/S43</f>
-        <v>-1</v>
+        <v>9.0277777777777707E-2</v>
       </c>
       <c r="Y44" s="38">
         <f t="shared" ref="Y44" si="96">(Y43-T43)/T43</f>
@@ -10865,7 +11510,7 @@
       </c>
       <c r="AA44" s="42">
         <f t="shared" ref="AA44" si="98">(AA43-V43)/V43</f>
-        <v>-0.72711571675302233</v>
+        <v>-0.45595854922279794</v>
       </c>
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.25">
@@ -10939,12 +11584,14 @@
       <c r="W45" s="49">
         <v>2.1</v>
       </c>
-      <c r="X45" s="49"/>
+      <c r="X45" s="49">
+        <v>3</v>
+      </c>
       <c r="Y45" s="49"/>
       <c r="Z45" s="49"/>
       <c r="AA45" s="50">
         <f>SUM(W45:Z45)</f>
-        <v>2.1</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.25">
@@ -11020,12 +11667,14 @@
       <c r="W46" s="37">
         <v>2.7E-2</v>
       </c>
-      <c r="X46" s="37"/>
+      <c r="X46" s="37">
+        <v>3.4000000000000002E-2</v>
+      </c>
       <c r="Y46" s="32"/>
       <c r="Z46" s="32"/>
       <c r="AA46" s="45">
         <f>AA45/AA39</f>
-        <v>2.7061855670103097E-2</v>
+        <v>3.0649038461538457E-2</v>
       </c>
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.25">
@@ -11129,12 +11778,14 @@
       <c r="W48" s="49">
         <v>25.1</v>
       </c>
-      <c r="X48" s="49"/>
+      <c r="X48" s="49">
+        <v>31.9</v>
+      </c>
       <c r="Y48" s="49"/>
       <c r="Z48" s="49"/>
       <c r="AA48" s="51">
         <f>SUM(W48:Z48)</f>
-        <v>25.1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.25">
@@ -11208,12 +11859,14 @@
       <c r="W49" s="49">
         <v>14.9</v>
       </c>
-      <c r="X49" s="49"/>
+      <c r="X49" s="49">
+        <v>15.8</v>
+      </c>
       <c r="Y49" s="49"/>
       <c r="Z49" s="49"/>
       <c r="AA49" s="51">
         <f>SUM(W49:Z49)</f>
-        <v>14.9</v>
+        <v>30.700000000000003</v>
       </c>
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.25">
@@ -11306,7 +11959,7 @@
       </c>
       <c r="X50" s="52">
         <f>SUM(X48:X49)</f>
-        <v>0</v>
+        <v>47.7</v>
       </c>
       <c r="Y50" s="52">
         <f t="shared" ref="Y50:Z50" si="116">SUM(Y48:Y49)</f>
@@ -11318,7 +11971,7 @@
       </c>
       <c r="AA50" s="50">
         <f>SUM(AA48:AA49)</f>
-        <v>40</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.25">
@@ -11396,7 +12049,7 @@
       </c>
       <c r="X51" s="38">
         <f>(X50-S50)/S50</f>
-        <v>-1</v>
+        <v>9.4036697247706455E-2</v>
       </c>
       <c r="Y51" s="38">
         <f t="shared" ref="Y51" si="126">(Y50-T50)/T50</f>
@@ -11408,7 +12061,7 @@
       </c>
       <c r="AA51" s="42">
         <f>(AA50-V50)/V50</f>
-        <v>-0.7782705099778271</v>
+        <v>-0.51385809312638586</v>
       </c>
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.25">
@@ -11482,12 +12135,14 @@
       <c r="W52" s="49">
         <v>14.4</v>
       </c>
-      <c r="X52" s="49"/>
+      <c r="X52" s="49">
+        <v>15.4</v>
+      </c>
       <c r="Y52" s="49"/>
       <c r="Z52" s="49"/>
       <c r="AA52" s="50">
         <f>SUM(W52:Z52)</f>
-        <v>14.4</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="53" spans="2:27" x14ac:dyDescent="0.25">
@@ -11561,12 +12216,14 @@
       <c r="W53" s="35">
         <v>0.36</v>
       </c>
-      <c r="X53" s="35"/>
+      <c r="X53" s="35">
+        <v>0.32300000000000001</v>
+      </c>
       <c r="Y53" s="35"/>
       <c r="Z53" s="35"/>
       <c r="AA53" s="43">
         <f>AA52/AA50</f>
-        <v>0.36</v>
+        <v>0.33979475484606614</v>
       </c>
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.25">
@@ -11640,12 +12297,14 @@
       <c r="W54" s="34">
         <v>12.7</v>
       </c>
-      <c r="X54" s="34"/>
+      <c r="X54" s="34">
+        <v>13.3</v>
+      </c>
       <c r="Y54" s="34"/>
       <c r="Z54" s="34"/>
       <c r="AA54" s="41">
         <f>SUM(W54:Z54)</f>
-        <v>12.7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="2:27" x14ac:dyDescent="0.25">
@@ -11723,7 +12382,7 @@
       </c>
       <c r="X55" s="38">
         <f>(X54-S54)/S54</f>
-        <v>-1</v>
+        <v>9.917355371900835E-2</v>
       </c>
       <c r="Y55" s="38">
         <f t="shared" ref="Y55" si="135">(Y54-T54)/T54</f>
@@ -11735,7 +12394,7 @@
       </c>
       <c r="AA55" s="42">
         <f>(AA54-V54)/V54</f>
-        <v>-0.73975409836065564</v>
+        <v>-0.46721311475409832</v>
       </c>
     </row>
     <row r="56" spans="2:27" x14ac:dyDescent="0.25">
@@ -11809,12 +12468,14 @@
       <c r="W56" s="49">
         <v>1.7</v>
       </c>
-      <c r="X56" s="49"/>
+      <c r="X56" s="49">
+        <v>2.1</v>
+      </c>
       <c r="Y56" s="49"/>
       <c r="Z56" s="49"/>
       <c r="AA56" s="50">
         <f>SUM(W56:Z56)</f>
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="57" spans="2:27" x14ac:dyDescent="0.25">
@@ -11890,12 +12551,14 @@
       <c r="W57" s="37">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="X57" s="37"/>
+      <c r="X57" s="37">
+        <v>4.3999999999999997E-2</v>
+      </c>
       <c r="Y57" s="32"/>
       <c r="Z57" s="32"/>
       <c r="AA57" s="45">
         <f>AA56/AA50</f>
-        <v>4.2499999999999996E-2</v>
+        <v>4.3329532497149367E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11908,85 +12571,85 @@
   <dimension ref="C6:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.83203125" style="54"/>
-    <col min="3" max="3" width="13.33203125" style="54" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" style="54" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="54"/>
-    <col min="6" max="6" width="14.5" style="54" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" style="54" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" style="54" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="54"/>
+    <col min="1" max="2" width="10.83203125" style="53"/>
+    <col min="3" max="3" width="13.33203125" style="53" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" style="53" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="53"/>
+    <col min="6" max="6" width="14.5" style="53" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" style="53" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="53" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="53"/>
   </cols>
   <sheetData>
     <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55" t="s">
+      <c r="E6" s="54"/>
+      <c r="F6" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="54" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="55">
         <v>500</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12022,15 +12685,15 @@
       </c>
       <c r="D5" s="31">
         <f>Modell!$B$9/Modell!AG12</f>
-        <v>10.684273446464207</v>
+        <v>12.561811396781362</v>
       </c>
       <c r="E5" s="31">
         <f>Modell!$B$9/Modell!AH12</f>
-        <v>9.6027444305480305</v>
+        <v>8.6356827136650871</v>
       </c>
       <c r="F5" s="31">
         <f>Modell!$B$9/Modell!AI12</f>
-        <v>8.6550488240122938</v>
+        <v>7.8066414387440624</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -12039,15 +12702,15 @@
       </c>
       <c r="D6" s="31">
         <f>Modell!$B$4/Modell!AG18</f>
-        <v>17.112031170752896</v>
+        <v>21.012518821317848</v>
       </c>
       <c r="E6" s="31">
         <f>Modell!$B$4/Modell!AH18</f>
-        <v>15.176886168831501</v>
+        <v>13.537500225011167</v>
       </c>
       <c r="F6" s="31">
         <f>Modell!$B$4/Modell!AI18</f>
-        <v>13.519725834911723</v>
+        <v>12.110731882685855</v>
       </c>
     </row>
   </sheetData>
